--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45215</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45112</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45363</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46184</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45703</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>45146</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>46128</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>45455</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>44637</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>44570</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45118</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44868</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44459</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44966</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45763</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45160</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45328</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>44946</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>45117</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45117</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>44917</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45264</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45180</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45709</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>44683</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>44958</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45232</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45359</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>44981</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45218</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45216</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>45254</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44981</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45696</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45953</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45974</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45534</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44775</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45587</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45112</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45112</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45288</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45448</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45561</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45803</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45897</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44524</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45762</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45248</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>44881</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>46140</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>46140</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>46141</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>45215</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45197</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44602</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>44510</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45308</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44726</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>45930</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>45471</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>45933</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>45621</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>45939</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>45938</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>45358</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>45117</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>45276</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>45254</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>45951</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>45954</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45272</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45954</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44494</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>45957</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45112</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>45112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45288</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45763</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>45763</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44882</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45180</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>45180</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45308</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>45982</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>45982</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>45993</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>45993</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45993</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45993</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45992</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45117</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45117</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45992</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45373</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45611</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45994</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45999</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>44754</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45629</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45721</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>46021</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>46021</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>46174</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>46037</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>44882</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>44658</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>46044</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>46048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>46048</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45308</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>46052</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>44915</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>46052</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>46052</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>46052</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>45604</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>46059</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45701</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45112</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45112</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45624</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>46184</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45219</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>44946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>46084</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>46188</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>46090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>46090</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46188</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45377</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>46092</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>46093</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44883</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>46093</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44900</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>46191</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44893</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46099</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>44900</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>46100</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45117</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45568</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44882</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45070</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44914</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44914</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45586</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>46134</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45071</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44708</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45303</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45310</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45112</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45112</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45112</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>46251</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>46251</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45476</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>46206</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45041</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>44628</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44992</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45117</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45117</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>45117</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45624</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>46259</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45112</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>46259</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>44537</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45117</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45117</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45254</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45112</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45629</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45453</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>46272</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>46120</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>46231</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45455</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45784</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45377</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>46283</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>46283</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45713</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45476</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45825</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45722</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>45715</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45834</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45836</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45838</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45476</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45664</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45872</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45934</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>46154</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>46246</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE242"/>
+  <dimension ref="A1:AE239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45215</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45112</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45363</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46184</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30745-2023</t>
+          <t>A 7339-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45112</v>
+        <v>45703</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3077,42 +3077,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30745-2023 artfynd.xlsx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30745-2023 karta.png", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30745-2023 georefererad karta.tif", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30745-2023 FSC-klagomål.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30745-2023 FSC-klagomål mail.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30745-2023 tillsynsbegäran.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30745-2023 tillsynsbegäran mail.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7339-2025</t>
+          <t>A 30745-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45703</v>
+        <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3182,35 +3182,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30745-2023 artfynd.xlsx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30745-2023 karta.png", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30745-2023 georefererad karta.tif", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30745-2023 FSC-klagomål.docx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30745-2023 FSC-klagomål mail.docx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30745-2023 tillsynsbegäran.docx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30745-2023 tillsynsbegäran mail.docx", "A 30745-2023")</f>
         <v/>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
         <v>45146</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30662-2023</t>
+          <t>A 18822-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45112</v>
+        <v>46128</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3356,23 +3356,23 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
@@ -3380,10 +3380,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3392,46 +3392,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18822-2026</t>
+          <t>A 30662-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46128</v>
+        <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3485,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3497,39 +3497,39 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>45455</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>44637</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>44570</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30633-2023</t>
+          <t>A 30772-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4607,7 +4607,7 @@
         <v>45112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31889-2023</t>
+          <t>A 30633-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45118</v>
+        <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51229-2022</t>
+          <t>A 4782-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44868</v>
+        <v>45328</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30769-2023</t>
+          <t>A 51229-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45112</v>
+        <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30794-2023</t>
+          <t>A 30769-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4899,7 +4899,7 @@
         <v>45112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50647-2021</t>
+          <t>A 30794-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44459</v>
+        <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44966</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45763</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38074-2023</t>
+          <t>A 3237-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45160</v>
+        <v>44946</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30772-2023</t>
+          <t>A 31724-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4782-2024</t>
+          <t>A 31726-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45328</v>
+        <v>45117</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3237-2023</t>
+          <t>A 61671-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44946</v>
+        <v>44917</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5466,7 +5466,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31724-2023</t>
+          <t>A 31889-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45117</v>
+        <v>45118</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5539,7 +5539,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31726-2023</t>
+          <t>A 61318-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45117</v>
+        <v>45264</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61671-2022</t>
+          <t>A 42483-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44917</v>
+        <v>45180</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56334-2024</t>
+          <t>A 47265-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45624</v>
+        <v>45586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5758,7 +5758,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61318-2023</t>
+          <t>A 8570-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45264</v>
+        <v>45709</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42483-2023</t>
+          <t>A 17925-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45180</v>
+        <v>44683</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8570-2025</t>
+          <t>A 5072-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45709</v>
+        <v>44958</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47265-2024</t>
+          <t>A 54295-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45586</v>
+        <v>45232</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17925-2022</t>
+          <t>A 56334-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44683</v>
+        <v>45624</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 5072-2023</t>
+          <t>A 47980-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44958</v>
+        <v>45204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6196,7 +6196,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54295-2023</t>
+          <t>A 9401-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45232</v>
+        <v>45359</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47980-2023</t>
+          <t>A 9527-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45204</v>
+        <v>44981</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9401-2024</t>
+          <t>A 36650-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45359</v>
+        <v>45872</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6415,7 +6415,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9527-2023</t>
+          <t>A 50981-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6429,10 +6429,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44981</v>
+        <v>45218</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6444,8 +6444,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6488,7 +6493,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 50981-2023</t>
+          <t>A 50302-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6502,10 +6507,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45218</v>
+        <v>45216</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6517,13 +6522,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 50302-2023</t>
+          <t>A 19644-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45216</v>
+        <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59472-2023</t>
+          <t>A 47522-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45254</v>
+        <v>45587</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6668,8 +6668,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6712,7 +6717,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9530-2023</t>
+          <t>A 65143-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6726,10 +6731,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44981</v>
+        <v>45288</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6742,7 +6747,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6785,7 +6790,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6064-2025</t>
+          <t>A 59472-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6799,10 +6804,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45696</v>
+        <v>45254</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6815,7 +6820,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6858,7 +6863,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52371-2025</t>
+          <t>A 9530-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6872,10 +6877,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45953</v>
+        <v>44981</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6888,7 +6893,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6931,7 +6936,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56305-2025</t>
+          <t>A 31546-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6941,14 +6946,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45974</v>
+        <v>44775</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6961,7 +6966,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7004,7 +7009,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36131-2024</t>
+          <t>A 40774-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7018,10 +7023,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45534</v>
+        <v>45897</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7034,7 +7039,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>6.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7077,7 +7082,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31546-2022</t>
+          <t>A 6064-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7087,14 +7092,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44775</v>
+        <v>45696</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7107,7 +7112,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7150,7 +7155,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36532-2024</t>
+          <t>A 52371-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7164,10 +7169,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45537</v>
+        <v>45953</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7180,7 +7185,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7223,7 +7228,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47522-2024</t>
+          <t>A 56305-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7237,10 +7242,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45587</v>
+        <v>45974</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7252,13 +7257,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30628-2023</t>
+          <t>A 36131-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45112</v>
+        <v>45534</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7374,7 +7374,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30643-2023</t>
+          <t>A 36532-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45112</v>
+        <v>45537</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7447,7 +7447,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 65143-2023</t>
+          <t>A 25694-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45288</v>
+        <v>45803</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 22834-2024</t>
+          <t>A 25928-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45448</v>
+        <v>45090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7593,7 +7593,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41910-2024</t>
+          <t>A 30628-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45561</v>
+        <v>45112</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7666,7 +7666,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25694-2025</t>
+          <t>A 30643-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7680,10 +7680,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45803</v>
+        <v>45112</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7739,7 +7739,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40774-2025</t>
+          <t>A 22834-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7753,10 +7753,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45897</v>
+        <v>45448</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.7</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7812,7 +7812,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 67455-2021</t>
+          <t>A 41910-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44524</v>
+        <v>45561</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7885,7 +7885,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18305-2025</t>
+          <t>A 47279-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45762</v>
+        <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7958,7 +7958,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58093-2023</t>
+          <t>A 20598-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7972,10 +7972,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45248</v>
+        <v>46140</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8031,7 +8031,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25928-2023</t>
+          <t>A 48212-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45090</v>
+        <v>45933</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8104,7 +8104,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 54144-2022</t>
+          <t>A 20600-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44881</v>
+        <v>46140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8177,7 +8177,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20598-2026</t>
+          <t>A 67455-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46140</v>
+        <v>44524</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8250,7 +8250,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20600-2026</t>
+          <t>A 20782-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8264,10 +8264,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8323,7 +8323,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20782-2026</t>
+          <t>A 58093-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8337,10 +8337,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46141</v>
+        <v>45248</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8396,7 +8396,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50057-2023</t>
+          <t>A 49460-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45215</v>
+        <v>45939</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8469,7 +8469,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46511-2023</t>
+          <t>A 54144-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8483,10 +8483,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45197</v>
+        <v>44881</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8542,7 +8542,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 6653-2022</t>
+          <t>A 49269-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44602</v>
+        <v>45938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8615,7 +8615,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 64207-2021</t>
+          <t>A 50057-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44510</v>
+        <v>45215</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8688,7 +8688,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2006-2024</t>
+          <t>A 46511-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8702,10 +8702,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45308</v>
+        <v>45197</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8761,7 +8761,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24368-2022</t>
+          <t>A 51613-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8775,10 +8775,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44726</v>
+        <v>45951</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47279-2025</t>
+          <t>A 52513-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45930</v>
+        <v>45954</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.8</v>
+        <v>0.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8907,7 +8907,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47258-2025</t>
+          <t>A 52511-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45930</v>
+        <v>45954</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8980,7 +8980,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 27103-2024</t>
+          <t>A 52939-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45471</v>
+        <v>45957</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9053,7 +9053,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48212-2025</t>
+          <t>A 6653-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45933</v>
+        <v>44602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9126,7 +9126,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 55159-2024</t>
+          <t>A 64207-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45621</v>
+        <v>44510</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9199,7 +9199,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 49460-2025</t>
+          <t>A 2006-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45939</v>
+        <v>45308</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49269-2025</t>
+          <t>A 24368-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45938</v>
+        <v>44726</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9345,7 +9345,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 38586-2023</t>
+          <t>A 27103-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9359,10 +9359,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45162</v>
+        <v>45471</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9159-2024</t>
+          <t>A 55159-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9432,10 +9432,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45358</v>
+        <v>45621</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9491,7 +9491,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31746-2023</t>
+          <t>A 38586-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45117</v>
+        <v>45162</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 63725-2023</t>
+          <t>A 9159-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9578,10 +9578,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45276</v>
+        <v>45358</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9637,7 +9637,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59613-2023</t>
+          <t>A 31746-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9651,10 +9651,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45254</v>
+        <v>45117</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 51613-2025</t>
+          <t>A 63725-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45951</v>
+        <v>45276</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9783,7 +9783,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52513-2025</t>
+          <t>A 58137-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45954</v>
+        <v>45982</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9856,7 +9856,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62986-2023</t>
+          <t>A 58139-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45272</v>
+        <v>45982</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9929,7 +9929,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 52511-2025</t>
+          <t>A 59613-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45954</v>
+        <v>45254</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10002,7 +10002,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59816-2021</t>
+          <t>A 60089-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44494</v>
+        <v>45993</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10075,7 +10075,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 52939-2025</t>
+          <t>A 60093-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45957</v>
+        <v>45993</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10148,7 +10148,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 30650-2023</t>
+          <t>A 60091-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10162,10 +10162,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45112</v>
+        <v>45993</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10221,7 +10221,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30637-2023</t>
+          <t>A 60092-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10235,10 +10235,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45112</v>
+        <v>45993</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 65118-2023</t>
+          <t>A 59871-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45288</v>
+        <v>45992</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18613-2025</t>
+          <t>A 62986-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45763</v>
+        <v>45272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10440,7 +10440,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 18614-2025</t>
+          <t>A 59816-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45763</v>
+        <v>44494</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10513,7 +10513,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 54289-2022</t>
+          <t>A 59872-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44882</v>
+        <v>45992</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10586,7 +10586,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 42250-2023</t>
+          <t>A 24965-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10600,10 +10600,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45180</v>
+        <v>46174</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10659,7 +10659,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 42256-2023</t>
+          <t>A 60181-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10673,10 +10673,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45180</v>
+        <v>45994</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10732,7 +10732,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1921-2024</t>
+          <t>A 60946-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45308</v>
+        <v>45999</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 58137-2025</t>
+          <t>A 30650-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10819,10 +10819,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45982</v>
+        <v>45112</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10878,7 +10878,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 58139-2025</t>
+          <t>A 30637-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10892,10 +10892,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45982</v>
+        <v>45112</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10951,7 +10951,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60089-2025</t>
+          <t>A 65118-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10965,10 +10965,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45993</v>
+        <v>45288</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60093-2025</t>
+          <t>A 18613-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11038,10 +11038,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45993</v>
+        <v>45763</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11097,7 +11097,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60091-2025</t>
+          <t>A 18614-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11111,10 +11111,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45993</v>
+        <v>45763</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11170,7 +11170,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 60092-2025</t>
+          <t>A 54289-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11184,10 +11184,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45993</v>
+        <v>44882</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11243,7 +11243,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 59871-2025</t>
+          <t>A 10610-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11257,10 +11257,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45992</v>
+        <v>45721</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31711-2023</t>
+          <t>A 64003-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11330,10 +11330,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45117</v>
+        <v>46021</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 31727-2023</t>
+          <t>A 64005-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11403,10 +11403,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45117</v>
+        <v>46021</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 59872-2025</t>
+          <t>A 42250-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11476,10 +11476,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45992</v>
+        <v>45180</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11535,7 +11535,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11605-2024</t>
+          <t>A 42256-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45373</v>
+        <v>45180</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11608,7 +11608,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 53055-2024</t>
+          <t>A 1921-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11622,10 +11622,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45611</v>
+        <v>45308</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11681,7 +11681,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 60181-2025</t>
+          <t>A 26642-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45994</v>
+        <v>46184</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11754,7 +11754,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 60946-2025</t>
+          <t>A 2497-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11768,10 +11768,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45999</v>
+        <v>46037</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 29658-2022</t>
+          <t>A 27098-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44754</v>
+        <v>46188</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11900,7 +11900,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57036-2024</t>
+          <t>A 27248-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11914,10 +11914,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45629</v>
+        <v>46188</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11973,7 +11973,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 10610-2025</t>
+          <t>A 31711-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11987,10 +11987,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45721</v>
+        <v>45117</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12046,7 +12046,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 64003-2025</t>
+          <t>A 31727-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12060,10 +12060,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12119,7 +12119,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 64005-2025</t>
+          <t>A 11605-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12133,10 +12133,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46021</v>
+        <v>45373</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12192,7 +12192,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 24965-2026</t>
+          <t>A 4119-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12206,10 +12206,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46174</v>
+        <v>46044</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12221,8 +12221,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12265,7 +12270,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 2497-2026</t>
+          <t>A 4587-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12279,10 +12284,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12295,7 +12300,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12338,7 +12343,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 54287-2022</t>
+          <t>A 4588-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12352,10 +12357,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44882</v>
+        <v>46048</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12368,7 +12373,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12411,7 +12416,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15112-2022</t>
+          <t>A 27782-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12425,10 +12430,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44658</v>
+        <v>46191</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12441,7 +12446,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12484,7 +12489,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 4119-2026</t>
+          <t>A 53055-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12498,10 +12503,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46044</v>
+        <v>45611</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12513,13 +12518,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12562,7 +12562,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 4587-2026</t>
+          <t>A 6071-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12576,10 +12576,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12635,7 +12635,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4588-2026</t>
+          <t>A 6074-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12649,10 +12649,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 1922-2024</t>
+          <t>A 6104-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12722,10 +12722,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45308</v>
+        <v>46052</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12781,7 +12781,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 6071-2026</t>
+          <t>A 6103-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12798,7 +12798,7 @@
         <v>46052</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 61334-2022</t>
+          <t>A 7546-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44915</v>
+        <v>46059</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12927,7 +12927,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 6074-2026</t>
+          <t>A 29658-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12941,10 +12941,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46052</v>
+        <v>44754</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13000,7 +13000,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 6104-2026</t>
+          <t>A 57036-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13014,10 +13014,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46052</v>
+        <v>45629</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6103-2026</t>
+          <t>A 11584-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13087,10 +13087,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46052</v>
+        <v>46084</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 51564-2024</t>
+          <t>A 12503-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13160,10 +13160,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45604</v>
+        <v>46090</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13219,7 +13219,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 7546-2026</t>
+          <t>A 12469-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13233,10 +13233,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46059</v>
+        <v>46090</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13292,7 +13292,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 7046-2025</t>
+          <t>A 12879-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13302,14 +13302,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45701</v>
+        <v>46092</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13321,8 +13321,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13365,7 +13370,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 30760-2023</t>
+          <t>A 13120-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13379,10 +13384,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45112</v>
+        <v>46093</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13395,7 +13400,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13438,7 +13443,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 30762-2023</t>
+          <t>A 13121-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13452,10 +13457,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45112</v>
+        <v>46093</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13468,7 +13473,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13511,7 +13516,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 56331-2024</t>
+          <t>A 58011-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13525,10 +13530,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45624</v>
+        <v>44900</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13541,7 +13546,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13584,7 +13589,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 26642-2026</t>
+          <t>A 56452-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13598,10 +13603,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46184</v>
+        <v>44893</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13614,7 +13619,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13657,7 +13662,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 51314-2023</t>
+          <t>A 14111-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13667,14 +13672,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45219</v>
+        <v>46099</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13687,7 +13692,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13730,7 +13735,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 3238-2023</t>
+          <t>A 54287-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13744,10 +13749,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44946</v>
+        <v>44882</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13760,7 +13765,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13803,7 +13808,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 11584-2026</t>
+          <t>A 58010-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13817,10 +13822,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46084</v>
+        <v>44900</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13833,7 +13838,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13876,7 +13881,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 27098-2026</t>
+          <t>A 15112-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13890,10 +13895,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46188</v>
+        <v>44658</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13906,7 +13911,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13949,7 +13954,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 12503-2026</t>
+          <t>A 14545-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13959,14 +13964,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13979,7 +13984,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14022,7 +14027,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12469-2026</t>
+          <t>A 1922-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14036,10 +14041,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46090</v>
+        <v>45308</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14052,7 +14057,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14095,7 +14100,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 27248-2026</t>
+          <t>A 33852-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14109,10 +14114,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46188</v>
+        <v>46251</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14125,7 +14130,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14168,7 +14173,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 12160-2024</t>
+          <t>A 33853-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14182,10 +14187,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45377</v>
+        <v>46251</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14198,7 +14203,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14241,7 +14246,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 12879-2026</t>
+          <t>A 61334-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14251,14 +14256,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46092</v>
+        <v>44915</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14270,13 +14275,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14319,7 +14319,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 13120-2026</t>
+          <t>A 30098-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14333,10 +14333,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46093</v>
+        <v>46206</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14392,7 +14392,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 54659-2022</t>
+          <t>A 51564-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14406,10 +14406,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44883</v>
+        <v>45604</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14465,7 +14465,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13121-2026</t>
+          <t>A 7046-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14479,10 +14479,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46093</v>
+        <v>45701</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14538,7 +14538,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 58011-2022</t>
+          <t>A 30760-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14552,10 +14552,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44900</v>
+        <v>45112</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 27782-2026</t>
+          <t>A 30762-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14625,10 +14625,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46191</v>
+        <v>45112</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14684,7 +14684,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 56452-2022</t>
+          <t>A 56331-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14698,10 +14698,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44893</v>
+        <v>45624</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 14111-2026</t>
+          <t>A 51314-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14767,14 +14767,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46099</v>
+        <v>45219</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14830,7 +14830,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 58010-2022</t>
+          <t>A 3238-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14844,10 +14844,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44900</v>
+        <v>44946</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 14545-2026</t>
+          <t>A 12160-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14913,14 +14913,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46100</v>
+        <v>45377</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14976,7 +14976,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31718-2023</t>
+          <t>A 54659-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14990,10 +14990,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45117</v>
+        <v>44883</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15049,7 +15049,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 43398-2024</t>
+          <t>A 35071-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45568</v>
+        <v>46259</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15122,7 +15122,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 54311-2022</t>
+          <t>A 31718-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15136,10 +15136,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44882</v>
+        <v>45117</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15195,7 +15195,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 22443-2023</t>
+          <t>A 35072-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15209,10 +15209,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45070</v>
+        <v>46259</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15268,7 +15268,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 60792-2022</t>
+          <t>A 43398-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44914</v>
+        <v>45568</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15341,7 +15341,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 61026-2022</t>
+          <t>A 54311-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15355,10 +15355,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44914</v>
+        <v>44882</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15414,7 +15414,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 47264-2024</t>
+          <t>A 22443-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45586</v>
+        <v>45070</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15487,7 +15487,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 19644-2026</t>
+          <t>A 60792-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15501,10 +15501,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46134</v>
+        <v>44914</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15560,7 +15560,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 22541-2023</t>
+          <t>A 61026-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45071</v>
+        <v>44914</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15633,7 +15633,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 21751-2022</t>
+          <t>A 47264-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15647,10 +15647,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44708</v>
+        <v>45586</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15706,7 +15706,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 1395-2024</t>
+          <t>A 22541-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15720,10 +15720,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45303</v>
+        <v>45071</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15779,7 +15779,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 2398-2024</t>
+          <t>A 21751-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15793,10 +15793,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45310</v>
+        <v>44708</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15852,7 +15852,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 30793-2023</t>
+          <t>A 1395-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45112</v>
+        <v>45303</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15925,7 +15925,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 30795-2023</t>
+          <t>A 2398-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15939,10 +15939,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45112</v>
+        <v>45310</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15998,7 +15998,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30800-2023</t>
+          <t>A 36861-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16012,10 +16012,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45112</v>
+        <v>46272</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16071,7 +16071,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 33852-2026</t>
+          <t>A 30793-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16085,10 +16085,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46251</v>
+        <v>45112</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16144,7 +16144,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 33853-2026</t>
+          <t>A 30795-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46251</v>
+        <v>45112</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16217,7 +16217,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 28040-2024</t>
+          <t>A 30800-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16231,10 +16231,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45476</v>
+        <v>45112</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 30098-2026</t>
+          <t>A 17434-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16300,14 +16300,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46206</v>
+        <v>46120</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 18337-2023</t>
+          <t>A 28040-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16377,10 +16377,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45041</v>
+        <v>45476</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16436,7 +16436,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 11021-2022</t>
+          <t>A 31907-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44628</v>
+        <v>46231</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16465,8 +16465,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16509,7 +16514,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 11239-2023</t>
+          <t>A 18337-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16523,10 +16528,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44992</v>
+        <v>45041</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16539,7 +16544,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16582,7 +16587,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31717-2023</t>
+          <t>A 11021-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16596,10 +16601,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45117</v>
+        <v>44628</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16612,7 +16617,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16655,7 +16660,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 31719-2023</t>
+          <t>A 11239-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16669,10 +16674,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45117</v>
+        <v>44992</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16685,7 +16690,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16728,7 +16733,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 31745-2023</t>
+          <t>A 12124-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16742,10 +16747,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45117</v>
+        <v>45377</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16757,8 +16762,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16801,7 +16811,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 56335-2024</t>
+          <t>A 31717-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16815,10 +16825,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45624</v>
+        <v>45117</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16831,7 +16841,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16874,7 +16884,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35071-2026</t>
+          <t>A 31719-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16888,10 +16898,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46259</v>
+        <v>45117</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16904,7 +16914,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16947,7 +16957,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 30801-2023</t>
+          <t>A 31745-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16961,10 +16971,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16977,7 +16987,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17020,7 +17030,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 35072-2026</t>
+          <t>A 56335-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17034,10 +17044,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46259</v>
+        <v>45624</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17050,7 +17060,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17093,7 +17103,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 70708-2021</t>
+          <t>A 38521-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17107,10 +17117,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44537</v>
+        <v>46283</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17123,7 +17133,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17166,7 +17176,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31712-2023</t>
+          <t>A 38601-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17180,10 +17190,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45117</v>
+        <v>46283</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17196,7 +17206,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17239,7 +17249,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31715-2023</t>
+          <t>A 30801-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17253,10 +17263,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17269,7 +17279,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>12.4</v>
+        <v>2.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17312,7 +17322,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 59517-2023</t>
+          <t>A 70708-2021</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17326,10 +17336,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45254</v>
+        <v>44537</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17342,7 +17352,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17385,7 +17395,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 30724-2023</t>
+          <t>A 31712-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17399,10 +17409,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17415,7 +17425,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17458,7 +17468,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 57443-2024</t>
+          <t>A 31715-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17472,10 +17482,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45629</v>
+        <v>45117</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17488,7 +17498,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.1</v>
+        <v>12.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17531,7 +17541,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 23330-2024</t>
+          <t>A 47258-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17541,14 +17551,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45453</v>
+        <v>45930</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17560,13 +17570,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17609,7 +17614,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36861-2026</t>
+          <t>A 59517-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17623,10 +17628,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46272</v>
+        <v>45254</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17639,7 +17644,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17682,7 +17687,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 17434-2026</t>
+          <t>A 30724-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17692,14 +17697,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46120</v>
+        <v>45112</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17712,7 +17717,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17755,7 +17760,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 31907-2026</t>
+          <t>A 57443-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17769,10 +17774,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46231</v>
+        <v>45629</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17784,13 +17789,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17833,7 +17833,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23907-2024</t>
+          <t>A 23330-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17843,14 +17843,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45455</v>
+        <v>45453</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17862,8 +17862,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17906,7 +17911,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 21878-2025</t>
+          <t>A 23907-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17920,10 +17925,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45784</v>
+        <v>45455</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17936,7 +17941,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17979,7 +17984,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 43938-2024</t>
+          <t>A 21878-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17993,10 +17998,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45572</v>
+        <v>45784</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18009,7 +18014,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18052,7 +18057,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 12124-2024</t>
+          <t>A 43938-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18066,10 +18071,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45377</v>
+        <v>45572</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18081,13 +18086,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18130,7 +18130,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 38521-2026</t>
+          <t>A 9086-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18144,10 +18144,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46283</v>
+        <v>45713</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18203,7 +18203,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 38601-2026</t>
+          <t>A 28073-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18217,10 +18217,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46283</v>
+        <v>45476</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18276,7 +18276,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 9086-2025</t>
+          <t>A 29794-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18290,10 +18290,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45713</v>
+        <v>45825</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 28073-2024</t>
+          <t>A 10918-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45476</v>
+        <v>45722</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18422,7 +18422,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 29794-2025</t>
+          <t>A 9471-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18436,10 +18436,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45825</v>
+        <v>45715</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18495,7 +18495,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 10918-2025</t>
+          <t>A 31804-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18509,10 +18509,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45722</v>
+        <v>45834</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18568,7 +18568,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 9471-2025</t>
+          <t>A 32320-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18582,10 +18582,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45715</v>
+        <v>45836</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.5</v>
+        <v>11.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18641,7 +18641,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 31804-2025</t>
+          <t>A 32506-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45834</v>
+        <v>45838</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18714,7 +18714,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 32320-2025</t>
+          <t>A 28158-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18728,10 +18728,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45836</v>
+        <v>45476</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>11.7</v>
+        <v>6.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18787,7 +18787,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 32506-2025</t>
+          <t>A 435-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18801,10 +18801,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45838</v>
+        <v>45664</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18860,24 +18860,24 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 28158-2024</t>
+          <t>S 2751-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45476</v>
+        <v>45934</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18933,24 +18933,24 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 435-2025</t>
+          <t>S 1396-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45664</v>
+        <v>46154</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19003,27 +19003,27 @@
       </c>
       <c r="V238" s="2" t="inlineStr"/>
     </row>
-    <row r="239" ht="15" customHeight="1">
+    <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 36650-2025</t>
+          <t>S 2143-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45872</v>
+        <v>46246</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19075,225 +19075,6 @@
         <v>0</v>
       </c>
       <c r="V239" s="2" t="inlineStr"/>
-    </row>
-    <row r="240" ht="15" customHeight="1">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>S 2751-2025</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D240" s="1" t="n">
-        <v>45934</v>
-      </c>
-      <c r="E240" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I240" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J240" t="n">
-        <v>0</v>
-      </c>
-      <c r="K240" t="n">
-        <v>0</v>
-      </c>
-      <c r="L240" t="n">
-        <v>0</v>
-      </c>
-      <c r="M240" t="n">
-        <v>0</v>
-      </c>
-      <c r="N240" t="n">
-        <v>0</v>
-      </c>
-      <c r="O240" t="n">
-        <v>0</v>
-      </c>
-      <c r="P240" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
-      <c r="S240" t="n">
-        <v>0</v>
-      </c>
-      <c r="T240" t="n">
-        <v>0</v>
-      </c>
-      <c r="U240" t="n">
-        <v>0</v>
-      </c>
-      <c r="V240" s="2" t="inlineStr"/>
-    </row>
-    <row r="241" ht="15" customHeight="1">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>S 1396-2026</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D241" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="E241" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I241" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J241" t="n">
-        <v>0</v>
-      </c>
-      <c r="K241" t="n">
-        <v>0</v>
-      </c>
-      <c r="L241" t="n">
-        <v>0</v>
-      </c>
-      <c r="M241" t="n">
-        <v>0</v>
-      </c>
-      <c r="N241" t="n">
-        <v>0</v>
-      </c>
-      <c r="O241" t="n">
-        <v>0</v>
-      </c>
-      <c r="P241" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0</v>
-      </c>
-      <c r="S241" t="n">
-        <v>0</v>
-      </c>
-      <c r="T241" t="n">
-        <v>0</v>
-      </c>
-      <c r="U241" t="n">
-        <v>0</v>
-      </c>
-      <c r="V241" s="2" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>S 2143-2026</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D242" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="E242" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I242" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J242" t="n">
-        <v>0</v>
-      </c>
-      <c r="K242" t="n">
-        <v>0</v>
-      </c>
-      <c r="L242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M242" t="n">
-        <v>0</v>
-      </c>
-      <c r="N242" t="n">
-        <v>0</v>
-      </c>
-      <c r="O242" t="n">
-        <v>0</v>
-      </c>
-      <c r="P242" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
-      <c r="S242" t="n">
-        <v>0</v>
-      </c>
-      <c r="T242" t="n">
-        <v>0</v>
-      </c>
-      <c r="U242" t="n">
-        <v>0</v>
-      </c>
-      <c r="V242" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50011-2023</t>
+          <t>A 30777-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45215</v>
+        <v>45112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,45 +845,267 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Oxtungssvamp
+Vågbandad barkbock
+Tofsmes
+Svartvit flugsnappare
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 50084-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Spillkråka
+Grönsiska
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50084-2025 artfynd.xlsx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50084-2025 karta.png", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50084-2025 georefererad karta.tif", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50084-2025 FSC-klagomål.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50084-2025 FSC-klagomål mail.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50084-2025 tillsynsbegäran.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50084-2025 tillsynsbegäran mail.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50084-2025 prioriterade fågelarter.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 50011-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45215</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Svartbent strandpipare
 Sexfläckig bastardsvärmare
@@ -892,258 +1114,36 @@
 Sädesärla</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 30777-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U5" t="n">
-        <v>8</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Oxtungssvamp
-Vågbandad barkbock
-Tofsmes
-Svartvit flugsnappare
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 50084-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Spillkråka
-Grönsiska
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50084-2025 artfynd.xlsx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50084-2025 karta.png", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50084-2025 georefererad karta.tif", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50084-2025 FSC-klagomål.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50084-2025 FSC-klagomål mail.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50084-2025 tillsynsbegäran.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50084-2025 tillsynsbegäran mail.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50084-2025 prioriterade fågelarter.docx", "A 50084-2025")</f>
         <v/>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 31728-2023</t>
+          <t>A 30671-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1410,19 +1410,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1437,176 +1437,176 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>12</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Järnsparv
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30671-2023 artfynd.xlsx", "A 30671-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30671-2023 karta.png", "A 30671-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30671-2023 georefererad karta.tif", "A 30671-2023")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 30671-2023 karta knärot.png", "A 30671-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30671-2023 FSC-klagomål.docx", "A 30671-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30671-2023 FSC-klagomål mail.docx", "A 30671-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30671-2023 tillsynsbegäran.docx", "A 30671-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30671-2023 tillsynsbegäran mail.docx", "A 30671-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30671-2023 prioriterade fågelarter.docx", "A 30671-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31728-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
         <v>3</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gammelgransskål
 Kattfotslav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31728-2023 artfynd.xlsx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31728-2023 karta.png", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31728-2023 georefererad karta.tif", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31728-2023 FSC-klagomål.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31728-2023 FSC-klagomål mail.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31728-2023 tillsynsbegäran.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31728-2023 tillsynsbegäran mail.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31728-2023 prioriterade fågelarter.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 30671-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>12</v>
-      </c>
-      <c r="U10" t="n">
-        <v>10</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Järnsparv
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30671-2023 artfynd.xlsx", "A 30671-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30671-2023 karta.png", "A 30671-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30671-2023 georefererad karta.tif", "A 30671-2023")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 30671-2023 karta knärot.png", "A 30671-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30671-2023 FSC-klagomål.docx", "A 30671-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30671-2023 FSC-klagomål mail.docx", "A 30671-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30671-2023 tillsynsbegäran.docx", "A 30671-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30671-2023 tillsynsbegäran mail.docx", "A 30671-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30671-2023 prioriterade fågelarter.docx", "A 30671-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30785-2023</t>
+          <t>A 30655-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1623,7 +1623,7 @@
         <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1636,16 +1636,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1669,158 +1669,158 @@
         <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trädporella
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30655-2023 artfynd.xlsx", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30655-2023 karta.png", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30655-2023 georefererad karta.tif", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30655-2023 FSC-klagomål.docx", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30655-2023 FSC-klagomål mail.docx", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30655-2023 tillsynsbegäran.docx", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30655-2023 tillsynsbegäran mail.docx", "A 30655-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 30785-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>5</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Grönvit nattviol
 Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30785-2023 artfynd.xlsx", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30785-2023 karta.png", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30785-2023 georefererad karta.tif", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30785-2023 FSC-klagomål.docx", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30785-2023 FSC-klagomål mail.docx", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30785-2023 tillsynsbegäran.docx", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30785-2023 tillsynsbegäran mail.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 30655-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trädporella
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30655-2023 artfynd.xlsx", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30655-2023 karta.png", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30655-2023 georefererad karta.tif", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30655-2023 FSC-klagomål.docx", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30655-2023 FSC-klagomål mail.docx", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30655-2023 tillsynsbegäran.docx", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30655-2023 tillsynsbegäran mail.docx", "A 30655-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 9930-2024</t>
+          <t>A 30666-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45363</v>
+        <v>45112</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1850,31 +1850,31 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1890,805 +1890,805 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Talltita
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 60380-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9930-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45363</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Större träfjäril
 Spillkråka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 9930-2024 artfynd.xlsx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 9930-2024 karta.png", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 9930-2024 georefererad karta.tif", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 9930-2024 FSC-klagomål.docx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 9930-2024 FSC-klagomål mail.docx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 9930-2024 tillsynsbegäran.docx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 9930-2024 tillsynsbegäran mail.docx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 9930-2024 prioriterade fågelarter.docx", "A 9930-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 13115-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 13115-2026 artfynd.xlsx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 13115-2026 karta.png", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 13115-2026 georefererad karta.tif", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 13115-2026 FSC-klagomål.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 13115-2026 FSC-klagomål mail.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 13115-2026 tillsynsbegäran.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 13115-2026 tillsynsbegäran mail.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26670-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tofsmes
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 26670-2026 artfynd.xlsx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 26670-2026 karta.png", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 26670-2026 georefererad karta.tif", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 26670-2026 FSC-klagomål.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 26670-2026 FSC-klagomål mail.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 26670-2026 tillsynsbegäran.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 26670-2026 tillsynsbegäran mail.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 31714-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>45117</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>2.4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U18" t="n">
         <v>6</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Grönsiska</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 30666-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 30763-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45112</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30763-2023 artfynd.xlsx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30763-2023 karta.png", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30763-2023 georefererad karta.tif", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30763-2023 FSC-klagomål.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30763-2023 FSC-klagomål mail.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30763-2023 tillsynsbegäran.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30763-2023 tillsynsbegäran mail.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30763-2023 prioriterade fågelarter.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 30792-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>45112</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>1.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 13115-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46093</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 13115-2026 artfynd.xlsx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 13115-2026 karta.png", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 13115-2026 georefererad karta.tif", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 13115-2026 FSC-klagomål.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 13115-2026 FSC-klagomål mail.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 13115-2026 tillsynsbegäran.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 13115-2026 tillsynsbegäran mail.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 30763-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30763-2023 artfynd.xlsx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30763-2023 karta.png", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30763-2023 georefererad karta.tif", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30763-2023 FSC-klagomål.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30763-2023 FSC-klagomål mail.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30763-2023 tillsynsbegäran.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30763-2023 tillsynsbegäran mail.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30763-2023 prioriterade fågelarter.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 60380-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 26670-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Tofsmes
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 26670-2026 artfynd.xlsx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 26670-2026 karta.png", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 26670-2026 georefererad karta.tif", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 26670-2026 FSC-klagomål.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 26670-2026 FSC-klagomål mail.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 26670-2026 tillsynsbegäran.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 26670-2026 tillsynsbegäran mail.docx", "A 26670-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 35526-2023</t>
+          <t>A 30754-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45147</v>
+        <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2754,46 +2754,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35526-2023 artfynd.xlsx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35526-2023 karta.png", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35526-2023 georefererad karta.tif", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35526-2023 FSC-klagomål.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35526-2023 FSC-klagomål mail.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35526-2023 tillsynsbegäran.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35526-2023 tillsynsbegäran mail.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30653-2023</t>
+          <t>A 35526-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45112</v>
+        <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2859,50 +2859,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35526-2023 artfynd.xlsx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35526-2023 karta.png", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35526-2023 georefererad karta.tif", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35526-2023 FSC-klagomål.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35526-2023 FSC-klagomål mail.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35526-2023 tillsynsbegäran.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35526-2023 tillsynsbegäran mail.docx", "A 35526-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30662-2023</t>
+          <t>A 30653-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2919,7 +2915,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2932,7 +2928,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2972,42 +2968,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30754-2023</t>
+          <t>A 7339-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45112</v>
+        <v>45703</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3077,35 +3077,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32503-2025</t>
+          <t>A 35491-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45838</v>
+        <v>45146</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,20 +3247,20 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3271,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,46 +3283,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7339-2025</t>
+          <t>A 18822-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3336,10 +3340,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45703</v>
+        <v>46128</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3352,7 +3356,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3367,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3376,10 +3380,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3388,46 +3392,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31742-2023</t>
+          <t>A 30662-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3441,10 +3445,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3457,7 +3461,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3490,53 +3494,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18822-2026</t>
+          <t>A 31742-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46128</v>
+        <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3590,58 +3590,62 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35491-2023</t>
+          <t>A 23906-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3655,10 +3659,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45146</v>
+        <v>45455</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3671,10 +3675,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3683,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3695,10 +3699,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3707,50 +3711,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
-        <v/>
-      </c>
-      <c r="Z30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23906-2024</t>
+          <t>A 32503-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45455</v>
+        <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3780,13 +3780,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3820,35 +3820,35 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
         <v>44637</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>44570</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 31746-2023</t>
+          <t>A 39556-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45117</v>
+        <v>44818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 31711-2023</t>
+          <t>A 30633-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31727-2023</t>
+          <t>A 30772-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39556-2022</t>
+          <t>A 31889-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44818</v>
+        <v>45118</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51314-2023</t>
+          <t>A 4782-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45219</v>
+        <v>45328</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46511-2023</t>
+          <t>A 51229-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45197</v>
+        <v>44868</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47980-2023</t>
+          <t>A 30769-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45204</v>
+        <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12160-2024</t>
+          <t>A 30794-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45377</v>
+        <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8570-2025</t>
+          <t>A 6745-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5111,14 +5111,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45709</v>
+        <v>44966</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43938-2024</t>
+          <t>A 18615-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45572</v>
+        <v>45763</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25928-2023</t>
+          <t>A 3237-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45090</v>
+        <v>44946</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18337-2023</t>
+          <t>A 31724-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45041</v>
+        <v>45117</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22541-2023</t>
+          <t>A 31726-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45071</v>
+        <v>45117</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5466,7 +5466,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 50057-2023</t>
+          <t>A 61671-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45215</v>
+        <v>44917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5539,7 +5539,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29658-2022</t>
+          <t>A 56334-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44754</v>
+        <v>45624</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 67455-2021</t>
+          <t>A 61318-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44524</v>
+        <v>45264</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30628-2023</t>
+          <t>A 42483-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45112</v>
+        <v>45180</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5758,7 +5758,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30643-2023</t>
+          <t>A 47265-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45112</v>
+        <v>45586</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18615-2025</t>
+          <t>A 8570-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45763</v>
+        <v>45709</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31717-2023</t>
+          <t>A 5072-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45117</v>
+        <v>44958</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31719-2023</t>
+          <t>A 17925-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45117</v>
+        <v>44683</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30800-2023</t>
+          <t>A 54295-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45112</v>
+        <v>45232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24368-2022</t>
+          <t>A 47980-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44726</v>
+        <v>45204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6196,7 +6196,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30650-2023</t>
+          <t>A 9527-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45112</v>
+        <v>44981</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54289-2022</t>
+          <t>A 9401-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44882</v>
+        <v>45359</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60792-2022</t>
+          <t>A 50981-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44914</v>
+        <v>45218</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6371,8 +6371,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6415,7 +6420,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9401-2024</t>
+          <t>A 28158-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6429,10 +6434,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45359</v>
+        <v>45476</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6445,7 +6450,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6488,7 +6493,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47522-2024</t>
+          <t>A 435-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6502,10 +6507,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45587</v>
+        <v>45664</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6517,13 +6522,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 65143-2023</t>
+          <t>A 36650-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45288</v>
+        <v>45872</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 1922-2024</t>
+          <t>A 50302-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45308</v>
+        <v>45216</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54287-2022</t>
+          <t>A 19644-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44882</v>
+        <v>46134</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5072-2023</t>
+          <t>A 47522-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44958</v>
+        <v>45587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6814,8 +6814,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6858,7 +6863,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40774-2025</t>
+          <t>A 65143-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6872,10 +6877,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45897</v>
+        <v>45288</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6888,7 +6893,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6931,7 +6936,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 65118-2023</t>
+          <t>A 40774-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6945,10 +6950,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45288</v>
+        <v>45897</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6961,7 +6966,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>6.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7004,7 +7009,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30769-2023</t>
+          <t>A 59472-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7018,10 +7023,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45112</v>
+        <v>45254</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7034,7 +7039,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7077,7 +7082,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54659-2022</t>
+          <t>A 9530-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7091,10 +7096,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44883</v>
+        <v>44981</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7107,7 +7112,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7150,7 +7155,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30794-2023</t>
+          <t>A 31546-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7160,14 +7165,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45112</v>
+        <v>44775</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7180,7 +7185,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7223,7 +7228,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31718-2023</t>
+          <t>A 25928-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7237,10 +7242,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45117</v>
+        <v>45090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7253,7 +7258,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7296,7 +7301,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56335-2024</t>
+          <t>A 6064-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7310,10 +7315,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45624</v>
+        <v>45696</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7369,7 +7374,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28040-2024</t>
+          <t>A 30628-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7383,10 +7388,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45476</v>
+        <v>45112</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7399,7 +7404,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7442,7 +7447,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 22834-2024</t>
+          <t>A 30643-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7456,10 +7461,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45448</v>
+        <v>45112</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7472,7 +7477,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7515,7 +7520,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4782-2024</t>
+          <t>A 22834-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7529,10 +7534,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45328</v>
+        <v>45448</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7545,7 +7550,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7588,7 +7593,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43398-2024</t>
+          <t>A 41910-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7602,10 +7607,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45568</v>
+        <v>45561</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7618,7 +7623,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7661,7 +7666,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59517-2023</t>
+          <t>A 52371-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7675,10 +7680,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45254</v>
+        <v>45953</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7691,7 +7696,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7734,7 +7739,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59816-2021</t>
+          <t>A 56305-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7748,10 +7753,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44494</v>
+        <v>45974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7764,7 +7769,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7807,7 +7812,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3237-2023</t>
+          <t>A 36131-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7821,10 +7826,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44946</v>
+        <v>45534</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7837,7 +7842,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7880,7 +7885,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6745-2023</t>
+          <t>A 47279-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7890,14 +7895,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44966</v>
+        <v>45930</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7910,7 +7915,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7953,7 +7958,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11605-2024</t>
+          <t>A 67455-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7967,10 +7972,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45373</v>
+        <v>44524</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7983,7 +7988,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8026,7 +8031,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 70708-2021</t>
+          <t>A 36532-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8040,10 +8045,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44537</v>
+        <v>45537</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8056,7 +8061,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8099,7 +8104,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1395-2024</t>
+          <t>A 58093-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8113,10 +8118,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45303</v>
+        <v>45248</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8129,7 +8134,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8172,7 +8177,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1921-2024</t>
+          <t>A 54144-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8186,10 +8191,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45308</v>
+        <v>44881</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8202,7 +8207,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8245,7 +8250,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42250-2023</t>
+          <t>A 48212-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8259,10 +8264,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45180</v>
+        <v>45933</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8275,7 +8280,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8318,7 +8323,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30633-2023</t>
+          <t>A 49460-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8332,10 +8337,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45112</v>
+        <v>45939</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8348,7 +8353,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8391,7 +8396,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23330-2024</t>
+          <t>A 49269-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8401,14 +8406,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45453</v>
+        <v>45938</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8420,13 +8425,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8469,7 +8469,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47279-2025</t>
+          <t>A 25694-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8483,10 +8483,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45930</v>
+        <v>45803</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8542,7 +8542,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 57036-2024</t>
+          <t>A 50057-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45629</v>
+        <v>45215</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8615,7 +8615,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9159-2024</t>
+          <t>A 46511-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45358</v>
+        <v>45197</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8688,7 +8688,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 9086-2025</t>
+          <t>A 51613-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8702,10 +8702,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45713</v>
+        <v>45951</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8761,7 +8761,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11021-2022</t>
+          <t>A 6653-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8775,10 +8775,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44628</v>
+        <v>44602</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11239-2023</t>
+          <t>A 64207-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44992</v>
+        <v>44510</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50302-2023</t>
+          <t>A 52513-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8921,10 +8921,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45216</v>
+        <v>45954</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8980,7 +8980,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 53055-2024</t>
+          <t>A 52511-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45611</v>
+        <v>45954</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9053,7 +9053,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48212-2025</t>
+          <t>A 2006-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45933</v>
+        <v>45308</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9126,7 +9126,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 18613-2025</t>
+          <t>A 24368-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45763</v>
+        <v>44726</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9199,7 +9199,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 18614-2025</t>
+          <t>A 52939-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45763</v>
+        <v>45957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>9.699999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 31712-2023</t>
+          <t>A 27103-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45117</v>
+        <v>45471</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9345,7 +9345,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31715-2023</t>
+          <t>A 55159-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9359,10 +9359,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45117</v>
+        <v>45621</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31745-2023</t>
+          <t>A 38586-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9432,10 +9432,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45117</v>
+        <v>45162</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9491,7 +9491,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 49269-2025</t>
+          <t>A 20598-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45938</v>
+        <v>46140</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 49460-2025</t>
+          <t>A 20600-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9578,10 +9578,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45939</v>
+        <v>46140</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9637,7 +9637,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 31889-2023</t>
+          <t>A 20782-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9651,10 +9651,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45118</v>
+        <v>46141</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9710,7 +9710,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 47264-2024</t>
+          <t>A 9159-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45586</v>
+        <v>45358</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9783,7 +9783,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 47265-2024</t>
+          <t>A 31746-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9797,10 +9797,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45586</v>
+        <v>45117</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9856,7 +9856,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15112-2022</t>
+          <t>A 63725-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44658</v>
+        <v>45276</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9929,7 +9929,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 3238-2023</t>
+          <t>A 59613-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44946</v>
+        <v>45254</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10002,7 +10002,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59472-2023</t>
+          <t>A 58137-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45254</v>
+        <v>45982</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10075,7 +10075,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 42483-2023</t>
+          <t>A 62986-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45180</v>
+        <v>45272</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10148,7 +10148,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 6653-2022</t>
+          <t>A 59816-2021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10162,10 +10162,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44602</v>
+        <v>44494</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10221,7 +10221,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28073-2024</t>
+          <t>A 58139-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10235,10 +10235,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45476</v>
+        <v>45982</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 51613-2025</t>
+          <t>A 30650-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45951</v>
+        <v>45112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9530-2023</t>
+          <t>A 30637-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44981</v>
+        <v>45112</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10440,7 +10440,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 52511-2025</t>
+          <t>A 60089-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45954</v>
+        <v>45993</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10513,7 +10513,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22443-2023</t>
+          <t>A 60093-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45070</v>
+        <v>45993</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10586,7 +10586,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 52513-2025</t>
+          <t>A 60091-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10600,10 +10600,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45954</v>
+        <v>45993</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10659,7 +10659,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 54295-2023</t>
+          <t>A 60092-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10673,10 +10673,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45232</v>
+        <v>45993</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10732,7 +10732,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 52939-2025</t>
+          <t>A 59871-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45957</v>
+        <v>45992</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 30801-2023</t>
+          <t>A 59872-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10819,10 +10819,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45112</v>
+        <v>45992</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10878,7 +10878,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56331-2024</t>
+          <t>A 60181-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10892,10 +10892,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45624</v>
+        <v>45994</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10951,7 +10951,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31724-2023</t>
+          <t>A 60946-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10965,10 +10965,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45117</v>
+        <v>45999</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11024,7 +11024,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 31726-2023</t>
+          <t>A 65118-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11038,10 +11038,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45117</v>
+        <v>45288</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11097,7 +11097,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17925-2022</t>
+          <t>A 18613-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11111,10 +11111,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44683</v>
+        <v>45763</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11170,7 +11170,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 21751-2022</t>
+          <t>A 18614-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11184,10 +11184,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44708</v>
+        <v>45763</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11243,7 +11243,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 7046-2025</t>
+          <t>A 54289-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11257,10 +11257,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45701</v>
+        <v>44882</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11316,7 +11316,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 42256-2023</t>
+          <t>A 42250-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11333,7 +11333,7 @@
         <v>45180</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 41910-2024</t>
+          <t>A 42256-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11403,10 +11403,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45561</v>
+        <v>45180</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 62986-2023</t>
+          <t>A 1921-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11476,10 +11476,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45272</v>
+        <v>45308</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>7.5</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11535,7 +11535,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 58139-2025</t>
+          <t>A 10610-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45982</v>
+        <v>45721</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11608,7 +11608,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 58137-2025</t>
+          <t>A 64003-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11622,10 +11622,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45982</v>
+        <v>46021</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11681,7 +11681,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 30637-2023</t>
+          <t>A 64005-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45112</v>
+        <v>46021</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11754,7 +11754,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29794-2025</t>
+          <t>A 31711-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11768,10 +11768,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45825</v>
+        <v>45117</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11827,7 +11827,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 51564-2024</t>
+          <t>A 31727-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45604</v>
+        <v>45117</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11900,7 +11900,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 59871-2025</t>
+          <t>A 11605-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11914,10 +11914,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45992</v>
+        <v>45373</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11973,7 +11973,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60091-2025</t>
+          <t>A 2497-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11987,10 +11987,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45993</v>
+        <v>46037</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12046,7 +12046,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 60092-2025</t>
+          <t>A 53055-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12060,10 +12060,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45993</v>
+        <v>45611</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12119,7 +12119,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 10918-2025</t>
+          <t>A 4119-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12133,10 +12133,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45722</v>
+        <v>46044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12148,8 +12148,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12192,7 +12197,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 9471-2025</t>
+          <t>A 4587-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12206,10 +12211,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45715</v>
+        <v>46048</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12222,7 +12227,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12265,7 +12270,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 60089-2025</t>
+          <t>A 4588-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12279,10 +12284,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45993</v>
+        <v>46048</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12295,7 +12300,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12338,7 +12343,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60093-2025</t>
+          <t>A 6071-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12352,10 +12357,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45993</v>
+        <v>46052</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12368,7 +12373,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12411,7 +12416,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 59872-2025</t>
+          <t>A 6074-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12425,10 +12430,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45992</v>
+        <v>46052</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12441,7 +12446,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12484,7 +12489,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 60181-2025</t>
+          <t>A 6104-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12498,10 +12503,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45994</v>
+        <v>46052</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12557,7 +12562,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60946-2025</t>
+          <t>A 6103-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12571,10 +12576,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45999</v>
+        <v>46052</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12587,7 +12592,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12630,7 +12635,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 59613-2023</t>
+          <t>A 29658-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12644,10 +12649,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45254</v>
+        <v>44754</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12660,7 +12665,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12703,7 +12708,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 31804-2025</t>
+          <t>A 7546-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12717,10 +12722,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45834</v>
+        <v>46059</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12733,7 +12738,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12776,7 +12781,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 61318-2023</t>
+          <t>A 57036-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12790,10 +12795,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45264</v>
+        <v>45629</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12806,7 +12811,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12849,7 +12854,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 32506-2025</t>
+          <t>A 24965-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12863,10 +12868,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45838</v>
+        <v>46174</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12879,7 +12884,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12922,7 +12927,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 2497-2026</t>
+          <t>A 54287-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12936,10 +12941,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46037</v>
+        <v>44882</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12952,7 +12957,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12995,7 +13000,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 32320-2025</t>
+          <t>A 11584-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13009,10 +13014,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45836</v>
+        <v>46084</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13025,7 +13030,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13068,7 +13073,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 4119-2026</t>
+          <t>A 12503-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13082,10 +13087,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46044</v>
+        <v>46090</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13097,13 +13102,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 10610-2025</t>
+          <t>A 12469-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13160,10 +13160,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45721</v>
+        <v>46090</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13219,7 +13219,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 4587-2026</t>
+          <t>A 12879-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13229,14 +13229,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46048</v>
+        <v>46092</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13248,8 +13248,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13292,7 +13297,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 4588-2026</t>
+          <t>A 15112-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13306,10 +13311,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46048</v>
+        <v>44658</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13322,7 +13327,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13365,7 +13370,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 64003-2025</t>
+          <t>A 13120-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13379,10 +13384,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46021</v>
+        <v>46093</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13395,7 +13400,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13438,7 +13443,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 64005-2025</t>
+          <t>A 13121-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13452,10 +13457,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46021</v>
+        <v>46093</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13468,7 +13473,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13511,7 +13516,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6071-2026</t>
+          <t>A 58011-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13525,10 +13530,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46052</v>
+        <v>44900</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13541,7 +13546,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13584,7 +13589,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 6074-2026</t>
+          <t>A 56452-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13598,10 +13603,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46052</v>
+        <v>44893</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13614,7 +13619,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13657,7 +13662,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 55159-2024</t>
+          <t>A 14111-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13671,10 +13676,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45621</v>
+        <v>46099</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13687,7 +13692,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13730,7 +13735,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 6104-2026</t>
+          <t>A 58010-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13744,10 +13749,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46052</v>
+        <v>44900</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13760,7 +13765,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13803,7 +13808,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 6103-2026</t>
+          <t>A 14545-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13813,14 +13818,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46052</v>
+        <v>46100</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13833,7 +13838,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13876,7 +13881,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 7546-2026</t>
+          <t>A 1922-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13890,10 +13895,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46059</v>
+        <v>45308</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13906,7 +13911,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13949,7 +13954,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 38521-2026</t>
+          <t>A 26642-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13963,10 +13968,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46283</v>
+        <v>46184</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13979,7 +13984,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14022,7 +14027,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 38601-2026</t>
+          <t>A 27098-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14036,10 +14041,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46283</v>
+        <v>46188</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14052,7 +14057,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14095,7 +14100,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 39344-2026</t>
+          <t>A 27248-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14109,10 +14114,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46288</v>
+        <v>46188</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14125,7 +14130,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14168,7 +14173,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 47258-2025</t>
+          <t>A 61334-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14182,10 +14187,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45930</v>
+        <v>44915</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14198,7 +14203,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14241,7 +14246,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 11584-2026</t>
+          <t>A 51564-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14255,10 +14260,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46084</v>
+        <v>45604</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14271,7 +14276,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14314,7 +14319,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 12469-2026</t>
+          <t>A 7046-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14328,10 +14333,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46090</v>
+        <v>45701</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14387,7 +14392,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12503-2026</t>
+          <t>A 27782-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14401,10 +14406,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46090</v>
+        <v>46191</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14417,7 +14422,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14460,7 +14465,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 54144-2022</t>
+          <t>A 30760-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14474,10 +14479,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44881</v>
+        <v>45112</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14490,7 +14495,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14533,7 +14538,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 13120-2026</t>
+          <t>A 30762-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14547,10 +14552,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46093</v>
+        <v>45112</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14563,7 +14568,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14606,7 +14611,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 13121-2026</t>
+          <t>A 56331-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14620,10 +14625,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46093</v>
+        <v>45624</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14636,7 +14641,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14679,7 +14684,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 12879-2026</t>
+          <t>A 51314-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14693,10 +14698,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46092</v>
+        <v>45219</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14708,13 +14713,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 2006-2024</t>
+          <t>A 3238-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14771,10 +14771,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45308</v>
+        <v>44946</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14830,7 +14830,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 61671-2022</t>
+          <t>A 12160-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14844,10 +14844,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44917</v>
+        <v>45377</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 14111-2026</t>
+          <t>A 54659-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14917,10 +14917,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46099</v>
+        <v>44883</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14976,7 +14976,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 14545-2026</t>
+          <t>A 31718-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14986,14 +14986,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46100</v>
+        <v>45117</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15049,7 +15049,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 58011-2022</t>
+          <t>A 33852-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15063,10 +15063,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44900</v>
+        <v>46251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15122,7 +15122,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 56452-2022</t>
+          <t>A 33853-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15136,10 +15136,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44893</v>
+        <v>46251</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15195,7 +15195,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 58010-2022</t>
+          <t>A 30098-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15209,10 +15209,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44900</v>
+        <v>46206</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15268,7 +15268,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 51229-2022</t>
+          <t>A 43398-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44868</v>
+        <v>45568</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15341,7 +15341,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 61334-2022</t>
+          <t>A 54311-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15355,10 +15355,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44915</v>
+        <v>44882</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15414,7 +15414,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30793-2023</t>
+          <t>A 22443-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15428,10 +15428,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45112</v>
+        <v>45070</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15487,7 +15487,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30795-2023</t>
+          <t>A 60792-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15501,10 +15501,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45112</v>
+        <v>44914</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30724-2023</t>
+          <t>A 61026-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45112</v>
+        <v>44914</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15633,7 +15633,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 435-2025</t>
+          <t>A 47264-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15647,10 +15647,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45664</v>
+        <v>45586</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15706,7 +15706,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 28158-2024</t>
+          <t>A 22541-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15720,10 +15720,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45476</v>
+        <v>45071</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15779,7 +15779,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 54311-2022</t>
+          <t>A 21751-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15793,10 +15793,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44882</v>
+        <v>44708</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15852,7 +15852,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 56334-2024</t>
+          <t>A 35071-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15866,10 +15866,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45624</v>
+        <v>46259</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15925,7 +15925,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 61026-2022</t>
+          <t>A 1395-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15939,10 +15939,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44914</v>
+        <v>45303</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15998,7 +15998,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 63725-2023</t>
+          <t>A 2398-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16012,10 +16012,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45276</v>
+        <v>45310</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16071,7 +16071,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 9527-2023</t>
+          <t>A 35072-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16085,10 +16085,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44981</v>
+        <v>46259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16144,7 +16144,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 19644-2026</t>
+          <t>A 30793-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46134</v>
+        <v>45112</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16217,7 +16217,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 30760-2023</t>
+          <t>A 30795-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16234,7 +16234,7 @@
         <v>45112</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 30762-2023</t>
+          <t>A 30800-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16307,7 +16307,7 @@
         <v>45112</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16363,7 +16363,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 36650-2025</t>
+          <t>A 28040-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16377,10 +16377,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45872</v>
+        <v>45476</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16436,7 +16436,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 6064-2025</t>
+          <t>A 18337-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45696</v>
+        <v>45041</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16509,7 +16509,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 38586-2023</t>
+          <t>A 11021-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16523,10 +16523,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45162</v>
+        <v>44628</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16582,7 +16582,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31546-2022</t>
+          <t>A 11239-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16592,14 +16592,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44775</v>
+        <v>44992</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16655,7 +16655,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 30772-2023</t>
+          <t>A 31717-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16669,10 +16669,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 36131-2024</t>
+          <t>A 31719-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16742,10 +16742,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45534</v>
+        <v>45117</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16801,7 +16801,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 36532-2024</t>
+          <t>A 36861-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16815,10 +16815,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45537</v>
+        <v>46272</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 20600-2026</t>
+          <t>A 31745-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16888,10 +16888,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46140</v>
+        <v>45117</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16947,7 +16947,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 52371-2025</t>
+          <t>A 56335-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16961,10 +16961,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45953</v>
+        <v>45624</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17020,7 +17020,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 56305-2025</t>
+          <t>A 30801-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17034,10 +17034,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45974</v>
+        <v>45112</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17093,7 +17093,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 2398-2024</t>
+          <t>A 17434-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17103,14 +17103,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45310</v>
+        <v>46120</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17166,7 +17166,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 20598-2026</t>
+          <t>A 70708-2021</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17180,10 +17180,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46140</v>
+        <v>44537</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17239,7 +17239,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 25694-2025</t>
+          <t>A 31712-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17253,10 +17253,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45803</v>
+        <v>45117</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17312,7 +17312,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 50981-2023</t>
+          <t>A 31715-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17326,10 +17326,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45218</v>
+        <v>45117</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17341,13 +17341,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>1.9</v>
+        <v>12.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17390,7 +17385,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 58093-2023</t>
+          <t>A 31907-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17404,10 +17399,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45248</v>
+        <v>46231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17419,8 +17414,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17463,7 +17463,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 20782-2026</t>
+          <t>A 59517-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17477,10 +17477,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46141</v>
+        <v>45254</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 64207-2021</t>
+          <t>A 30724-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17550,10 +17550,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44510</v>
+        <v>45112</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17609,7 +17609,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27103-2024</t>
+          <t>A 12124-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17623,10 +17623,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45471</v>
+        <v>45377</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17638,8 +17638,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17699,7 +17704,7 @@
         <v>45629</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17755,7 +17760,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 21878-2025</t>
+          <t>A 23330-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17765,14 +17770,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45784</v>
+        <v>45453</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17784,8 +17789,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17828,7 +17838,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23907-2024</t>
+          <t>A 38521-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17842,10 +17852,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45455</v>
+        <v>46283</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17858,7 +17868,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17901,7 +17911,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 24965-2026</t>
+          <t>A 38601-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17915,10 +17925,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46174</v>
+        <v>46283</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17931,7 +17941,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17974,7 +17984,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 26642-2026</t>
+          <t>A 23907-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17988,10 +17998,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46184</v>
+        <v>45455</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18004,7 +18014,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18047,7 +18057,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 27098-2026</t>
+          <t>A 21878-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18061,10 +18071,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46188</v>
+        <v>45784</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18077,7 +18087,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18120,7 +18130,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 27248-2026</t>
+          <t>A 47258-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18134,10 +18144,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46188</v>
+        <v>45930</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18150,7 +18160,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18193,7 +18203,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 27782-2026</t>
+          <t>A 43938-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18207,10 +18217,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46191</v>
+        <v>45572</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18223,7 +18233,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18266,7 +18276,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 33852-2026</t>
+          <t>A 39344-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18280,10 +18290,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46251</v>
+        <v>46288</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18296,7 +18306,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18339,7 +18349,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 33853-2026</t>
+          <t>A 9086-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18353,10 +18363,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46251</v>
+        <v>45713</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18369,7 +18379,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18412,7 +18422,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 30098-2026</t>
+          <t>A 28073-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18426,10 +18436,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46206</v>
+        <v>45476</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18442,7 +18452,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18485,7 +18495,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 35072-2026</t>
+          <t>A 29794-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18499,10 +18509,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46259</v>
+        <v>45825</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18515,7 +18525,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18558,7 +18568,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 35071-2026</t>
+          <t>A 10918-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18572,10 +18582,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46259</v>
+        <v>45722</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18588,7 +18598,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18631,7 +18641,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 36861-2026</t>
+          <t>A 9471-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18645,10 +18655,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46272</v>
+        <v>45715</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18661,7 +18671,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18704,7 +18714,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 31907-2026</t>
+          <t>A 31804-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18718,10 +18728,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46231</v>
+        <v>45834</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18733,13 +18743,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18782,7 +18787,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 17434-2026</t>
+          <t>A 32320-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18792,14 +18797,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46120</v>
+        <v>45836</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18812,7 +18817,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.9</v>
+        <v>11.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18855,7 +18860,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 12124-2024</t>
+          <t>A 32506-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18869,10 +18874,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45377</v>
+        <v>45838</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18884,13 +18889,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18950,7 +18950,7 @@
         <v>45934</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>46154</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>46246</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>45112</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45363</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>45117</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>46093</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45147</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>46128</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45703</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45838</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>45112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45146</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45455</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>44637</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>44570</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45377</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45215</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44754</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45197</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44914</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45359</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44882</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>46021</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>46021</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>44883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>45117</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45476</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45448</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45328</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>44946</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45373</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44537</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45288</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>46037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45303</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>46044</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>46048</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>46048</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45453</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>46052</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>46052</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>46052</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>46052</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45358</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44628</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45216</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46059</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45611</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45118</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45930</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44658</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44946</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>46084</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45933</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>46090</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>46090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>46093</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>46093</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>46092</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>45713</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45938</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>44981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45070</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46099</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45232</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>46100</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>44900</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44893</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>44900</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45112</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45951</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45624</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45954</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45954</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45957</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45112</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>46134</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45604</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45982</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45982</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45696</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45992</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45117</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45993</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45993</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45993</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45476</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45994</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45117</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45117</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45999</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45219</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45534</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45537</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>46140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45953</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45204</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45709</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45974</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45721</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45041</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>46140</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45803</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45071</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45825</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>46141</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44524</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45112</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45112</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45722</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45715</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45763</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45117</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45112</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44726</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45112</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45834</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45838</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44882</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45836</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45308</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44958</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45288</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45624</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45568</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45254</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44494</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44966</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>46174</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45664</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45476</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45308</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45180</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>46184</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>44992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>46188</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46188</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>45872</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45763</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45763</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>46191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>45117</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45117</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45117</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45586</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45586</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45180</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44602</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44775</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45090</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>46251</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>46251</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>46206</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45117</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>45117</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44683</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44708</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45701</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45180</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45561</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45272</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>46259</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>46259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45254</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45264</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>46272</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>46231</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45621</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45377</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>46283</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>46283</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>46288</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>44881</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>46290</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>46290</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>46290</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>45308</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>46120</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44917</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44868</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44915</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45112</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45112</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45112</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44882</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45624</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>44914</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45276</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>44981</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45112</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45112</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>45162</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45112</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45310</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45218</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>45248</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>44510</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45471</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45629</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45784</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45455</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45572</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45934</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>46154</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>46246</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>45112</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45363</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>45117</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>46093</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45147</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>46128</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45703</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45838</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>45112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45146</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45455</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>44637</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>44570</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45377</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45215</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44754</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45197</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44914</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45359</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44882</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>46021</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>46021</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>44883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>45117</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45476</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45448</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45328</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>44946</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45373</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44537</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45288</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>46037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45303</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45897</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>46044</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>46048</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>46048</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45453</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>46052</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>46052</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>46052</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>46052</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45358</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44628</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45216</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46059</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45611</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>45118</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45930</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44658</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44946</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>46084</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45933</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>46090</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>46090</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>46093</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>46093</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>46092</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>45713</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45938</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>44981</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45070</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>46099</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45232</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>46100</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>44900</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44893</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>44900</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45112</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45951</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45624</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45954</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45954</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45957</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45112</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>46134</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45604</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45982</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45982</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45696</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45992</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45117</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45993</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45993</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45993</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45476</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45994</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45117</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45117</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45999</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45219</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45534</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45537</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>46140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45953</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45204</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45709</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45974</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45721</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45041</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>46140</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45803</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45071</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45825</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>46141</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44524</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45112</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45112</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45722</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45715</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45763</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45117</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45112</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44726</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45112</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45834</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45838</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44882</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45836</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45308</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44958</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45288</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45624</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45568</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45254</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44494</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>44966</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>46174</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45664</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45476</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45308</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45180</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>46184</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>44992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>46188</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46188</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>45872</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45763</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45763</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>46191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>45117</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45117</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45117</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45586</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45586</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45180</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44602</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44775</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45090</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>46251</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>46251</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>46206</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45117</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>45117</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44683</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44708</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45701</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45180</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45561</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45272</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>46259</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>46259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45254</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45264</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>46272</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>46231</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45621</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45377</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>46283</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>46283</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>46288</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>44881</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>46290</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>46290</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>46290</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>45308</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>46120</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44917</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44868</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44915</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45112</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45112</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45112</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44882</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45624</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>44914</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45276</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>44981</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45112</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45112</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>45162</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45112</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45310</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45218</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>45248</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>44510</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45471</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45629</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45784</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45455</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45572</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45934</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>46154</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>46246</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45943</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45112</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45215</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45112</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>46093</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45363</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45703</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46128</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>45838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45146</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45455</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>44637</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>44570</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45118</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44868</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45328</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44966</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45763</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45090</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45721</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>46021</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>46021</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45587</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45288</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45117</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45117</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44917</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>46037</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45624</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46044</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>46048</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>46048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45264</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>46052</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>46052</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>46052</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>46052</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45180</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>46059</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45930</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45586</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45933</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45709</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45938</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44958</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>44683</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45232</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45204</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45359</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45713</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>45954</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>46084</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45954</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45957</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46090</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>44981</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>46090</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>46092</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>46093</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>46093</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45218</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44900</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>44893</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>46099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>44900</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>46100</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45216</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45982</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45982</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45825</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45254</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44981</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45993</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45993</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45993</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45993</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45722</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45992</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45994</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45999</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45715</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>46134</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45834</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45448</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45561</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45836</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45838</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44524</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45248</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44881</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45696</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45215</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45974</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45197</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45534</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45537</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45803</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44602</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45308</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44726</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45471</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45621</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>46140</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>46140</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45162</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46141</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45358</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45476</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45117</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45664</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45276</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45254</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45872</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45272</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44494</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45112</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45112</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45288</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45763</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45763</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44882</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45180</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45180</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45308</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45117</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45117</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45373</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>44775</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45611</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>46184</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46188</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>46191</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44754</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>46206</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44882</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44658</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>46259</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46259</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45308</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45604</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45701</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45112</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45112</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45624</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>46272</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45219</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44946</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>46231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45377</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45377</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44883</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>46283</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>46283</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45117</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45930</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45568</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>46288</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44882</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45070</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44914</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>46290</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>44914</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45586</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>46120</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>46290</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>46290</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45071</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>44708</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45303</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>45310</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45112</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45112</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>46251</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>46251</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45476</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45041</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44628</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>44992</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45117</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45117</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45117</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45624</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45112</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44537</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45117</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45117</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45254</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45112</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45629</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45453</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45455</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45784</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45572</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45934</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>46154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>46246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45943</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45112</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45215</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45112</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>46093</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45363</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46184</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45703</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46128</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>45838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45146</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45455</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>44637</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>44570</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44727</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44502</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44530</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>44818</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45118</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44868</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45328</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44966</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45763</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45090</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45721</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>46021</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>46021</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45587</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45288</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45117</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45117</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44917</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>46037</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45624</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46044</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>46048</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>46048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45264</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>46052</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>46052</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>46052</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>46052</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45180</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>46059</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45930</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45586</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45933</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45709</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45938</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44958</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>44683</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45232</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45204</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45359</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45713</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45951</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>45954</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>46084</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45954</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45957</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46090</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>44981</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>46090</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>46092</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>46093</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>46093</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45218</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44900</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>44893</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>46099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>44900</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>46100</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45216</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45982</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45982</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45825</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45254</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44981</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45993</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45993</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45993</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45993</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45722</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45992</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45994</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45999</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45715</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45112</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>46134</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45834</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45448</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45561</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45836</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45838</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44524</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45248</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44881</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45696</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45215</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45974</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45197</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45534</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45537</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45803</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44602</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44510</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45308</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44726</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45471</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45621</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>46140</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>46140</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45162</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46141</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45358</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45476</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45117</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45664</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45276</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45254</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45872</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45272</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>44494</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45112</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45112</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45288</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45763</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45763</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44882</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45180</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45180</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45308</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45117</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45117</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45373</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>44775</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45611</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>46184</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46188</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>46191</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44754</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>46206</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44882</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44658</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>46259</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46259</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45308</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45604</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45701</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45112</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45112</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45624</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>46272</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45219</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44946</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>46231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45377</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45377</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44883</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>46283</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>46283</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45117</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45930</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45568</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>46288</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44882</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45070</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44914</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>46290</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>44914</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45586</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>46120</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>46290</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>46290</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45071</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>44708</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>45303</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>45310</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45112</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45112</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>46251</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>46251</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45476</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45041</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44628</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>44992</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45117</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45117</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45117</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45624</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45112</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44537</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45117</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45117</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45254</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45112</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45629</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45453</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45455</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45784</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45572</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45934</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>46154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>46246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50011-2023</t>
+          <t>A 30777-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45215</v>
+        <v>45112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,45 +845,267 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Oxtungssvamp
+Vågbandad barkbock
+Tofsmes
+Svartvit flugsnappare
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 50084-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J5" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Spillkråka
+Grönsiska
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50084-2025 artfynd.xlsx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50084-2025 karta.png", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50084-2025 georefererad karta.tif", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50084-2025 FSC-klagomål.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50084-2025 FSC-klagomål mail.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50084-2025 tillsynsbegäran.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50084-2025 tillsynsbegäran mail.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50084-2025 prioriterade fågelarter.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 50011-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45215</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Svartbent strandpipare
 Sexfläckig bastardsvärmare
@@ -892,258 +1114,36 @@
 Sädesärla</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 30777-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U5" t="n">
-        <v>8</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Oxtungssvamp
-Vågbandad barkbock
-Tofsmes
-Svartvit flugsnappare
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 50084-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45943</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Spillkråka
-Grönsiska
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50084-2025 artfynd.xlsx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50084-2025 karta.png", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50084-2025 georefererad karta.tif", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50084-2025 FSC-klagomål.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50084-2025 FSC-klagomål mail.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50084-2025 tillsynsbegäran.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50084-2025 tillsynsbegäran mail.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50084-2025 prioriterade fågelarter.docx", "A 50084-2025")</f>
         <v/>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30785-2023</t>
+          <t>A 31728-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1525,17 +1525,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1558,269 +1558,269 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Gammelgransskål
+Kattfotslav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31728-2023 artfynd.xlsx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31728-2023 karta.png", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31728-2023 georefererad karta.tif", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31728-2023 FSC-klagomål.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31728-2023 FSC-klagomål mail.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31728-2023 tillsynsbegäran.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31728-2023 tillsynsbegäran mail.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31728-2023 prioriterade fågelarter.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 30655-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Trädporella
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30655-2023 artfynd.xlsx", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30655-2023 karta.png", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30655-2023 georefererad karta.tif", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30655-2023 FSC-klagomål.docx", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30655-2023 FSC-klagomål mail.docx", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30655-2023 tillsynsbegäran.docx", "A 30655-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30655-2023 tillsynsbegäran mail.docx", "A 30655-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 30785-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
         <v>6</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Lunglav
 Grönvit nattviol
 Revlummer</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30785-2023 artfynd.xlsx", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30785-2023 karta.png", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30785-2023 georefererad karta.tif", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30785-2023 FSC-klagomål.docx", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30785-2023 FSC-klagomål mail.docx", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30785-2023 tillsynsbegäran.docx", "A 30785-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30785-2023 tillsynsbegäran mail.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31728-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Gammelgransskål
-Kattfotslav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31728-2023 artfynd.xlsx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31728-2023 karta.png", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31728-2023 georefererad karta.tif", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31728-2023 FSC-klagomål.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31728-2023 FSC-klagomål mail.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31728-2023 tillsynsbegäran.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31728-2023 tillsynsbegäran mail.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31728-2023 prioriterade fågelarter.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 30655-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Trädporella
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30655-2023 artfynd.xlsx", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30655-2023 karta.png", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30655-2023 georefererad karta.tif", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30655-2023 FSC-klagomål.docx", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30655-2023 FSC-klagomål mail.docx", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30655-2023 tillsynsbegäran.docx", "A 30655-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30655-2023 tillsynsbegäran mail.docx", "A 30655-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 9930-2024</t>
+          <t>A 30666-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45363</v>
+        <v>45112</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1850,31 +1850,31 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1890,805 +1890,805 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Talltita
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 13115-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 13115-2026 artfynd.xlsx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 13115-2026 karta.png", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 13115-2026 georefererad karta.tif", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 13115-2026 FSC-klagomål.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 13115-2026 FSC-klagomål mail.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 13115-2026 tillsynsbegäran.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 13115-2026 tillsynsbegäran mail.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9930-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45363</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Större träfjäril
 Spillkråka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 9930-2024 artfynd.xlsx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 9930-2024 karta.png", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 9930-2024 georefererad karta.tif", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 9930-2024 FSC-klagomål.docx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 9930-2024 FSC-klagomål mail.docx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 9930-2024 tillsynsbegäran.docx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 9930-2024 tillsynsbegäran mail.docx", "A 9930-2024")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 9930-2024 prioriterade fågelarter.docx", "A 9930-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 60380-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26670-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tofsmes
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 26670-2026 artfynd.xlsx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 26670-2026 karta.png", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 26670-2026 georefererad karta.tif", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 26670-2026 FSC-klagomål.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 26670-2026 FSC-klagomål mail.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 26670-2026 tillsynsbegäran.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 26670-2026 tillsynsbegäran mail.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 31714-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>45117</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>2.4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U18" t="n">
         <v>6</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Grönsiska</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 30666-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 30763-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45112</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 60380-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30763-2023 artfynd.xlsx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30763-2023 karta.png", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30763-2023 georefererad karta.tif", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30763-2023 FSC-klagomål.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30763-2023 FSC-klagomål mail.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30763-2023 tillsynsbegäran.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30763-2023 tillsynsbegäran mail.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30763-2023 prioriterade fågelarter.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 30792-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 30792-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 26670-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tofsmes
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 26670-2026 artfynd.xlsx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 26670-2026 karta.png", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 26670-2026 georefererad karta.tif", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 26670-2026 FSC-klagomål.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 26670-2026 FSC-klagomål mail.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 26670-2026 tillsynsbegäran.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 26670-2026 tillsynsbegäran mail.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 13115-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46093</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 13115-2026 artfynd.xlsx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 13115-2026 karta.png", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 13115-2026 georefererad karta.tif", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 13115-2026 FSC-klagomål.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 13115-2026 FSC-klagomål mail.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 13115-2026 tillsynsbegäran.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 13115-2026 tillsynsbegäran mail.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 30763-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30763-2023 artfynd.xlsx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30763-2023 karta.png", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30763-2023 georefererad karta.tif", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30763-2023 FSC-klagomål.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30763-2023 FSC-klagomål mail.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30763-2023 tillsynsbegäran.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30763-2023 tillsynsbegäran mail.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30763-2023 prioriterade fågelarter.docx", "A 30763-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23906-2024</t>
+          <t>A 30754-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45455</v>
+        <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2758,35 +2758,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30653-2023</t>
+          <t>A 32503-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45112</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2928,13 +2928,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2968,46 +2968,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30662-2023</t>
+          <t>A 30653-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3024,7 +3020,7 @@
         <v>45112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,7 +3033,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3077,42 +3073,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32503-2025</t>
+          <t>A 18822-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45838</v>
+        <v>46128</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,23 +3142,23 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3166,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3178,46 +3178,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30754-2023</t>
+          <t>A 7339-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45112</v>
+        <v>45703</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3287,35 +3287,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7339-2025</t>
+          <t>A 35491-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45703</v>
+        <v>45146</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3493,46 +3493,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31742-2023</t>
+          <t>A 30662-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3546,10 +3550,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3562,7 +3566,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3595,53 +3599,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18822-2026</t>
+          <t>A 31742-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46128</v>
+        <v>45117</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3695,58 +3695,62 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35491-2023</t>
+          <t>A 23906-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3760,10 +3764,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45146</v>
+        <v>45455</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3776,10 +3780,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3788,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3800,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3812,43 +3816,39 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
-        <v/>
-      </c>
-      <c r="Z31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44764</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44502</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44683</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51314-2023</t>
+          <t>A 3360-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4491,14 +4491,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45219</v>
+        <v>44585</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 39556-2022</t>
+          <t>A 69413-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44818</v>
+        <v>44531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47980-2023</t>
+          <t>A 39556-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45204</v>
+        <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.4</v>
+        <v>0.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8570-2025</t>
+          <t>A 30633-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45709</v>
+        <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46511-2023</t>
+          <t>A 31889-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45197</v>
+        <v>45118</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3360-2022</t>
+          <t>A 51229-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44585</v>
+        <v>44868</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12160-2024</t>
+          <t>A 30769-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45377</v>
+        <v>45112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18337-2023</t>
+          <t>A 30794-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45041</v>
+        <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 69413-2021</t>
+          <t>A 6745-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5075,14 +5075,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44531</v>
+        <v>44966</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22541-2023</t>
+          <t>A 30772-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45071</v>
+        <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27103-2024</t>
+          <t>A 18615-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45471</v>
+        <v>45763</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57443-2024</t>
+          <t>A 4782-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45629</v>
+        <v>45328</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 67455-2021</t>
+          <t>A 3237-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44524</v>
+        <v>44946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5430,7 +5430,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25928-2023</t>
+          <t>A 31724-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5444,10 +5444,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45090</v>
+        <v>45117</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5503,7 +5503,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 50057-2023</t>
+          <t>A 31726-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45215</v>
+        <v>45117</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 21878-2025</t>
+          <t>A 61671-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45784</v>
+        <v>44917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23907-2024</t>
+          <t>A 56334-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45455</v>
+        <v>45624</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29658-2022</t>
+          <t>A 61318-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44754</v>
+        <v>45264</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>7.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5795,7 +5795,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30628-2023</t>
+          <t>A 42483-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45112</v>
+        <v>45180</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5868,7 +5868,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30643-2023</t>
+          <t>A 47265-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45112</v>
+        <v>45586</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18615-2025</t>
+          <t>A 8570-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45763</v>
+        <v>45709</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31717-2023</t>
+          <t>A 5072-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45117</v>
+        <v>44958</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6087,7 +6087,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31719-2023</t>
+          <t>A 17925-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6101,10 +6101,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45117</v>
+        <v>44683</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30800-2023</t>
+          <t>A 31804-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45112</v>
+        <v>45834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6233,7 +6233,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24368-2022</t>
+          <t>A 47980-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44726</v>
+        <v>45204</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6306,7 +6306,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43938-2024</t>
+          <t>A 9401-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45572</v>
+        <v>45359</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30650-2023</t>
+          <t>A 54295-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6393,10 +6393,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45112</v>
+        <v>45232</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47522-2024</t>
+          <t>A 32320-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45587</v>
+        <v>45836</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6481,13 +6481,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>11.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6530,7 +6525,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 65143-2023</t>
+          <t>A 32506-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6544,10 +6539,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45288</v>
+        <v>45838</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6560,7 +6555,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6603,7 +6598,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 54289-2022</t>
+          <t>A 12503-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6617,10 +6612,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44882</v>
+        <v>46090</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6633,7 +6628,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6676,7 +6671,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60792-2022</t>
+          <t>A 9527-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6690,10 +6685,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44914</v>
+        <v>44981</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6706,7 +6701,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6749,7 +6744,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40774-2025</t>
+          <t>A 12469-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6763,10 +6758,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45897</v>
+        <v>46090</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6779,7 +6774,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.7</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6822,7 +6817,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1922-2024</t>
+          <t>A 47522-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6836,10 +6831,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45308</v>
+        <v>45587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6851,8 +6846,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6895,7 +6895,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9401-2024</t>
+          <t>A 65143-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45359</v>
+        <v>45288</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6968,7 +6968,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54287-2022</t>
+          <t>A 28158-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44882</v>
+        <v>45476</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7041,7 +7041,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5072-2023</t>
+          <t>A 435-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44958</v>
+        <v>45664</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 65118-2023</t>
+          <t>A 50981-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45288</v>
+        <v>45218</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7143,8 +7143,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7187,7 +7192,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56335-2024</t>
+          <t>A 12879-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7197,14 +7202,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45624</v>
+        <v>46092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7216,8 +7221,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7260,7 +7270,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30769-2023</t>
+          <t>A 40774-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7274,10 +7284,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45112</v>
+        <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7290,7 +7300,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>6.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7333,7 +7343,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54659-2022</t>
+          <t>A 36650-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7347,10 +7357,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44883</v>
+        <v>45872</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7363,7 +7373,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7406,7 +7416,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30794-2023</t>
+          <t>A 50302-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7420,10 +7430,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45112</v>
+        <v>45216</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7436,7 +7446,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7479,7 +7489,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31718-2023</t>
+          <t>A 13120-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7493,10 +7503,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45117</v>
+        <v>46093</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7509,7 +7519,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7552,7 +7562,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28040-2024</t>
+          <t>A 13121-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7566,10 +7576,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45476</v>
+        <v>46093</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7582,7 +7592,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7625,7 +7635,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 22834-2024</t>
+          <t>A 59472-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7639,10 +7649,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45448</v>
+        <v>45254</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7655,7 +7665,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7698,7 +7708,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4782-2024</t>
+          <t>A 9530-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7712,10 +7722,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45328</v>
+        <v>44981</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7728,7 +7738,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7771,7 +7781,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9086-2025</t>
+          <t>A 58011-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7785,10 +7795,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45713</v>
+        <v>44900</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7801,7 +7811,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7844,7 +7854,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 43398-2024</t>
+          <t>A 56452-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7858,10 +7868,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45568</v>
+        <v>44893</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7874,7 +7884,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7917,7 +7927,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 59517-2023</t>
+          <t>A 14111-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7931,10 +7941,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45254</v>
+        <v>46099</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7947,7 +7957,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7990,7 +8000,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59816-2021</t>
+          <t>A 31546-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8000,14 +8010,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44494</v>
+        <v>44775</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8020,7 +8030,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8063,7 +8073,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3237-2023</t>
+          <t>A 58010-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8077,10 +8087,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44946</v>
+        <v>44900</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8093,7 +8103,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8136,7 +8146,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28073-2024</t>
+          <t>A 14545-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8146,14 +8156,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45476</v>
+        <v>46100</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8166,7 +8176,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8209,7 +8219,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 6745-2023</t>
+          <t>A 25928-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8219,14 +8229,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44966</v>
+        <v>45090</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8239,7 +8249,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8299,7 +8309,7 @@
         <v>45930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8355,7 +8365,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29794-2025</t>
+          <t>A 30628-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8369,10 +8379,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45825</v>
+        <v>45112</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8385,7 +8395,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8428,7 +8438,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11605-2024</t>
+          <t>A 30643-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8442,10 +8452,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45373</v>
+        <v>45112</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8458,7 +8468,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8501,7 +8511,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 70708-2021</t>
+          <t>A 48212-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8515,10 +8525,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44537</v>
+        <v>45933</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8531,7 +8541,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8574,7 +8584,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10918-2025</t>
+          <t>A 22834-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8588,10 +8598,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45722</v>
+        <v>45448</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8604,7 +8614,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8647,7 +8657,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9471-2025</t>
+          <t>A 41910-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8661,10 +8671,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45715</v>
+        <v>45561</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8677,7 +8687,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8720,7 +8730,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1921-2024</t>
+          <t>A 49269-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8734,10 +8744,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45308</v>
+        <v>45938</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8750,7 +8760,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8793,7 +8803,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 42250-2023</t>
+          <t>A 67455-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8807,10 +8817,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45180</v>
+        <v>44524</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8823,7 +8833,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8866,7 +8876,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1395-2024</t>
+          <t>A 58093-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8880,10 +8890,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45303</v>
+        <v>45248</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8896,7 +8906,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8939,7 +8949,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48212-2025</t>
+          <t>A 54144-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8953,10 +8963,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45933</v>
+        <v>44881</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8969,7 +8979,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9012,7 +9022,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31804-2025</t>
+          <t>A 51613-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9026,10 +9036,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45834</v>
+        <v>45951</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9042,7 +9052,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9085,7 +9095,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49269-2025</t>
+          <t>A 50057-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9099,10 +9109,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45938</v>
+        <v>45215</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9115,7 +9125,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9158,7 +9168,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32506-2025</t>
+          <t>A 46511-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9172,10 +9182,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45838</v>
+        <v>45197</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9188,7 +9198,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9231,7 +9241,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30633-2023</t>
+          <t>A 52513-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9245,10 +9255,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45112</v>
+        <v>45954</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9261,7 +9271,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9304,7 +9314,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32320-2025</t>
+          <t>A 52511-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9318,10 +9328,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45836</v>
+        <v>45954</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9334,7 +9344,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9377,7 +9387,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 23330-2024</t>
+          <t>A 52939-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9387,14 +9397,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45453</v>
+        <v>45957</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9406,13 +9416,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9455,7 +9460,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 11239-2023</t>
+          <t>A 6653-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9469,10 +9474,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44992</v>
+        <v>44602</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9485,7 +9490,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9528,7 +9533,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57036-2024</t>
+          <t>A 64207-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9542,10 +9547,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45629</v>
+        <v>44510</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9558,7 +9563,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9601,7 +9606,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9159-2024</t>
+          <t>A 2006-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9615,10 +9620,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45358</v>
+        <v>45308</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9631,7 +9636,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9674,7 +9679,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11021-2022</t>
+          <t>A 24368-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9688,10 +9693,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44628</v>
+        <v>44726</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9704,7 +9709,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9747,7 +9752,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 18613-2025</t>
+          <t>A 27103-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9761,10 +9766,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45763</v>
+        <v>45471</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9777,7 +9782,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9820,7 +9825,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 18614-2025</t>
+          <t>A 55159-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9834,10 +9839,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45763</v>
+        <v>45621</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9850,7 +9855,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>9.699999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9893,7 +9898,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 50302-2023</t>
+          <t>A 38586-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9907,10 +9912,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45216</v>
+        <v>45162</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9923,7 +9928,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9966,7 +9971,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 31712-2023</t>
+          <t>A 9159-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9980,10 +9985,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45117</v>
+        <v>45358</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9996,7 +10001,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10039,7 +10044,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31715-2023</t>
+          <t>A 31746-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10056,7 +10061,7 @@
         <v>45117</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10069,7 +10074,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10112,7 +10117,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31745-2023</t>
+          <t>A 63725-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10126,10 +10131,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45117</v>
+        <v>45276</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10142,7 +10147,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10185,7 +10190,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 51613-2025</t>
+          <t>A 58137-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10199,10 +10204,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45951</v>
+        <v>45982</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10215,7 +10220,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10258,7 +10263,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53055-2024</t>
+          <t>A 58139-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10272,10 +10277,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45611</v>
+        <v>45982</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10288,7 +10293,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10331,7 +10336,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 52511-2025</t>
+          <t>A 59613-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10345,10 +10350,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45954</v>
+        <v>45254</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10361,7 +10366,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10404,7 +10409,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 52513-2025</t>
+          <t>A 60089-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10418,10 +10423,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45954</v>
+        <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10434,7 +10439,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10477,7 +10482,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 47264-2024</t>
+          <t>A 60093-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10491,10 +10496,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45586</v>
+        <v>45993</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10507,7 +10512,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10550,7 +10555,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 52939-2025</t>
+          <t>A 60091-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10564,10 +10569,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45957</v>
+        <v>45993</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10580,7 +10585,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10623,7 +10628,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 31889-2023</t>
+          <t>A 60092-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10637,10 +10642,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45118</v>
+        <v>45993</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10653,7 +10658,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10696,7 +10701,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 47265-2024</t>
+          <t>A 59871-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10710,10 +10715,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45586</v>
+        <v>45992</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10726,7 +10731,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10769,7 +10774,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 42483-2023</t>
+          <t>A 19644-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10783,10 +10788,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45180</v>
+        <v>46134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10799,7 +10804,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10842,7 +10847,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 6653-2022</t>
+          <t>A 62986-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10856,10 +10861,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44602</v>
+        <v>45272</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10872,7 +10877,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10915,7 +10920,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 435-2025</t>
+          <t>A 59816-2021</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10929,10 +10934,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45664</v>
+        <v>44494</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10988,7 +10993,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28158-2024</t>
+          <t>A 59872-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11002,10 +11007,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45476</v>
+        <v>45992</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11018,7 +11023,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11061,7 +11066,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15112-2022</t>
+          <t>A 30650-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11075,10 +11080,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44658</v>
+        <v>45112</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11091,7 +11096,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11134,7 +11139,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 3238-2023</t>
+          <t>A 60181-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11148,10 +11153,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44946</v>
+        <v>45994</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11164,7 +11169,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11207,7 +11212,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59472-2023</t>
+          <t>A 30637-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11221,10 +11226,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45254</v>
+        <v>45112</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11237,7 +11242,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11280,7 +11285,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 36650-2025</t>
+          <t>A 60946-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11294,10 +11299,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45872</v>
+        <v>45999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11310,7 +11315,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11353,7 +11358,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31546-2022</t>
+          <t>A 65118-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11363,14 +11368,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44775</v>
+        <v>45288</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11383,7 +11388,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11426,7 +11431,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 36131-2024</t>
+          <t>A 6064-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11440,10 +11445,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45534</v>
+        <v>45696</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11456,7 +11461,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11499,7 +11504,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 9530-2023</t>
+          <t>A 18613-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11513,10 +11518,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44981</v>
+        <v>45763</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11529,7 +11534,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11572,7 +11577,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 36532-2024</t>
+          <t>A 18614-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11586,10 +11591,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45537</v>
+        <v>45763</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11602,7 +11607,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11645,7 +11650,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 22443-2023</t>
+          <t>A 52371-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11659,10 +11664,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45070</v>
+        <v>45953</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11675,7 +11680,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11718,7 +11723,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 20600-2026</t>
+          <t>A 56305-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11732,10 +11737,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46140</v>
+        <v>45974</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11748,7 +11753,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11791,7 +11796,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 52371-2025</t>
+          <t>A 36131-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11805,10 +11810,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45953</v>
+        <v>45534</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11821,7 +11826,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11864,7 +11869,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 54295-2023</t>
+          <t>A 36532-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11878,10 +11883,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45232</v>
+        <v>45537</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11894,7 +11899,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11937,7 +11942,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 56305-2025</t>
+          <t>A 10610-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11951,10 +11956,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45974</v>
+        <v>45721</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11967,7 +11972,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12010,7 +12015,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 58139-2025</t>
+          <t>A 54289-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12024,10 +12029,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45982</v>
+        <v>44882</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12040,7 +12045,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12083,7 +12088,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58137-2025</t>
+          <t>A 64005-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12097,10 +12102,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45982</v>
+        <v>46021</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12113,7 +12118,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12156,7 +12161,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20598-2026</t>
+          <t>A 42250-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12170,10 +12175,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46140</v>
+        <v>45180</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12186,7 +12191,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12229,7 +12234,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 25694-2025</t>
+          <t>A 42256-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12243,10 +12248,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45803</v>
+        <v>45180</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12259,7 +12264,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12302,7 +12307,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31724-2023</t>
+          <t>A 25694-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12316,10 +12321,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45117</v>
+        <v>45803</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12332,7 +12337,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12375,7 +12380,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31726-2023</t>
+          <t>A 1921-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12389,10 +12394,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45117</v>
+        <v>45308</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12405,7 +12410,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12448,7 +12453,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 30801-2023</t>
+          <t>A 2497-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12462,10 +12467,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45112</v>
+        <v>46037</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12478,7 +12483,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12521,7 +12526,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 17925-2022</t>
+          <t>A 31711-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12535,10 +12540,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44683</v>
+        <v>45117</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12551,7 +12556,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12594,7 +12599,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 56331-2024</t>
+          <t>A 31727-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12608,10 +12613,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45624</v>
+        <v>45117</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12624,7 +12629,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12667,7 +12672,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 20782-2026</t>
+          <t>A 11605-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12681,10 +12686,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46141</v>
+        <v>45373</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12697,7 +12702,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12740,7 +12745,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 21751-2022</t>
+          <t>A 4119-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12754,10 +12759,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44708</v>
+        <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12769,8 +12774,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12813,7 +12823,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 7046-2025</t>
+          <t>A 4587-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12827,10 +12837,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45701</v>
+        <v>46048</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12843,7 +12853,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12886,7 +12896,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 42256-2023</t>
+          <t>A 4588-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12900,10 +12910,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45180</v>
+        <v>46048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12916,7 +12926,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12959,7 +12969,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 41910-2024</t>
+          <t>A 53055-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12973,10 +12983,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45561</v>
+        <v>45611</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12989,7 +12999,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13032,7 +13042,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59871-2025</t>
+          <t>A 20598-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13046,10 +13056,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45992</v>
+        <v>46140</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13062,7 +13072,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13105,7 +13115,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 60091-2025</t>
+          <t>A 6071-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13119,10 +13129,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45993</v>
+        <v>46052</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13135,7 +13145,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13178,7 +13188,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 60092-2025</t>
+          <t>A 20600-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13192,10 +13202,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45993</v>
+        <v>46140</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13208,7 +13218,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13251,7 +13261,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60089-2025</t>
+          <t>A 6074-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13265,10 +13275,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45993</v>
+        <v>46052</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13281,7 +13291,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13324,7 +13334,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 60093-2025</t>
+          <t>A 6104-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13338,10 +13348,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45993</v>
+        <v>46052</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13354,7 +13364,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13397,7 +13407,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 59872-2025</t>
+          <t>A 6103-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13411,10 +13421,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45992</v>
+        <v>46052</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13427,7 +13437,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13470,7 +13480,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 60181-2025</t>
+          <t>A 20782-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13484,10 +13494,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45994</v>
+        <v>46141</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13500,7 +13510,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13543,7 +13553,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 62986-2023</t>
+          <t>A 7546-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13557,10 +13567,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45272</v>
+        <v>46059</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13573,7 +13583,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13616,7 +13626,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 60946-2025</t>
+          <t>A 29658-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13630,10 +13640,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45999</v>
+        <v>44754</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13646,7 +13656,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13689,7 +13699,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 30637-2023</t>
+          <t>A 57036-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13703,10 +13713,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45112</v>
+        <v>45629</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13719,7 +13729,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13762,7 +13772,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 51564-2024</t>
+          <t>A 11584-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13776,10 +13786,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45604</v>
+        <v>46084</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13792,7 +13802,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13835,7 +13845,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 59613-2023</t>
+          <t>A 54287-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13849,10 +13859,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45254</v>
+        <v>44882</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13865,7 +13875,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13908,7 +13918,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 10610-2025</t>
+          <t>A 15112-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13922,10 +13932,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45721</v>
+        <v>44658</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13938,7 +13948,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13981,7 +13991,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 64005-2025</t>
+          <t>A 1922-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13995,10 +14005,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46021</v>
+        <v>45308</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14011,7 +14021,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14054,7 +14064,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 61318-2023</t>
+          <t>A 61334-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14068,10 +14078,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45264</v>
+        <v>44915</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14084,7 +14094,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14127,7 +14137,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 31746-2023</t>
+          <t>A 51564-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14141,10 +14151,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45117</v>
+        <v>45604</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14157,7 +14167,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14200,7 +14210,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 31711-2023</t>
+          <t>A 7046-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14214,10 +14224,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45117</v>
+        <v>45701</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14230,7 +14240,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14273,7 +14283,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 31727-2023</t>
+          <t>A 30760-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14287,10 +14297,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14303,7 +14313,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14346,7 +14356,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 24965-2026</t>
+          <t>A 30762-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14360,10 +14370,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46174</v>
+        <v>45112</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14376,7 +14386,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14419,7 +14429,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 2497-2026</t>
+          <t>A 56331-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14433,10 +14443,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46037</v>
+        <v>45624</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14449,7 +14459,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14492,7 +14502,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 55159-2024</t>
+          <t>A 24965-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14506,10 +14516,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45621</v>
+        <v>46174</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14522,7 +14532,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14565,7 +14575,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 4119-2026</t>
+          <t>A 51314-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14575,14 +14585,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46044</v>
+        <v>45219</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14594,13 +14604,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14643,7 +14648,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 4587-2026</t>
+          <t>A 3238-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14657,10 +14662,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46048</v>
+        <v>44946</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14673,7 +14678,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14716,7 +14721,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 4588-2026</t>
+          <t>A 12160-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14730,10 +14735,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46048</v>
+        <v>45377</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14746,7 +14751,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14789,7 +14794,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 6071-2026</t>
+          <t>A 54659-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14803,10 +14808,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46052</v>
+        <v>44883</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14819,7 +14824,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14862,7 +14867,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 6074-2026</t>
+          <t>A 26642-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14876,10 +14881,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46052</v>
+        <v>46184</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14892,7 +14897,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14935,7 +14940,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 26642-2026</t>
+          <t>A 31718-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14949,10 +14954,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46184</v>
+        <v>45117</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14965,7 +14970,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15008,7 +15013,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 6104-2026</t>
+          <t>A 27248-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15022,10 +15027,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46052</v>
+        <v>46188</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15038,7 +15043,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15081,7 +15086,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 6103-2026</t>
+          <t>A 43398-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15095,10 +15100,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46052</v>
+        <v>45568</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15111,7 +15116,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15154,7 +15159,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 27248-2026</t>
+          <t>A 27782-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15168,10 +15173,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15184,7 +15189,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15227,7 +15232,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 7546-2026</t>
+          <t>A 54311-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15241,10 +15246,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46059</v>
+        <v>44882</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15257,7 +15262,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15300,7 +15305,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27782-2026</t>
+          <t>A 22443-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15314,10 +15319,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46191</v>
+        <v>45070</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15330,7 +15335,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>6.1</v>
+        <v>4.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15373,7 +15378,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 54144-2022</t>
+          <t>A 60792-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15387,10 +15392,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44881</v>
+        <v>44914</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15403,7 +15408,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15446,7 +15451,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 11584-2026</t>
+          <t>A 61026-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15460,10 +15465,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46084</v>
+        <v>44914</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15476,7 +15481,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15519,7 +15524,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 2006-2024</t>
+          <t>A 47264-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15533,10 +15538,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45308</v>
+        <v>45586</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15549,7 +15554,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15592,7 +15597,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 12469-2026</t>
+          <t>A 22541-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15606,10 +15611,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46090</v>
+        <v>45071</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15622,7 +15627,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15665,7 +15670,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 12503-2026</t>
+          <t>A 21751-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15679,10 +15684,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46090</v>
+        <v>44708</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15695,7 +15700,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15738,7 +15743,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 61671-2022</t>
+          <t>A 1395-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15752,10 +15757,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44917</v>
+        <v>45303</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15768,7 +15773,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15811,7 +15816,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 51229-2022</t>
+          <t>A 2398-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15825,10 +15830,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44868</v>
+        <v>45310</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15841,7 +15846,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15884,7 +15889,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 13120-2026</t>
+          <t>A 30793-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15898,10 +15903,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46093</v>
+        <v>45112</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15914,7 +15919,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15957,7 +15962,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 13121-2026</t>
+          <t>A 30795-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15971,10 +15976,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46093</v>
+        <v>45112</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15987,7 +15992,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16030,7 +16035,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 12879-2026</t>
+          <t>A 30800-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16040,14 +16045,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46092</v>
+        <v>45112</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16059,13 +16064,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16108,7 +16108,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 61334-2022</t>
+          <t>A 30098-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44915</v>
+        <v>46206</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16181,7 +16181,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 14111-2026</t>
+          <t>A 28040-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46099</v>
+        <v>45476</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16254,7 +16254,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 14545-2026</t>
+          <t>A 18337-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16264,14 +16264,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46100</v>
+        <v>45041</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16327,7 +16327,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 58011-2022</t>
+          <t>A 11021-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16341,10 +16341,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44900</v>
+        <v>44628</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16400,7 +16400,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 56452-2022</t>
+          <t>A 11239-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16414,10 +16414,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44893</v>
+        <v>44992</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16473,7 +16473,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 58010-2022</t>
+          <t>A 31717-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44900</v>
+        <v>45117</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16546,7 +16546,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 30098-2026</t>
+          <t>A 31719-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16560,10 +16560,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46206</v>
+        <v>45117</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16619,7 +16619,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 30793-2023</t>
+          <t>A 31745-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16633,10 +16633,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16692,7 +16692,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 30795-2023</t>
+          <t>A 56335-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16706,10 +16706,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45112</v>
+        <v>45624</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16765,7 +16765,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 30724-2023</t>
+          <t>A 30801-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16782,7 +16782,7 @@
         <v>45112</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16838,7 +16838,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 54311-2022</t>
+          <t>A 70708-2021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16852,10 +16852,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44882</v>
+        <v>44537</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16911,7 +16911,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 56334-2024</t>
+          <t>A 36861-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45624</v>
+        <v>46272</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16984,7 +16984,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 61026-2022</t>
+          <t>A 31712-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16998,10 +16998,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44914</v>
+        <v>45117</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17057,7 +17057,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 63725-2023</t>
+          <t>A 31715-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17071,10 +17071,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45276</v>
+        <v>45117</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>12.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17130,7 +17130,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 9527-2023</t>
+          <t>A 59517-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17144,10 +17144,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44981</v>
+        <v>45254</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17203,7 +17203,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30760-2023</t>
+          <t>A 30724-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17220,7 +17220,7 @@
         <v>45112</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 30762-2023</t>
+          <t>A 31907-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17290,10 +17290,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45112</v>
+        <v>46231</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17305,8 +17305,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17349,7 +17354,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38586-2023</t>
+          <t>A 57443-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17363,10 +17368,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45162</v>
+        <v>45629</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17379,7 +17384,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17422,7 +17427,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 19644-2026</t>
+          <t>A 23330-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17432,14 +17437,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46134</v>
+        <v>45453</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17451,8 +17456,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17495,7 +17505,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 6064-2025</t>
+          <t>A 23907-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17509,10 +17519,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45696</v>
+        <v>45455</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17525,7 +17535,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17568,7 +17578,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 30772-2023</t>
+          <t>A 21878-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17582,10 +17592,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45112</v>
+        <v>45784</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17598,7 +17608,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17641,7 +17651,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36861-2026</t>
+          <t>A 38521-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17655,10 +17665,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46272</v>
+        <v>46283</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17671,7 +17681,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17714,7 +17724,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 2398-2024</t>
+          <t>A 43938-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17728,10 +17738,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45310</v>
+        <v>45572</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17744,7 +17754,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17787,7 +17797,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 31907-2026</t>
+          <t>A 38601-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17801,10 +17811,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46231</v>
+        <v>46283</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17816,13 +17826,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17865,7 +17870,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 50981-2023</t>
+          <t>A 47258-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17879,10 +17884,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45218</v>
+        <v>45930</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17894,13 +17899,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17943,7 +17943,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 58093-2023</t>
+          <t>A 39344-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17957,10 +17957,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45248</v>
+        <v>46288</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 64207-2021</t>
+          <t>A 39852-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18030,10 +18030,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44510</v>
+        <v>46290</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 38521-2026</t>
+          <t>A 39841-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18162,7 +18162,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 38601-2026</t>
+          <t>A 9086-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18176,10 +18176,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46283</v>
+        <v>45713</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 39344-2026</t>
+          <t>A 39896-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18249,10 +18249,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18308,7 +18308,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 47258-2025</t>
+          <t>A 28073-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18322,10 +18322,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45930</v>
+        <v>45476</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18381,7 +18381,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 39852-2026</t>
+          <t>A 29794-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18395,10 +18395,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46290</v>
+        <v>45825</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18454,7 +18454,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 39841-2026</t>
+          <t>A 10918-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18468,10 +18468,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46290</v>
+        <v>45722</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18527,7 +18527,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 39896-2026</t>
+          <t>A 33852-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18541,10 +18541,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46290</v>
+        <v>46251</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 33852-2026</t>
+          <t>A 33853-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18617,7 +18617,7 @@
         <v>46251</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18673,7 +18673,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 33853-2026</t>
+          <t>A 9471-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18687,10 +18687,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46251</v>
+        <v>45715</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18763,7 +18763,7 @@
         <v>46120</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 35071-2026</t>
+          <t>A 35072-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18836,7 +18836,7 @@
         <v>46259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18892,7 +18892,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 35072-2026</t>
+          <t>A 12124-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18906,10 +18906,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46259</v>
+        <v>45377</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18921,8 +18921,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18965,7 +18970,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 12124-2024</t>
+          <t>A 35071-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18979,10 +18984,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45377</v>
+        <v>46259</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18994,13 +18999,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>45934</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>46154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>46246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 30777-2023</t>
+          <t>A 50011-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45112</v>
+        <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,45 +845,158 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Svartbent strandpipare
+Sexfläckig bastardsvärmare
+Grönsångare
+Strandskata
+Sädesärla</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 30777-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
         <v>10</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>8</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Oxtungssvamp
 Vågbandad barkbock
@@ -892,107 +1005,107 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 50084-2025</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>45943</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>12.5</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>5</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Spillkråka
@@ -1001,149 +1114,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50084-2025 artfynd.xlsx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50084-2025 karta.png", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50084-2025 georefererad karta.tif", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50084-2025 FSC-klagomål.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50084-2025 FSC-klagomål mail.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50084-2025 tillsynsbegäran.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50084-2025 tillsynsbegäran mail.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50084-2025 prioriterade fågelarter.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 50011-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45215</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Svartbent strandpipare
-Sexfläckig bastardsvärmare
-Grönsångare
-Strandskata
-Sädesärla</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
         <v/>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31728-2023</t>
+          <t>A 30785-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1525,17 +1525,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1558,269 +1558,269 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30785-2023 artfynd.xlsx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30785-2023 karta.png", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30785-2023 georefererad karta.tif", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30785-2023 FSC-klagomål.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30785-2023 FSC-klagomål mail.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30785-2023 tillsynsbegäran.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30785-2023 tillsynsbegäran mail.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31728-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Gammelgransskål
 Kattfotslav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31728-2023 artfynd.xlsx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31728-2023 karta.png", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31728-2023 georefererad karta.tif", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31728-2023 FSC-klagomål.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31728-2023 FSC-klagomål mail.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31728-2023 tillsynsbegäran.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31728-2023 tillsynsbegäran mail.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31728-2023 prioriterade fågelarter.docx", "A 31728-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 30655-2023</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>45112</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>2.9</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trädporella
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30655-2023 artfynd.xlsx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30655-2023 karta.png", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30655-2023 georefererad karta.tif", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30655-2023 FSC-klagomål.docx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30655-2023 FSC-klagomål mail.docx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30655-2023 tillsynsbegäran.docx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30655-2023 tillsynsbegäran mail.docx", "A 30655-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 30785-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30785-2023 artfynd.xlsx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30785-2023 karta.png", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30785-2023 georefererad karta.tif", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30785-2023 FSC-klagomål.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30785-2023 FSC-klagomål mail.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30785-2023 tillsynsbegäran.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30785-2023 tillsynsbegäran mail.docx", "A 30785-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30666-2023</t>
+          <t>A 9930-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45112</v>
+        <v>45363</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1890,805 +1890,805 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Större träfjäril
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 9930-2024 artfynd.xlsx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 9930-2024 karta.png", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 9930-2024 georefererad karta.tif", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 9930-2024 FSC-klagomål.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 9930-2024 FSC-klagomål mail.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 9930-2024 tillsynsbegäran.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 9930-2024 tillsynsbegäran mail.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 9930-2024 prioriterade fågelarter.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 31714-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 30666-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>Talltita
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30792-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 30763-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30763-2023 artfynd.xlsx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30763-2023 karta.png", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30763-2023 georefererad karta.tif", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30763-2023 FSC-klagomål.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30763-2023 FSC-klagomål mail.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30763-2023 tillsynsbegäran.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30763-2023 tillsynsbegäran mail.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30763-2023 prioriterade fågelarter.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 60380-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 13115-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>46093</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>6.5</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 13115-2026 artfynd.xlsx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 13115-2026 karta.png", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 13115-2026 georefererad karta.tif", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 13115-2026 FSC-klagomål.docx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 13115-2026 FSC-klagomål mail.docx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 13115-2026 tillsynsbegäran.docx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 13115-2026 tillsynsbegäran mail.docx", "A 13115-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9930-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45363</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 26670-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Större träfjäril
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 9930-2024 artfynd.xlsx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 9930-2024 karta.png", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 9930-2024 georefererad karta.tif", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 9930-2024 FSC-klagomål.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 9930-2024 FSC-klagomål mail.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 9930-2024 tillsynsbegäran.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 9930-2024 tillsynsbegäran mail.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 9930-2024 prioriterade fågelarter.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 60380-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26670-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Tofsmes
 Grönsiska</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 26670-2026 artfynd.xlsx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 26670-2026 karta.png", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 26670-2026 georefererad karta.tif", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 26670-2026 FSC-klagomål.docx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 26670-2026 FSC-klagomål mail.docx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 26670-2026 tillsynsbegäran.docx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 26670-2026 tillsynsbegäran mail.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 31714-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 30763-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30763-2023 artfynd.xlsx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30763-2023 karta.png", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30763-2023 georefererad karta.tif", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30763-2023 FSC-klagomål.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30763-2023 FSC-klagomål mail.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30763-2023 tillsynsbegäran.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30763-2023 tillsynsbegäran mail.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30763-2023 prioriterade fågelarter.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 30792-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30754-2023</t>
+          <t>A 35491-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45112</v>
+        <v>45146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2718,20 +2718,20 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2754,39 +2754,43 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
     </row>
@@ -2810,7 +2814,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2902,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32503-2025</t>
+          <t>A 30653-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2912,10 +2916,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45838</v>
+        <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2928,13 +2932,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2968,42 +2972,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30653-2023</t>
+          <t>A 30662-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3020,7 +3028,7 @@
         <v>45112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3033,7 +3041,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3073,46 +3081,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18822-2026</t>
+          <t>A 23906-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3126,10 +3130,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46128</v>
+        <v>45455</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3146,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3157,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3166,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3178,46 +3182,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7339-2025</t>
+          <t>A 30754-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3235,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45703</v>
+        <v>45112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,13 +3251,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3287,35 +3291,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
     </row>
@@ -3339,7 +3343,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3427,7 +3431,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35491-2023</t>
+          <t>A 32503-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3441,10 +3445,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45146</v>
+        <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3457,19 +3461,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3481,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3493,50 +3497,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30662-2023</t>
+          <t>A 18822-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45112</v>
+        <v>46128</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3566,23 +3566,23 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
@@ -3590,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3602,46 +3602,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31742-2023</t>
+          <t>A 7339-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45703</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3704,53 +3704,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23906-2024</t>
+          <t>A 31742-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3764,10 +3760,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45455</v>
+        <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3780,10 +3776,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3813,42 +3809,46 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
         <v/>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44764</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44502</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 68882-2021</t>
+          <t>A 17990-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44530</v>
+        <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17990-2022</t>
+          <t>A 3360-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4418,14 +4418,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44683</v>
+        <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3360-2022</t>
+          <t>A 68882-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44585</v>
+        <v>44530</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>44531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 39556-2022</t>
+          <t>A 29658-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44818</v>
+        <v>44754</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30633-2023</t>
+          <t>A 18615-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45112</v>
+        <v>45763</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 31889-2023</t>
+          <t>A 31717-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45118</v>
+        <v>45117</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51229-2022</t>
+          <t>A 31719-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44868</v>
+        <v>45117</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30769-2023</t>
+          <t>A 39556-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45112</v>
+        <v>44818</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30794-2023</t>
+          <t>A 30800-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5009,7 +5009,7 @@
         <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6745-2023</t>
+          <t>A 30760-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5075,14 +5075,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44966</v>
+        <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30772-2023</t>
+          <t>A 30762-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5155,7 +5155,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18615-2025</t>
+          <t>A 24368-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45763</v>
+        <v>44726</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4782-2024</t>
+          <t>A 30650-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45328</v>
+        <v>45112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3237-2023</t>
+          <t>A 46511-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44946</v>
+        <v>45197</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5430,7 +5430,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31724-2023</t>
+          <t>A 12160-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5444,10 +5444,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45117</v>
+        <v>45377</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5503,7 +5503,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31726-2023</t>
+          <t>A 38586-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45117</v>
+        <v>45162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61671-2022</t>
+          <t>A 54289-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44917</v>
+        <v>44882</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56334-2024</t>
+          <t>A 1922-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45624</v>
+        <v>45308</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61318-2023</t>
+          <t>A 30772-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45264</v>
+        <v>45112</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5795,7 +5795,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 42483-2023</t>
+          <t>A 5072-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45180</v>
+        <v>44958</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5868,7 +5868,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47265-2024</t>
+          <t>A 60792-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45586</v>
+        <v>44914</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8570-2025</t>
+          <t>A 65118-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45709</v>
+        <v>45288</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5072-2023</t>
+          <t>A 50057-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44958</v>
+        <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6087,7 +6087,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17925-2022</t>
+          <t>A 31546-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6097,14 +6097,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44683</v>
+        <v>44775</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31804-2025</t>
+          <t>A 56335-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45834</v>
+        <v>45624</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6233,7 +6233,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47980-2023</t>
+          <t>A 9401-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45204</v>
+        <v>45359</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6306,7 +6306,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9401-2024</t>
+          <t>A 25928-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45359</v>
+        <v>45090</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6379,7 +6379,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 54295-2023</t>
+          <t>A 54287-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6393,10 +6393,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45232</v>
+        <v>44882</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32320-2025</t>
+          <t>A 43398-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45836</v>
+        <v>45568</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6525,7 +6525,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32506-2025</t>
+          <t>A 59517-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45838</v>
+        <v>45254</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6598,7 +6598,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12503-2026</t>
+          <t>A 30769-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46090</v>
+        <v>45112</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.2</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6671,7 +6671,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9527-2023</t>
+          <t>A 54659-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44981</v>
+        <v>44883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6744,7 +6744,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12469-2026</t>
+          <t>A 30794-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46090</v>
+        <v>45112</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6817,7 +6817,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 47522-2024</t>
+          <t>A 31718-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45587</v>
+        <v>45117</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6846,13 +6846,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6895,7 +6890,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 65143-2023</t>
+          <t>A 2398-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6909,10 +6904,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45288</v>
+        <v>45310</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6925,7 +6920,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6968,7 +6963,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28158-2024</t>
+          <t>A 28040-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6985,7 +6980,7 @@
         <v>45476</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +6993,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7041,7 +7036,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 435-2025</t>
+          <t>A 22834-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7055,10 +7050,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45664</v>
+        <v>45448</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7066,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7114,7 +7109,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50981-2023</t>
+          <t>A 59816-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7128,10 +7123,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45218</v>
+        <v>44494</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7143,13 +7138,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7192,7 +7182,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12879-2026</t>
+          <t>A 4782-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7202,14 +7192,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46092</v>
+        <v>45328</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7221,13 +7211,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7270,7 +7255,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40774-2025</t>
+          <t>A 47522-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7284,10 +7269,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45897</v>
+        <v>45587</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7299,8 +7284,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7343,7 +7333,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36650-2025</t>
+          <t>A 50981-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7357,10 +7347,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45872</v>
+        <v>45218</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7372,8 +7362,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7416,7 +7411,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50302-2023</t>
+          <t>A 3237-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7430,10 +7425,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45216</v>
+        <v>44946</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7446,7 +7441,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7489,7 +7484,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13120-2026</t>
+          <t>A 58093-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7503,10 +7498,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46093</v>
+        <v>45248</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7519,7 +7514,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7562,7 +7557,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13121-2026</t>
+          <t>A 6745-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7572,14 +7567,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46093</v>
+        <v>44966</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7592,7 +7587,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7635,7 +7630,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59472-2023</t>
+          <t>A 65143-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7649,10 +7644,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45254</v>
+        <v>45288</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7665,7 +7660,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7708,7 +7703,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9530-2023</t>
+          <t>A 64207-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7722,10 +7717,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44981</v>
+        <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7738,7 +7733,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7781,7 +7776,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58011-2022</t>
+          <t>A 40774-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7795,10 +7790,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44900</v>
+        <v>45897</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7811,7 +7806,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7854,7 +7849,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56452-2022</t>
+          <t>A 11605-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7868,10 +7863,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44893</v>
+        <v>45373</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7884,7 +7879,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7927,7 +7922,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14111-2026</t>
+          <t>A 70708-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7941,10 +7936,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46099</v>
+        <v>44537</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7957,7 +7952,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8000,7 +7995,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 31546-2022</t>
+          <t>A 27103-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8010,14 +8005,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44775</v>
+        <v>45471</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8030,7 +8025,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8073,7 +8068,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58010-2022</t>
+          <t>A 57443-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8087,10 +8082,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44900</v>
+        <v>45629</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8103,7 +8098,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8146,7 +8141,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14545-2026</t>
+          <t>A 1395-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8156,14 +8151,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46100</v>
+        <v>45303</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8176,7 +8171,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8219,7 +8214,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 25928-2023</t>
+          <t>A 30633-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8233,10 +8228,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45090</v>
+        <v>45112</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8249,7 +8244,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8292,7 +8287,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47279-2025</t>
+          <t>A 23330-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8302,14 +8297,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45930</v>
+        <v>45453</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8321,8 +8316,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8365,7 +8365,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30628-2023</t>
+          <t>A 1921-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45112</v>
+        <v>45308</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8438,7 +8438,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30643-2023</t>
+          <t>A 42250-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45112</v>
+        <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8511,7 +8511,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48212-2025</t>
+          <t>A 21878-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45933</v>
+        <v>45784</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8584,7 +8584,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22834-2024</t>
+          <t>A 57036-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8598,10 +8598,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45448</v>
+        <v>45629</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8657,7 +8657,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 41910-2024</t>
+          <t>A 23907-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45561</v>
+        <v>45455</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 49269-2025</t>
+          <t>A 9159-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45938</v>
+        <v>45358</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8803,7 +8803,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 67455-2021</t>
+          <t>A 11021-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44524</v>
+        <v>44628</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8876,7 +8876,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58093-2023</t>
+          <t>A 11239-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45248</v>
+        <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8949,7 +8949,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 54144-2022</t>
+          <t>A 50302-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8963,10 +8963,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44881</v>
+        <v>45216</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9022,7 +9022,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 51613-2025</t>
+          <t>A 53055-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45951</v>
+        <v>45611</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 50057-2023</t>
+          <t>A 18613-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45215</v>
+        <v>45763</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9168,7 +9168,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 46511-2023</t>
+          <t>A 18614-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45197</v>
+        <v>45763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9241,7 +9241,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52513-2025</t>
+          <t>A 31712-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45954</v>
+        <v>45117</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9314,7 +9314,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52511-2025</t>
+          <t>A 31715-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45954</v>
+        <v>45117</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9387,7 +9387,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52939-2025</t>
+          <t>A 31745-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9401,10 +9401,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45957</v>
+        <v>45117</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9460,7 +9460,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 6653-2022</t>
+          <t>A 43938-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44602</v>
+        <v>45572</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 64207-2021</t>
+          <t>A 31889-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44510</v>
+        <v>45118</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9606,7 +9606,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 2006-2024</t>
+          <t>A 47279-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9620,10 +9620,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45308</v>
+        <v>45930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9679,7 +9679,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24368-2022</t>
+          <t>A 47264-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9693,10 +9693,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44726</v>
+        <v>45586</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9752,7 +9752,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 27103-2024</t>
+          <t>A 47265-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45471</v>
+        <v>45586</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 55159-2024</t>
+          <t>A 15112-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45621</v>
+        <v>44658</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9898,7 +9898,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 38586-2023</t>
+          <t>A 3238-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9912,10 +9912,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45162</v>
+        <v>44946</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9971,7 +9971,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 9159-2024</t>
+          <t>A 42483-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45358</v>
+        <v>45180</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10044,7 +10044,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31746-2023</t>
+          <t>A 59472-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10058,10 +10058,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45117</v>
+        <v>45254</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10117,7 +10117,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63725-2023</t>
+          <t>A 6653-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45276</v>
+        <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10190,7 +10190,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 58137-2025</t>
+          <t>A 9530-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10204,10 +10204,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45982</v>
+        <v>44981</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10263,7 +10263,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58139-2025</t>
+          <t>A 48212-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10277,10 +10277,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45982</v>
+        <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10336,7 +10336,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 59613-2023</t>
+          <t>A 22443-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45254</v>
+        <v>45070</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10409,7 +10409,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 60089-2025</t>
+          <t>A 54295-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45993</v>
+        <v>45232</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10482,7 +10482,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 60093-2025</t>
+          <t>A 49269-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10496,10 +10496,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45993</v>
+        <v>45938</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10555,7 +10555,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60091-2025</t>
+          <t>A 9086-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10569,10 +10569,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45993</v>
+        <v>45713</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10628,7 +10628,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60092-2025</t>
+          <t>A 30801-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10642,10 +10642,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45993</v>
+        <v>45112</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10701,7 +10701,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59871-2025</t>
+          <t>A 56331-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10715,10 +10715,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45992</v>
+        <v>45624</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10774,7 +10774,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19644-2026</t>
+          <t>A 31724-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46134</v>
+        <v>45117</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10847,7 +10847,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62986-2023</t>
+          <t>A 31726-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45272</v>
+        <v>45117</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10920,7 +10920,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 59816-2021</t>
+          <t>A 17925-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44494</v>
+        <v>44683</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10993,7 +10993,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59872-2025</t>
+          <t>A 21751-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45992</v>
+        <v>44708</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30650-2023</t>
+          <t>A 28073-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11080,10 +11080,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45112</v>
+        <v>45476</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11139,7 +11139,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60181-2025</t>
+          <t>A 7046-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11153,10 +11153,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45994</v>
+        <v>45701</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11212,7 +11212,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 30637-2023</t>
+          <t>A 29794-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11226,10 +11226,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45112</v>
+        <v>45825</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11285,7 +11285,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60946-2025</t>
+          <t>A 42256-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45999</v>
+        <v>45180</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11358,7 +11358,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 65118-2023</t>
+          <t>A 41910-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11372,10 +11372,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45288</v>
+        <v>45561</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11431,7 +11431,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 6064-2025</t>
+          <t>A 10918-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11445,10 +11445,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45696</v>
+        <v>45722</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11504,7 +11504,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 18613-2025</t>
+          <t>A 9471-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11518,10 +11518,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45763</v>
+        <v>45715</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11577,7 +11577,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 18614-2025</t>
+          <t>A 51613-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45763</v>
+        <v>45951</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11650,7 +11650,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 52371-2025</t>
+          <t>A 62986-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11664,10 +11664,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45953</v>
+        <v>45272</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11723,7 +11723,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56305-2025</t>
+          <t>A 52511-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11737,10 +11737,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45974</v>
+        <v>45954</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11796,7 +11796,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 36131-2024</t>
+          <t>A 52513-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11810,10 +11810,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45534</v>
+        <v>45954</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36532-2024</t>
+          <t>A 52939-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11883,10 +11883,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45537</v>
+        <v>45957</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11942,7 +11942,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 10610-2025</t>
+          <t>A 31804-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11956,10 +11956,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45721</v>
+        <v>45834</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12015,7 +12015,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 54289-2022</t>
+          <t>A 32506-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12029,10 +12029,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44882</v>
+        <v>45838</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12088,7 +12088,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 64005-2025</t>
+          <t>A 30637-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12102,10 +12102,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46021</v>
+        <v>45112</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12161,7 +12161,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 42250-2023</t>
+          <t>A 32320-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12175,10 +12175,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45180</v>
+        <v>45836</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>11.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12234,7 +12234,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 42256-2023</t>
+          <t>A 51564-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12248,10 +12248,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45180</v>
+        <v>45604</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12307,7 +12307,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 25694-2025</t>
+          <t>A 59613-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12321,10 +12321,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45803</v>
+        <v>45254</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12380,7 +12380,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 1921-2024</t>
+          <t>A 31746-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12394,10 +12394,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45308</v>
+        <v>45117</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12453,7 +12453,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 2497-2026</t>
+          <t>A 31711-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12467,10 +12467,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46037</v>
+        <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 31711-2023</t>
+          <t>A 31727-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12543,7 +12543,7 @@
         <v>45117</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12599,7 +12599,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 31727-2023</t>
+          <t>A 61318-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12613,10 +12613,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45117</v>
+        <v>45264</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12672,7 +12672,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 11605-2024</t>
+          <t>A 51314-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12682,14 +12682,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45373</v>
+        <v>45219</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 4119-2026</t>
+          <t>A 435-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46044</v>
+        <v>45664</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12772,11 +12772,6 @@
       <c r="G153" t="inlineStr">
         <is>
           <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -12823,7 +12818,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4587-2026</t>
+          <t>A 28158-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12837,10 +12832,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46048</v>
+        <v>45476</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12853,7 +12848,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.8</v>
+        <v>6.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12896,7 +12891,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 4588-2026</t>
+          <t>A 47980-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12910,10 +12905,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46048</v>
+        <v>45204</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12926,7 +12921,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12969,7 +12964,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 53055-2024</t>
+          <t>A 8570-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12983,10 +12978,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45611</v>
+        <v>45709</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13042,7 +13037,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 20598-2026</t>
+          <t>A 36650-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13056,10 +13051,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46140</v>
+        <v>45872</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13072,7 +13067,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13115,7 +13110,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6071-2026</t>
+          <t>A 58139-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13129,10 +13124,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46052</v>
+        <v>45982</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13145,7 +13140,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13188,7 +13183,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 20600-2026</t>
+          <t>A 18337-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13202,10 +13197,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46140</v>
+        <v>45041</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13218,7 +13213,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13261,7 +13256,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 6074-2026</t>
+          <t>A 58137-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13275,10 +13270,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46052</v>
+        <v>45982</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13334,7 +13329,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 6104-2026</t>
+          <t>A 22541-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13348,10 +13343,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46052</v>
+        <v>45071</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13364,7 +13359,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13407,7 +13402,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 6103-2026</t>
+          <t>A 55159-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13421,10 +13416,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46052</v>
+        <v>45621</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13437,7 +13432,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13480,7 +13475,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20782-2026</t>
+          <t>A 14111-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13494,10 +13489,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46141</v>
+        <v>46099</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13510,7 +13505,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13553,7 +13548,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 7546-2026</t>
+          <t>A 14545-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13563,14 +13558,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46059</v>
+        <v>46100</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13583,7 +13578,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13626,7 +13621,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 29658-2022</t>
+          <t>A 58011-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13640,10 +13635,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44754</v>
+        <v>44900</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13656,7 +13651,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13699,7 +13694,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 57036-2024</t>
+          <t>A 56452-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13713,10 +13708,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45629</v>
+        <v>44893</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13729,7 +13724,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13772,7 +13767,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 11584-2026</t>
+          <t>A 58010-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13786,10 +13781,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46084</v>
+        <v>44900</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13802,7 +13797,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13845,7 +13840,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 54287-2022</t>
+          <t>A 67455-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13859,10 +13854,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44882</v>
+        <v>44524</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13875,7 +13870,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13918,7 +13913,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15112-2022</t>
+          <t>A 30628-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13932,10 +13927,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44658</v>
+        <v>45112</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13948,7 +13943,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13991,7 +13986,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 1922-2024</t>
+          <t>A 30643-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14005,10 +14000,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45308</v>
+        <v>45112</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14021,7 +14016,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14064,7 +14059,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 61334-2022</t>
+          <t>A 59871-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14078,10 +14073,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44915</v>
+        <v>45992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14094,7 +14089,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14137,7 +14132,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 51564-2024</t>
+          <t>A 60091-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14151,10 +14146,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45604</v>
+        <v>45993</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14167,7 +14162,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14210,7 +14205,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 7046-2025</t>
+          <t>A 60092-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14224,10 +14219,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45701</v>
+        <v>45993</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14240,7 +14235,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14283,7 +14278,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 30760-2023</t>
+          <t>A 60089-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14297,10 +14292,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45112</v>
+        <v>45993</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14313,7 +14308,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14356,7 +14351,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 30762-2023</t>
+          <t>A 60093-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14370,10 +14365,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45112</v>
+        <v>45993</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14429,7 +14424,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 56331-2024</t>
+          <t>A 59872-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14443,10 +14438,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45624</v>
+        <v>45992</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14459,7 +14454,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14502,7 +14497,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24965-2026</t>
+          <t>A 60181-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14516,10 +14511,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46174</v>
+        <v>45994</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14532,7 +14527,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14575,7 +14570,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 51314-2023</t>
+          <t>A 60946-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14585,14 +14580,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45219</v>
+        <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14605,7 +14600,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14648,7 +14643,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 3238-2023</t>
+          <t>A 19644-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14662,10 +14657,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44946</v>
+        <v>46134</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14678,7 +14673,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14721,7 +14716,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 12160-2024</t>
+          <t>A 54144-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14735,10 +14730,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45377</v>
+        <v>44881</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14751,7 +14746,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14794,7 +14789,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 54659-2022</t>
+          <t>A 6064-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14808,10 +14803,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44883</v>
+        <v>45696</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14824,7 +14819,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14867,7 +14862,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 26642-2026</t>
+          <t>A 2006-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14881,10 +14876,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46184</v>
+        <v>45308</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14897,7 +14892,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14940,7 +14935,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31718-2023</t>
+          <t>A 10610-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14954,10 +14949,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45117</v>
+        <v>45721</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14970,7 +14965,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15013,7 +15008,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 27248-2026</t>
+          <t>A 61671-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15027,10 +15022,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46188</v>
+        <v>44917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15043,7 +15038,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15086,7 +15081,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 43398-2024</t>
+          <t>A 64005-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15100,10 +15095,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45568</v>
+        <v>46021</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15116,7 +15111,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15159,7 +15154,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 27782-2026</t>
+          <t>A 51229-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15173,10 +15168,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46191</v>
+        <v>44868</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15189,7 +15184,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15232,7 +15227,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 54311-2022</t>
+          <t>A 36131-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15246,10 +15241,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44882</v>
+        <v>45534</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15262,7 +15257,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15305,7 +15300,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 22443-2023</t>
+          <t>A 36532-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15319,10 +15314,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45070</v>
+        <v>45537</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15335,7 +15330,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15378,7 +15373,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 60792-2022</t>
+          <t>A 61334-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15392,10 +15387,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44914</v>
+        <v>44915</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15408,7 +15403,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15451,7 +15446,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 61026-2022</t>
+          <t>A 20600-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15465,10 +15460,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44914</v>
+        <v>46140</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15481,7 +15476,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15524,7 +15519,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 47264-2024</t>
+          <t>A 52371-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15538,10 +15533,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45586</v>
+        <v>45953</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15554,7 +15549,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15597,7 +15592,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 22541-2023</t>
+          <t>A 2497-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15611,10 +15606,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45071</v>
+        <v>46037</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15627,7 +15622,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15670,7 +15665,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 21751-2022</t>
+          <t>A 56305-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15684,10 +15679,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44708</v>
+        <v>45974</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15700,7 +15695,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15743,7 +15738,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 1395-2024</t>
+          <t>A 30793-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15757,10 +15752,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45303</v>
+        <v>45112</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15773,7 +15768,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15816,7 +15811,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 2398-2024</t>
+          <t>A 30795-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15830,10 +15825,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45310</v>
+        <v>45112</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15846,7 +15841,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15889,7 +15884,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 30793-2023</t>
+          <t>A 30724-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15906,7 +15901,7 @@
         <v>45112</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15919,7 +15914,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15962,7 +15957,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 30795-2023</t>
+          <t>A 20598-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15976,10 +15971,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45112</v>
+        <v>46140</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15992,7 +15987,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16035,7 +16030,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30800-2023</t>
+          <t>A 25694-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16049,10 +16044,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45112</v>
+        <v>45803</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16065,7 +16060,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16108,7 +16103,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 30098-2026</t>
+          <t>A 4119-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16122,10 +16117,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46206</v>
+        <v>46044</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16137,8 +16132,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16181,7 +16181,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28040-2024</t>
+          <t>A 54311-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45476</v>
+        <v>44882</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16254,7 +16254,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 18337-2023</t>
+          <t>A 4587-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16268,10 +16268,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45041</v>
+        <v>46048</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16327,7 +16327,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 11021-2022</t>
+          <t>A 4588-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16341,10 +16341,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44628</v>
+        <v>46048</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16400,7 +16400,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 11239-2023</t>
+          <t>A 56334-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16414,10 +16414,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44992</v>
+        <v>45624</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16473,7 +16473,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 31717-2023</t>
+          <t>A 61026-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45117</v>
+        <v>44914</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16546,7 +16546,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31719-2023</t>
+          <t>A 20782-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16560,10 +16560,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45117</v>
+        <v>46141</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31745-2023</t>
+          <t>A 63725-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16633,10 +16633,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45117</v>
+        <v>45276</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16692,7 +16692,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 56335-2024</t>
+          <t>A 9527-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16706,10 +16706,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45624</v>
+        <v>44981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16765,7 +16765,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 30801-2023</t>
+          <t>A 6071-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16779,10 +16779,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45112</v>
+        <v>46052</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16838,7 +16838,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 70708-2021</t>
+          <t>A 6074-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16852,10 +16852,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44537</v>
+        <v>46052</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16911,7 +16911,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 36861-2026</t>
+          <t>A 6104-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16925,10 +16925,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46272</v>
+        <v>46052</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16984,7 +16984,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31712-2023</t>
+          <t>A 6103-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16998,10 +16998,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45117</v>
+        <v>46052</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17057,7 +17057,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 31715-2023</t>
+          <t>A 7546-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17071,10 +17071,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45117</v>
+        <v>46059</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>12.4</v>
+        <v>1.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17130,7 +17130,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 59517-2023</t>
+          <t>A 11584-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17144,10 +17144,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45254</v>
+        <v>46084</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17203,7 +17203,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30724-2023</t>
+          <t>A 12469-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17217,10 +17217,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45112</v>
+        <v>46090</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31907-2026</t>
+          <t>A 12503-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17290,10 +17290,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46231</v>
+        <v>46090</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17305,13 +17305,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17354,7 +17349,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 57443-2024</t>
+          <t>A 13120-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17368,10 +17363,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45629</v>
+        <v>46093</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17384,7 +17379,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17427,7 +17422,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 23330-2024</t>
+          <t>A 13121-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17437,14 +17432,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45453</v>
+        <v>46093</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17456,13 +17451,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17505,7 +17495,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 23907-2024</t>
+          <t>A 12879-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17515,14 +17505,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45455</v>
+        <v>46092</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17534,8 +17524,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17578,7 +17573,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21878-2025</t>
+          <t>A 24965-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17592,10 +17587,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45784</v>
+        <v>46174</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17608,7 +17603,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17651,7 +17646,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 38521-2026</t>
+          <t>A 26642-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17665,10 +17660,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46283</v>
+        <v>46184</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17681,7 +17676,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17724,7 +17719,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 43938-2024</t>
+          <t>A 27248-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17738,10 +17733,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45572</v>
+        <v>46188</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17754,7 +17749,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17797,7 +17792,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 38601-2026</t>
+          <t>A 27782-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17811,10 +17806,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46283</v>
+        <v>46191</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17827,7 +17822,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17870,7 +17865,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 47258-2025</t>
+          <t>A 30098-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17884,10 +17879,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45930</v>
+        <v>46206</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17900,7 +17895,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17943,7 +17938,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 39344-2026</t>
+          <t>A 36861-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17957,10 +17952,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46288</v>
+        <v>46272</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17973,7 +17968,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18016,7 +18011,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 39852-2026</t>
+          <t>A 31907-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18030,10 +18025,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46290</v>
+        <v>46231</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18045,8 +18040,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 39841-2026</t>
+          <t>A 38521-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18162,7 +18162,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 9086-2025</t>
+          <t>A 38601-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18176,10 +18176,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45713</v>
+        <v>46283</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 39896-2026</t>
+          <t>A 39344-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18249,10 +18249,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18308,7 +18308,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 28073-2024</t>
+          <t>A 47258-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18322,10 +18322,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45476</v>
+        <v>45930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18381,7 +18381,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 29794-2025</t>
+          <t>A 39852-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18395,10 +18395,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45825</v>
+        <v>46290</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18454,7 +18454,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 10918-2025</t>
+          <t>A 39841-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18468,10 +18468,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45722</v>
+        <v>46290</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18527,7 +18527,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 33852-2026</t>
+          <t>A 39896-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18541,10 +18541,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46251</v>
+        <v>46290</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 33853-2026</t>
+          <t>A 33852-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18617,7 +18617,7 @@
         <v>46251</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18673,7 +18673,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 9471-2025</t>
+          <t>A 33853-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18687,10 +18687,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45715</v>
+        <v>46251</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18763,7 +18763,7 @@
         <v>46120</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 35072-2026</t>
+          <t>A 35071-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18836,7 +18836,7 @@
         <v>46259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18892,7 +18892,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 12124-2024</t>
+          <t>A 35072-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18906,10 +18906,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45377</v>
+        <v>46259</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18921,13 +18921,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18970,7 +18965,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 35071-2026</t>
+          <t>A 12124-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18984,10 +18979,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46259</v>
+        <v>45377</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18999,8 +18994,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>45934</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>46154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>46246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45112</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45943</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45112</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45363</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>45117</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45112</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45112</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45112</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>46093</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>45112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45455</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>45112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>46128</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45703</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44764</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44502</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44530</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44754</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45763</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45117</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45117</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44818</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44726</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45197</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45377</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44882</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45308</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45112</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44958</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44914</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45288</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44775</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45624</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45359</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45090</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44882</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>45568</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>45254</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45112</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45112</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45117</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45310</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>45476</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>45448</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>44494</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45328</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>45587</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45218</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44946</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45248</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44966</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45288</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45897</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45373</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44537</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45471</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45629</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45303</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45112</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45453</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>45308</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45784</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45629</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45455</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>45358</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44628</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45216</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45611</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>45763</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>45763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45117</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45117</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45117</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45572</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45118</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45586</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45586</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44658</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44946</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>45180</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>45254</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44981</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45070</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45232</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45938</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45713</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45112</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45624</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45117</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45117</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44683</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44708</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45476</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>45701</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45825</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45180</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>45561</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45722</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45715</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45951</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45272</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45954</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45954</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45957</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45834</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>45838</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>45112</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>45836</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45604</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45254</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45117</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>45117</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45264</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45219</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45664</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45476</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45204</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>45709</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45872</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45982</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45041</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45982</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45071</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45621</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>46099</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>46100</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44900</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44893</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44900</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44524</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45112</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45112</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45993</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45993</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45993</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45993</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45992</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45994</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>46134</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>44881</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45696</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45308</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45721</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46021</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44868</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45534</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45537</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44915</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>46140</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45953</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46037</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45974</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45112</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45112</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45112</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>46140</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45803</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>46044</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>44882</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>46048</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>46048</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45624</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>44914</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>46141</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45276</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>46052</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>46052</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>46052</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>46052</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>46059</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46084</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>46090</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46090</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>46093</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46093</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>46092</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>46174</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>46184</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>46188</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>46191</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>46206</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>46272</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>46231</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>46283</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>46288</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>46290</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>46290</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>46290</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46251</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>46251</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>46120</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>46259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>46259</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45377</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45934</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>46154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>46246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45112</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45943</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45112</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>45117</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45363</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>45117</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45112</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45112</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45112</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>46093</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46184</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>45112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45455</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>45112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>45838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>46128</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45703</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45117</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44764</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44502</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44683</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44585</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44530</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44754</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45763</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45117</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45117</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44818</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44726</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>45197</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45377</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44882</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45308</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45112</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44958</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44914</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45288</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44775</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45624</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45359</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45090</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44882</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>45568</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>45254</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45112</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>45112</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45117</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45310</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>45476</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>45448</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>44494</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45328</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>45587</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45218</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44946</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45248</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44966</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45288</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44510</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45897</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45373</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44537</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45471</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45629</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45303</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45112</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45453</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>45308</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45784</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45629</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45455</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>45358</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44628</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45216</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45611</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>45763</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>45763</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45117</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45117</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45117</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45572</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45118</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45586</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45586</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44658</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44946</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>45180</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>45254</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44981</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45070</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45232</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45938</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45713</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45112</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45624</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45117</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45117</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44683</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44708</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45476</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>45701</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45825</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45180</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>45561</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45722</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45715</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45951</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45272</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45954</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45954</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45957</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45834</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>45838</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>45112</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>45836</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45604</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45254</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45117</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>45117</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45264</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45219</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45664</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45476</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45204</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>45709</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45872</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>45982</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45041</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45982</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45071</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45621</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>46099</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>46100</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44900</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44893</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44900</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44524</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45112</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45112</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45993</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45993</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45993</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45993</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45992</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45994</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>46134</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>44881</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45696</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45308</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45721</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46021</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44868</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45534</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45537</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44915</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>46140</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45953</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46037</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45974</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45112</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45112</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45112</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>46140</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45803</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>46044</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>44882</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>46048</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>46048</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45624</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>44914</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>46141</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45276</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>46052</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>46052</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>46052</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>46052</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>46059</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46084</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>46090</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46090</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>46093</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46093</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>46092</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>46174</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>46184</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>46188</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>46191</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>46206</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>46272</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>46231</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>46283</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>46288</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45930</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>46290</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>46290</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>46290</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46251</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>46251</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>46120</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>46259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>46259</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45377</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45934</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>46154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>46246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50084-2025</t>
+          <t>A 50011-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45943</v>
+        <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,45 +845,158 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="R4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Svartbent strandpipare
+Sexfläckig bastardsvärmare
+Grönsångare
+Strandskata
+Sädesärla</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 50084-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Spillkråka
@@ -892,116 +1005,225 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50084-2025 artfynd.xlsx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50084-2025 karta.png", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50084-2025 georefererad karta.tif", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50084-2025 FSC-klagomål.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50084-2025 FSC-klagomål mail.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50084-2025 tillsynsbegäran.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50084-2025 tillsynsbegäran mail.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50084-2025 prioriterade fågelarter.docx", "A 50084-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 30777-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Oxtungssvamp
+Vågbandad barkbock
+Tofsmes
+Svartvit flugsnappare
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 12131-2024</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>45377</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I7" t="n">
         <v>2.1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T7" t="n">
         <v>6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Talltita
@@ -1010,258 +1232,36 @@
 Orre</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 12131-2024 artfynd.xlsx", "A 12131-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 12131-2024 karta.png", "A 12131-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 12131-2024 georefererad karta.tif", "A 12131-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 12131-2024 FSC-klagomål.docx", "A 12131-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 12131-2024 FSC-klagomål mail.docx", "A 12131-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 12131-2024 tillsynsbegäran.docx", "A 12131-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 12131-2024 tillsynsbegäran mail.docx", "A 12131-2024")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 12131-2024 prioriterade fågelarter.docx", "A 12131-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 30777-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" t="n">
-        <v>8</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Oxtungssvamp
-Vågbandad barkbock
-Tofsmes
-Svartvit flugsnappare
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 50011-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45215</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Svartbent strandpipare
-Sexfläckig bastardsvärmare
-Grönsångare
-Strandskata
-Sädesärla</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
         <v/>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30671-2023</t>
+          <t>A 31728-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1544,169 +1544,169 @@
         <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Gammelgransskål
+Kattfotslav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31728-2023 artfynd.xlsx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31728-2023 karta.png", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31728-2023 georefererad karta.tif", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31728-2023 FSC-klagomål.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31728-2023 FSC-klagomål mail.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31728-2023 tillsynsbegäran.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31728-2023 tillsynsbegäran mail.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31728-2023 prioriterade fågelarter.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 30671-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>12</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>10</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Järnsparv
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30671-2023 artfynd.xlsx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30671-2023 karta.png", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30671-2023 georefererad karta.tif", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 30671-2023 karta knärot.png", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30671-2023 FSC-klagomål.docx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30671-2023 FSC-klagomål mail.docx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30671-2023 tillsynsbegäran.docx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30671-2023 tillsynsbegäran mail.docx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30671-2023 prioriterade fågelarter.docx", "A 30671-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31728-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Gammelgransskål
-Kattfotslav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31728-2023 artfynd.xlsx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31728-2023 karta.png", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31728-2023 georefererad karta.tif", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31728-2023 FSC-klagomål.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31728-2023 FSC-klagomål mail.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31728-2023 tillsynsbegäran.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31728-2023 tillsynsbegäran mail.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31728-2023 prioriterade fågelarter.docx", "A 31728-2023")</f>
         <v/>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 26670-2026</t>
+          <t>A 9930-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46184</v>
+        <v>45363</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>15.4</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1886,692 +1886,692 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Större träfjäril
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 9930-2024 artfynd.xlsx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 9930-2024 karta.png", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 9930-2024 georefererad karta.tif", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 9930-2024 FSC-klagomål.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 9930-2024 FSC-klagomål mail.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 9930-2024 tillsynsbegäran.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 9930-2024 tillsynsbegäran mail.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 9930-2024 prioriterade fågelarter.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 31714-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 13115-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Mattlummer
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 13115-2026 artfynd.xlsx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 13115-2026 karta.png", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 13115-2026 georefererad karta.tif", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 13115-2026 FSC-klagomål.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 13115-2026 FSC-klagomål mail.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 13115-2026 tillsynsbegäran.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 13115-2026 tillsynsbegäran mail.docx", "A 13115-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 60380-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 30666-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 30792-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 26670-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Tofsmes
 Grönsiska</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 26670-2026 artfynd.xlsx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 26670-2026 karta.png", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 26670-2026 georefererad karta.tif", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 26670-2026 FSC-klagomål.docx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 26670-2026 FSC-klagomål mail.docx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 26670-2026 tillsynsbegäran.docx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 26670-2026 tillsynsbegäran mail.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 30792-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 13115-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46093</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 13115-2026 artfynd.xlsx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 13115-2026 karta.png", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 13115-2026 georefererad karta.tif", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 13115-2026 FSC-klagomål.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 13115-2026 FSC-klagomål mail.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 13115-2026 tillsynsbegäran.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 13115-2026 tillsynsbegäran mail.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 60380-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 30666-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 9930-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45363</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Större träfjäril
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 9930-2024 artfynd.xlsx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 9930-2024 karta.png", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 9930-2024 georefererad karta.tif", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 9930-2024 FSC-klagomål.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 9930-2024 FSC-klagomål mail.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 9930-2024 tillsynsbegäran.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 9930-2024 tillsynsbegäran mail.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 9930-2024 prioriterade fågelarter.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 31714-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>6</v>
-      </c>
-      <c r="U19" t="n">
-        <v>6</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
         <v/>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30754-2023</t>
+          <t>A 35526-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45112</v>
+        <v>45147</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2754,46 +2754,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35526-2023 artfynd.xlsx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35526-2023 karta.png", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35526-2023 georefererad karta.tif", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35526-2023 FSC-klagomål.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35526-2023 FSC-klagomål mail.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35526-2023 tillsynsbegäran.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35526-2023 tillsynsbegäran mail.docx", "A 35526-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23906-2024</t>
+          <t>A 32503-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45455</v>
+        <v>45838</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2863,42 +2863,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7339-2025</t>
+          <t>A 30745-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45703</v>
+        <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2928,13 +2928,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2968,42 +2968,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30745-2023 artfynd.xlsx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30745-2023 karta.png", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30745-2023 georefererad karta.tif", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30745-2023 FSC-klagomål.docx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30745-2023 FSC-klagomål mail.docx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30745-2023 tillsynsbegäran.docx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30745-2023 tillsynsbegäran mail.docx", "A 30745-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32503-2025</t>
+          <t>A 7339-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45838</v>
+        <v>45703</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3073,42 +3073,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35526-2023</t>
+          <t>A 18822-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45147</v>
+        <v>46128</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3138,23 +3138,23 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3162,10 +3162,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3178,42 +3178,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35526-2023 artfynd.xlsx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35526-2023 karta.png", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35526-2023 georefererad karta.tif", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35526-2023 FSC-klagomål.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35526-2023 FSC-klagomål mail.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35526-2023 tillsynsbegäran.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35526-2023 tillsynsbegäran mail.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41586-2026</t>
+          <t>A 30653-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46302</v>
+        <v>45112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3242,13 +3242,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3284,46 +3279,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 41586-2026 artfynd.xlsx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 41586-2026 karta.png", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 41586-2026 georefererad karta.tif", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 41586-2026 FSC-klagomål.docx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 41586-2026 FSC-klagomål mail.docx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 41586-2026 tillsynsbegäran.docx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 41586-2026 tillsynsbegäran mail.docx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18822-2026</t>
+          <t>A 30662-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3337,10 +3336,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46128</v>
+        <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3353,10 +3352,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3368,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3377,10 +3376,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3389,46 +3388,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30653-2023</t>
+          <t>A 30754-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3445,7 +3444,7 @@
         <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3458,13 +3457,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3498,46 +3497,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30745-2023</t>
+          <t>A 31742-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3551,10 +3546,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3567,13 +3562,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3600,42 +3595,46 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30745-2023 artfynd.xlsx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30745-2023 karta.png", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30745-2023 georefererad karta.tif", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30745-2023 FSC-klagomål.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30745-2023 FSC-klagomål mail.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30745-2023 tillsynsbegäran.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30745-2023 tillsynsbegäran mail.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
         <v/>
       </c>
     </row>
@@ -3659,7 +3658,7 @@
         <v>45146</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3751,7 +3750,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30662-2023</t>
+          <t>A 23906-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3765,10 +3764,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45112</v>
+        <v>45455</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3781,10 +3780,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3821,42 +3820,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31742-2023</t>
+          <t>A 41586-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,10 +3869,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45117</v>
+        <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3885,8 +3884,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3919,46 +3923,42 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 41586-2026 artfynd.xlsx", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 41586-2026 karta.png", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 41586-2026 georefererad karta.tif", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 41586-2026 FSC-klagomål.docx", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 41586-2026 FSC-klagomål mail.docx", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 41586-2026 tillsynsbegäran.docx", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 41586-2026 tillsynsbegäran mail.docx", "A 41586-2026")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>44637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44764</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44502</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44683</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44585</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47522-2024</t>
+          <t>A 12160-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45587</v>
+        <v>45377</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4729,13 +4729,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4778,7 +4773,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30633-2023</t>
+          <t>A 50057-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4792,10 +4787,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45112</v>
+        <v>45215</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4808,7 +4803,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4851,7 +4846,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 65143-2023</t>
+          <t>A 29658-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4865,10 +4860,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45288</v>
+        <v>44754</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4881,7 +4876,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4924,7 +4919,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 25928-2023</t>
+          <t>A 60792-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4938,10 +4933,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45090</v>
+        <v>44914</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4954,7 +4949,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4997,7 +4992,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40774-2025</t>
+          <t>A 46511-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45897</v>
+        <v>45197</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5027,7 +5022,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5070,7 +5065,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 31889-2023</t>
+          <t>A 9401-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5084,10 +5079,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45118</v>
+        <v>45359</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5100,7 +5095,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5143,7 +5138,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18337-2023</t>
+          <t>A 64005-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45041</v>
+        <v>46021</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5173,7 +5168,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5216,7 +5211,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30772-2023</t>
+          <t>A 54287-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5230,10 +5225,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45112</v>
+        <v>44882</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5246,7 +5241,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5289,7 +5284,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4782-2024</t>
+          <t>A 30769-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5303,10 +5298,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45328</v>
+        <v>45112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5319,7 +5314,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5362,7 +5357,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11021-2022</t>
+          <t>A 54659-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5376,10 +5371,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44628</v>
+        <v>44883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5392,7 +5387,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5435,7 +5430,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11239-2023</t>
+          <t>A 30794-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5449,10 +5444,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44992</v>
+        <v>45112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5465,7 +5460,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5508,7 +5503,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24965-2026</t>
+          <t>A 31718-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5522,10 +5517,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46174</v>
+        <v>45117</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5538,7 +5533,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5581,7 +5576,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30769-2023</t>
+          <t>A 28040-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5595,10 +5590,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45112</v>
+        <v>45476</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5611,7 +5606,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5654,7 +5649,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31717-2023</t>
+          <t>A 22834-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5668,10 +5663,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45117</v>
+        <v>45448</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5684,7 +5679,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5727,7 +5722,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31719-2023</t>
+          <t>A 4782-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5741,10 +5736,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45117</v>
+        <v>45328</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5757,7 +5752,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5800,7 +5795,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30794-2023</t>
+          <t>A 47522-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5814,10 +5809,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45112</v>
+        <v>45587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5829,8 +5824,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5873,7 +5873,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 51229-2022</t>
+          <t>A 65143-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44868</v>
+        <v>45288</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31745-2023</t>
+          <t>A 3237-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45117</v>
+        <v>44946</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56335-2024</t>
+          <t>A 40774-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45624</v>
+        <v>45897</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>6.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 30801-2023</t>
+          <t>A 11605-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6106,10 +6106,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45112</v>
+        <v>45373</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6165,7 +6165,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47279-2025</t>
+          <t>A 70708-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45930</v>
+        <v>44537</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 70708-2021</t>
+          <t>A 9086-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44537</v>
+        <v>45713</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31712-2023</t>
+          <t>A 1395-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45117</v>
+        <v>45303</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31715-2023</t>
+          <t>A 28073-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45117</v>
+        <v>45476</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>12.4</v>
+        <v>7.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26642-2026</t>
+          <t>A 30633-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46184</v>
+        <v>45112</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48212-2025</t>
+          <t>A 23330-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6540,14 +6540,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45933</v>
+        <v>45453</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6559,8 +6559,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6603,7 +6608,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49269-2025</t>
+          <t>A 29794-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6617,10 +6622,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45938</v>
+        <v>45825</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6633,7 +6638,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6676,7 +6681,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 27248-2026</t>
+          <t>A 10918-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6690,10 +6695,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46188</v>
+        <v>45722</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6706,7 +6711,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6749,7 +6754,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59517-2023</t>
+          <t>A 9471-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6763,10 +6768,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45254</v>
+        <v>45715</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6779,7 +6784,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6822,7 +6827,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30724-2023</t>
+          <t>A 57036-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6836,10 +6841,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45112</v>
+        <v>45629</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6852,7 +6857,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6895,7 +6900,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51613-2025</t>
+          <t>A 9159-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6909,10 +6914,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45951</v>
+        <v>45358</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6925,7 +6930,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6968,7 +6973,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 27782-2026</t>
+          <t>A 31804-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6982,10 +6987,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46191</v>
+        <v>45834</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +7003,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7041,7 +7046,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 52513-2025</t>
+          <t>A 11021-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7055,10 +7060,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45954</v>
+        <v>44628</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7076,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7114,7 +7119,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 52511-2025</t>
+          <t>A 47279-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7128,10 +7133,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45954</v>
+        <v>45930</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7149,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7187,7 +7192,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6745-2023</t>
+          <t>A 50302-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7197,14 +7202,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44966</v>
+        <v>45216</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7217,7 +7222,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7260,7 +7265,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52939-2025</t>
+          <t>A 32506-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7274,10 +7279,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45957</v>
+        <v>45838</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7290,7 +7295,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7333,7 +7338,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 57443-2024</t>
+          <t>A 32320-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7347,10 +7352,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45629</v>
+        <v>45836</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7363,7 +7368,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>11.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7406,7 +7411,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23330-2024</t>
+          <t>A 53055-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7416,14 +7421,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45453</v>
+        <v>45611</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7435,13 +7440,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23907-2024</t>
+          <t>A 2497-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45455</v>
+        <v>46037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7557,7 +7557,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21878-2025</t>
+          <t>A 48212-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45784</v>
+        <v>45933</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30098-2026</t>
+          <t>A 31889-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46206</v>
+        <v>45118</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 43938-2024</t>
+          <t>A 49269-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45572</v>
+        <v>45938</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18615-2025</t>
+          <t>A 4119-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45763</v>
+        <v>46044</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7805,8 +7805,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7849,7 +7854,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58137-2025</t>
+          <t>A 4587-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7863,10 +7868,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45982</v>
+        <v>46048</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7879,7 +7884,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7922,7 +7927,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58139-2025</t>
+          <t>A 4588-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7936,10 +7941,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45982</v>
+        <v>46048</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7952,7 +7957,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7995,7 +8000,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60089-2025</t>
+          <t>A 15112-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8009,10 +8014,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45993</v>
+        <v>44658</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8025,7 +8030,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8068,7 +8073,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60093-2025</t>
+          <t>A 3238-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8082,10 +8087,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45993</v>
+        <v>44946</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8098,7 +8103,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8141,7 +8146,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60091-2025</t>
+          <t>A 435-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8155,10 +8160,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45993</v>
+        <v>45664</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8171,7 +8176,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8214,7 +8219,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60092-2025</t>
+          <t>A 59472-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45993</v>
+        <v>45254</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8244,7 +8249,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8287,7 +8292,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59871-2025</t>
+          <t>A 51613-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8301,10 +8306,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45992</v>
+        <v>45951</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8317,7 +8322,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8360,7 +8365,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59872-2025</t>
+          <t>A 28158-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8374,10 +8379,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45992</v>
+        <v>45476</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8390,7 +8395,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8433,7 +8438,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 60181-2025</t>
+          <t>A 52511-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8447,10 +8452,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45994</v>
+        <v>45954</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8463,7 +8468,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8506,7 +8511,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60946-2025</t>
+          <t>A 52513-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8520,10 +8525,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45999</v>
+        <v>45954</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8536,7 +8541,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8579,7 +8584,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 36861-2026</t>
+          <t>A 52939-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8593,10 +8598,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46272</v>
+        <v>45957</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8609,7 +8614,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8652,7 +8657,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9086-2025</t>
+          <t>A 36650-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8666,10 +8671,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45713</v>
+        <v>45872</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8725,7 +8730,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 31907-2026</t>
+          <t>A 9530-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46231</v>
+        <v>44981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8754,13 +8759,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8803,7 +8803,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28073-2024</t>
+          <t>A 22443-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8817,10 +8817,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45476</v>
+        <v>45070</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8876,7 +8876,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 29794-2025</t>
+          <t>A 54295-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45825</v>
+        <v>45232</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8949,7 +8949,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10610-2025</t>
+          <t>A 31546-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8959,14 +8959,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45721</v>
+        <v>44775</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9022,7 +9022,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10918-2025</t>
+          <t>A 6071-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9036,10 +9036,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45722</v>
+        <v>46052</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 64005-2025</t>
+          <t>A 6074-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46021</v>
+        <v>46052</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9168,7 +9168,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9471-2025</t>
+          <t>A 30801-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45715</v>
+        <v>45112</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9241,7 +9241,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 31804-2025</t>
+          <t>A 56331-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45834</v>
+        <v>45624</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9314,7 +9314,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 2497-2026</t>
+          <t>A 25928-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46037</v>
+        <v>45090</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9387,7 +9387,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32320-2025</t>
+          <t>A 6104-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9401,10 +9401,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45836</v>
+        <v>46052</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9460,7 +9460,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 32506-2025</t>
+          <t>A 6103-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45838</v>
+        <v>46052</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 38521-2026</t>
+          <t>A 58139-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46283</v>
+        <v>45982</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9606,7 +9606,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38601-2026</t>
+          <t>A 58137-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9620,10 +9620,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46283</v>
+        <v>45982</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9679,7 +9679,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 4119-2026</t>
+          <t>A 7546-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9693,10 +9693,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46044</v>
+        <v>46059</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9708,13 +9708,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9757,7 +9752,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 4587-2026</t>
+          <t>A 59871-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9771,10 +9766,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46048</v>
+        <v>45992</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9787,7 +9782,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9830,7 +9825,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4588-2026</t>
+          <t>A 60091-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9844,10 +9839,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46048</v>
+        <v>45993</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9860,7 +9855,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9903,7 +9898,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 47258-2025</t>
+          <t>A 60092-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9917,10 +9912,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45930</v>
+        <v>45993</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9933,7 +9928,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9976,7 +9971,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6071-2026</t>
+          <t>A 60089-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9990,10 +9985,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46052</v>
+        <v>45993</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10006,7 +10001,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10049,7 +10044,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 6074-2026</t>
+          <t>A 60093-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10063,10 +10058,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46052</v>
+        <v>45993</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10079,7 +10074,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10122,7 +10117,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6104-2026</t>
+          <t>A 59872-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10136,10 +10131,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46052</v>
+        <v>45992</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10152,7 +10147,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10195,7 +10190,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 6103-2026</t>
+          <t>A 60181-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10209,10 +10204,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46052</v>
+        <v>45994</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10225,7 +10220,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10268,7 +10263,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 39344-2026</t>
+          <t>A 60946-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10282,10 +10277,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46288</v>
+        <v>45999</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10298,7 +10293,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10341,7 +10336,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28158-2024</t>
+          <t>A 30637-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10355,10 +10350,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45476</v>
+        <v>45112</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10371,7 +10366,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10414,7 +10409,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 435-2025</t>
+          <t>A 51564-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10428,10 +10423,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45664</v>
+        <v>45604</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10444,7 +10439,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10487,7 +10482,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 7546-2026</t>
+          <t>A 10610-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10501,10 +10496,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46059</v>
+        <v>45721</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10517,7 +10512,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10560,7 +10555,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 36650-2025</t>
+          <t>A 11584-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10574,10 +10569,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45872</v>
+        <v>46084</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10590,7 +10585,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10633,7 +10628,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 39852-2026</t>
+          <t>A 31746-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10647,10 +10642,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46290</v>
+        <v>45117</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10663,7 +10658,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10706,7 +10701,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 39841-2026</t>
+          <t>A 12469-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10720,10 +10715,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46290</v>
+        <v>46090</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10736,7 +10731,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10779,7 +10774,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 39896-2026</t>
+          <t>A 31711-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10793,10 +10788,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46290</v>
+        <v>45117</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10809,7 +10804,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10852,7 +10847,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11584-2026</t>
+          <t>A 31727-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10866,10 +10861,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46084</v>
+        <v>45117</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10882,7 +10877,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10925,7 +10920,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31546-2022</t>
+          <t>A 12503-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10935,14 +10930,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44775</v>
+        <v>46090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10955,7 +10950,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10998,7 +10993,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33852-2026</t>
+          <t>A 13120-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46251</v>
+        <v>46093</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11028,7 +11023,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11071,7 +11066,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33853-2026</t>
+          <t>A 13121-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11085,10 +11080,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46251</v>
+        <v>46093</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11101,7 +11096,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11144,7 +11139,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 12503-2026</t>
+          <t>A 12879-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11154,14 +11149,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11173,8 +11168,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11217,7 +11217,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 12469-2026</t>
+          <t>A 51314-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11227,14 +11227,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46090</v>
+        <v>45219</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11290,7 +11290,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 12879-2026</t>
+          <t>A 14111-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11300,14 +11300,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11319,13 +11319,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11368,7 +11363,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 13120-2026</t>
+          <t>A 47980-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11382,10 +11377,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46093</v>
+        <v>45204</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11398,7 +11393,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11441,7 +11436,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 13121-2026</t>
+          <t>A 14545-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11451,14 +11446,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11471,7 +11466,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11514,7 +11509,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3237-2023</t>
+          <t>A 58011-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11528,10 +11523,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44946</v>
+        <v>44900</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11544,7 +11539,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11587,7 +11582,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 58011-2022</t>
+          <t>A 8570-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11601,10 +11596,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44900</v>
+        <v>45709</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11617,7 +11612,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11677,7 +11672,7 @@
         <v>44893</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11733,7 +11728,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14111-2026</t>
+          <t>A 58010-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11747,10 +11742,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46099</v>
+        <v>44900</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11763,7 +11758,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11806,7 +11801,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31724-2023</t>
+          <t>A 18337-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11820,10 +11815,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45117</v>
+        <v>45041</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11879,7 +11874,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 31726-2023</t>
+          <t>A 22541-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11893,10 +11888,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45117</v>
+        <v>45071</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11909,7 +11904,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11952,7 +11947,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 58010-2022</t>
+          <t>A 67455-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11966,10 +11961,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44900</v>
+        <v>44524</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11982,7 +11977,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12025,7 +12020,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14545-2026</t>
+          <t>A 30628-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12035,14 +12030,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46100</v>
+        <v>45112</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12055,7 +12050,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12098,7 +12093,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 61671-2022</t>
+          <t>A 30643-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12112,10 +12107,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44917</v>
+        <v>45112</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12128,7 +12123,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12171,7 +12166,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 17434-2026</t>
+          <t>A 18615-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12181,14 +12176,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46120</v>
+        <v>45763</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12201,7 +12196,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12244,7 +12239,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 35072-2026</t>
+          <t>A 31717-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12258,10 +12253,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46259</v>
+        <v>45117</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12274,7 +12269,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12317,7 +12312,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56334-2024</t>
+          <t>A 31719-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12331,10 +12326,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45624</v>
+        <v>45117</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12347,7 +12342,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12390,7 +12385,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 12124-2024</t>
+          <t>A 30800-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12404,10 +12399,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45377</v>
+        <v>45112</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12419,13 +12414,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12468,7 +12458,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 35071-2026</t>
+          <t>A 24368-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12482,10 +12472,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46259</v>
+        <v>44726</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12498,7 +12488,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12541,7 +12531,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 19644-2026</t>
+          <t>A 30650-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12555,10 +12545,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46134</v>
+        <v>45112</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12571,7 +12561,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12614,7 +12604,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 61318-2023</t>
+          <t>A 19644-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12628,10 +12618,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45264</v>
+        <v>46134</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12644,7 +12634,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12687,7 +12677,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 42483-2023</t>
+          <t>A 6064-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12701,10 +12691,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45180</v>
+        <v>45696</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12760,7 +12750,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6064-2025</t>
+          <t>A 54289-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12774,10 +12764,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45696</v>
+        <v>44882</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12790,7 +12780,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12833,7 +12823,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 52371-2025</t>
+          <t>A 1922-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12847,10 +12837,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45953</v>
+        <v>45308</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12863,7 +12853,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12906,7 +12896,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 56305-2025</t>
+          <t>A 5072-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12920,10 +12910,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45974</v>
+        <v>44958</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12936,7 +12926,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12979,7 +12969,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 47265-2024</t>
+          <t>A 65118-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12993,10 +12983,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45586</v>
+        <v>45288</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13009,7 +12999,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13052,7 +13042,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36131-2024</t>
+          <t>A 56335-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13066,10 +13056,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45534</v>
+        <v>45624</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13082,7 +13072,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13125,7 +13115,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 36532-2024</t>
+          <t>A 36131-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13139,10 +13129,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45537</v>
+        <v>45534</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13155,7 +13145,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13198,7 +13188,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 8570-2025</t>
+          <t>A 43398-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13212,10 +13202,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45709</v>
+        <v>45568</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13228,7 +13218,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13271,7 +13261,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 25694-2025</t>
+          <t>A 36532-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13285,10 +13275,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45803</v>
+        <v>45537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13301,7 +13291,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13344,7 +13334,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 5072-2023</t>
+          <t>A 59517-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13358,10 +13348,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44958</v>
+        <v>45254</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13374,7 +13364,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13417,7 +13407,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 17925-2022</t>
+          <t>A 20600-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13431,10 +13421,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44683</v>
+        <v>46140</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13447,7 +13437,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13490,7 +13480,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 54295-2023</t>
+          <t>A 59816-2021</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13504,10 +13494,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45232</v>
+        <v>44494</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13520,7 +13510,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13563,7 +13553,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 47980-2023</t>
+          <t>A 52371-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13577,10 +13567,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45204</v>
+        <v>45953</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13593,7 +13583,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13636,7 +13626,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 9401-2024</t>
+          <t>A 6745-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13646,14 +13636,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45359</v>
+        <v>44966</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13666,7 +13656,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13709,7 +13699,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 20598-2026</t>
+          <t>A 56305-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13723,10 +13713,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46140</v>
+        <v>45974</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13739,7 +13729,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13782,7 +13772,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 20600-2026</t>
+          <t>A 20598-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13799,7 +13789,7 @@
         <v>46140</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13812,7 +13802,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13855,7 +13845,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20782-2026</t>
+          <t>A 25694-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13869,10 +13859,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46141</v>
+        <v>45803</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13885,7 +13875,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13928,7 +13918,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 9527-2023</t>
+          <t>A 1921-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13942,10 +13932,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44981</v>
+        <v>45308</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13958,7 +13948,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14001,7 +13991,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 50981-2023</t>
+          <t>A 42250-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14015,10 +14005,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45218</v>
+        <v>45180</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14030,13 +14020,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14079,7 +14064,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 50302-2023</t>
+          <t>A 20782-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14093,10 +14078,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45216</v>
+        <v>46141</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14109,7 +14094,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14152,7 +14137,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 59472-2023</t>
+          <t>A 11239-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14166,10 +14151,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45254</v>
+        <v>44992</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14182,7 +14167,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14225,7 +14210,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 9530-2023</t>
+          <t>A 18613-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14239,10 +14224,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44981</v>
+        <v>45763</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14255,7 +14240,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14298,7 +14283,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 30628-2023</t>
+          <t>A 18614-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14312,10 +14297,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45112</v>
+        <v>45763</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14328,7 +14313,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14371,7 +14356,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 30643-2023</t>
+          <t>A 31712-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14385,10 +14370,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14401,7 +14386,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14444,7 +14429,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 22834-2024</t>
+          <t>A 31715-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14458,10 +14443,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45448</v>
+        <v>45117</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14474,7 +14459,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>12.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14517,7 +14502,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 41910-2024</t>
+          <t>A 31745-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14531,10 +14516,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45561</v>
+        <v>45117</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14547,7 +14532,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14590,7 +14575,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 67455-2021</t>
+          <t>A 47264-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14604,10 +14589,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44524</v>
+        <v>45586</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14620,7 +14605,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14663,7 +14648,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 58093-2023</t>
+          <t>A 47265-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14677,10 +14662,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45248</v>
+        <v>45586</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14693,7 +14678,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14736,7 +14721,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 54144-2022</t>
+          <t>A 42483-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14750,10 +14735,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44881</v>
+        <v>45180</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14766,7 +14751,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14809,7 +14794,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 50057-2023</t>
+          <t>A 6653-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14823,10 +14808,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45215</v>
+        <v>44602</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14839,7 +14824,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14882,7 +14867,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 46511-2023</t>
+          <t>A 31724-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14896,10 +14881,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45197</v>
+        <v>45117</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14912,7 +14897,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14955,7 +14940,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 6653-2022</t>
+          <t>A 31726-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14969,10 +14954,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44602</v>
+        <v>45117</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14985,7 +14970,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15028,7 +15013,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 64207-2021</t>
+          <t>A 17925-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15042,10 +15027,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44510</v>
+        <v>44683</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15058,7 +15043,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15101,7 +15086,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 2006-2024</t>
+          <t>A 21751-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15115,10 +15100,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45308</v>
+        <v>44708</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15131,7 +15116,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15174,7 +15159,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 24368-2022</t>
+          <t>A 7046-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15188,10 +15173,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44726</v>
+        <v>45701</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15204,7 +15189,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15247,7 +15232,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 27103-2024</t>
+          <t>A 42256-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15261,10 +15246,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45471</v>
+        <v>45180</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15277,7 +15262,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15320,7 +15305,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 55159-2024</t>
+          <t>A 41910-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15334,10 +15319,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45621</v>
+        <v>45561</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15350,7 +15335,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15393,7 +15378,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 38586-2023</t>
+          <t>A 62986-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15407,10 +15392,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45162</v>
+        <v>45272</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15423,7 +15408,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15466,7 +15451,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 9159-2024</t>
+          <t>A 24965-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15480,10 +15465,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45358</v>
+        <v>46174</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15496,7 +15481,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15539,7 +15524,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 31746-2023</t>
+          <t>A 59613-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15553,10 +15538,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45117</v>
+        <v>45254</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15612,7 +15597,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 63725-2023</t>
+          <t>A 26642-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15626,10 +15611,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45276</v>
+        <v>46184</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15642,7 +15627,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15685,7 +15670,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 59613-2023</t>
+          <t>A 27248-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15699,10 +15684,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45254</v>
+        <v>46188</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15715,7 +15700,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15758,7 +15743,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 62986-2023</t>
+          <t>A 61318-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15772,10 +15757,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45272</v>
+        <v>45264</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15788,7 +15773,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15831,7 +15816,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 59816-2021</t>
+          <t>A 27782-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15845,10 +15830,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44494</v>
+        <v>46191</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15861,7 +15846,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15904,7 +15889,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 30650-2023</t>
+          <t>A 55159-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15918,10 +15903,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45112</v>
+        <v>45621</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15934,7 +15919,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15977,7 +15962,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 30637-2023</t>
+          <t>A 30098-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15991,10 +15976,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45112</v>
+        <v>46206</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16007,7 +15992,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16050,7 +16035,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 65118-2023</t>
+          <t>A 54144-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16064,10 +16049,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45288</v>
+        <v>44881</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16080,7 +16065,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16123,7 +16108,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 18613-2025</t>
+          <t>A 2006-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16137,10 +16122,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45763</v>
+        <v>45308</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16153,7 +16138,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16196,7 +16181,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 18614-2025</t>
+          <t>A 61671-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16210,10 +16195,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45763</v>
+        <v>44917</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16226,7 +16211,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>9.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16269,7 +16254,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 54289-2022</t>
+          <t>A 51229-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16283,10 +16268,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44882</v>
+        <v>44868</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16299,7 +16284,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16342,7 +16327,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 42250-2023</t>
+          <t>A 36861-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16356,10 +16341,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45180</v>
+        <v>46272</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16372,7 +16357,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16415,7 +16400,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 42256-2023</t>
+          <t>A 61334-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16429,10 +16414,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45180</v>
+        <v>44915</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16445,7 +16430,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16488,7 +16473,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 1921-2024</t>
+          <t>A 31907-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16502,10 +16487,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45308</v>
+        <v>46231</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16517,8 +16502,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16561,7 +16551,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31711-2023</t>
+          <t>A 30793-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16575,10 +16565,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16591,7 +16581,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16634,7 +16624,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31727-2023</t>
+          <t>A 30795-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16648,10 +16638,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16664,7 +16654,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16707,7 +16697,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 11605-2024</t>
+          <t>A 30724-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16721,10 +16711,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45373</v>
+        <v>45112</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16737,7 +16727,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16780,7 +16770,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 53055-2024</t>
+          <t>A 54311-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16794,10 +16784,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45611</v>
+        <v>44882</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16810,7 +16800,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16853,7 +16843,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 29658-2022</t>
+          <t>A 56334-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16867,10 +16857,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44754</v>
+        <v>45624</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16883,7 +16873,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16926,7 +16916,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 57036-2024</t>
+          <t>A 61026-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16940,10 +16930,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45629</v>
+        <v>44914</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16956,7 +16946,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16999,7 +16989,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 54287-2022</t>
+          <t>A 63725-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17013,10 +17003,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44882</v>
+        <v>45276</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17029,7 +17019,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17072,7 +17062,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 15112-2022</t>
+          <t>A 9527-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17086,10 +17076,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44658</v>
+        <v>44981</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17102,7 +17092,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17145,7 +17135,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 1922-2024</t>
+          <t>A 30760-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17159,10 +17149,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45308</v>
+        <v>45112</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17175,7 +17165,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17218,7 +17208,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 61334-2022</t>
+          <t>A 30762-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17232,10 +17222,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44915</v>
+        <v>45112</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17248,7 +17238,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17291,7 +17281,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 51564-2024</t>
+          <t>A 38586-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17305,10 +17295,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45604</v>
+        <v>45162</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17321,7 +17311,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17364,7 +17354,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 7046-2025</t>
+          <t>A 30772-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17378,10 +17368,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45701</v>
+        <v>45112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17394,7 +17384,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17437,7 +17427,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 30760-2023</t>
+          <t>A 38521-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17451,10 +17441,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45112</v>
+        <v>46283</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17467,7 +17457,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17510,7 +17500,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 30762-2023</t>
+          <t>A 38601-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17524,10 +17514,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45112</v>
+        <v>46283</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17540,7 +17530,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17583,7 +17573,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 56331-2024</t>
+          <t>A 39344-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17597,10 +17587,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45624</v>
+        <v>46288</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17613,7 +17603,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17656,7 +17646,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 51314-2023</t>
+          <t>A 47258-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17666,14 +17656,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45219</v>
+        <v>45930</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17686,7 +17676,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17729,7 +17719,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 3238-2023</t>
+          <t>A 39852-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17743,10 +17733,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44946</v>
+        <v>46290</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17759,7 +17749,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17802,7 +17792,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 12160-2024</t>
+          <t>A 39841-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17816,10 +17806,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45377</v>
+        <v>46290</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17832,7 +17822,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17875,7 +17865,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 54659-2022</t>
+          <t>A 39896-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17889,10 +17879,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44883</v>
+        <v>46290</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17905,7 +17895,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17948,7 +17938,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 31718-2023</t>
+          <t>A 2398-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17962,10 +17952,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45117</v>
+        <v>45310</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17978,7 +17968,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18021,7 +18011,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 43398-2024</t>
+          <t>A 50981-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18035,10 +18025,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45568</v>
+        <v>45218</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18050,8 +18040,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18094,7 +18089,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 54311-2022</t>
+          <t>A 58093-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18108,10 +18103,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44882</v>
+        <v>45248</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18124,7 +18119,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18167,7 +18162,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 22443-2023</t>
+          <t>A 64207-2021</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18181,10 +18176,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45070</v>
+        <v>44510</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18197,7 +18192,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18240,7 +18235,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 60792-2022</t>
+          <t>A 27103-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18254,10 +18249,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44914</v>
+        <v>45471</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18270,7 +18265,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18313,7 +18308,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 61026-2022</t>
+          <t>A 57443-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18327,10 +18322,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44914</v>
+        <v>45629</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18343,7 +18338,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18386,7 +18381,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 47264-2024</t>
+          <t>A 33852-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18400,10 +18395,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45586</v>
+        <v>46251</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18416,7 +18411,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18459,7 +18454,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 22541-2023</t>
+          <t>A 33853-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18473,10 +18468,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45071</v>
+        <v>46251</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18489,7 +18484,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18532,7 +18527,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 21751-2022</t>
+          <t>A 21878-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18546,10 +18541,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44708</v>
+        <v>45784</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18562,7 +18557,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18605,7 +18600,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 1395-2024</t>
+          <t>A 23907-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18619,10 +18614,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45303</v>
+        <v>45455</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18635,7 +18630,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18678,7 +18673,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 2398-2024</t>
+          <t>A 43938-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18692,10 +18687,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45310</v>
+        <v>45572</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18708,7 +18703,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18751,7 +18746,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 30793-2023</t>
+          <t>A 17434-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18761,14 +18756,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45112</v>
+        <v>46120</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18781,7 +18776,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18824,7 +18819,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 30795-2023</t>
+          <t>A 35071-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18838,10 +18833,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45112</v>
+        <v>46259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18854,7 +18849,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18897,7 +18892,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 30800-2023</t>
+          <t>A 35072-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18911,10 +18906,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45112</v>
+        <v>46259</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18927,7 +18922,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18970,7 +18965,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 28040-2024</t>
+          <t>A 12124-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18984,10 +18979,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45476</v>
+        <v>45377</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18999,8 +18994,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>45934</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>46154</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>46246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 50084-2025</t>
+          <t>A 50011-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45943</v>
+        <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,45 +845,267 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="R4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Svartbent strandpipare
+Sexfläckig bastardsvärmare
+Grönsångare
+Strandskata
+Sädesärla</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 30777-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Oxtungssvamp
+Vågbandad barkbock
+Tofsmes
+Svartvit flugsnappare
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 50084-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Spillkråka
@@ -892,258 +1114,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50084-2025 artfynd.xlsx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50084-2025 karta.png", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50084-2025 georefererad karta.tif", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50084-2025 FSC-klagomål.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50084-2025 FSC-klagomål mail.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50084-2025 tillsynsbegäran.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50084-2025 tillsynsbegäran mail.docx", "A 50084-2025")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50084-2025 prioriterade fågelarter.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 30777-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U5" t="n">
-        <v>8</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Oxtungssvamp
-Vågbandad barkbock
-Tofsmes
-Svartvit flugsnappare
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 50011-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45215</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Svartbent strandpipare
-Sexfläckig bastardsvärmare
-Grönsångare
-Strandskata
-Sädesärla</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
         <v/>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31728-2023</t>
+          <t>A 30785-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45117</v>
+        <v>45112</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1525,17 +1525,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1558,262 +1558,262 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30785-2023 artfynd.xlsx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30785-2023 karta.png", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30785-2023 georefererad karta.tif", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30785-2023 FSC-klagomål.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30785-2023 FSC-klagomål mail.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30785-2023 tillsynsbegäran.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30785-2023 tillsynsbegäran mail.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31728-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Gammelgransskål
 Kattfotslav
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31728-2023 artfynd.xlsx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31728-2023 karta.png", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31728-2023 georefererad karta.tif", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31728-2023 FSC-klagomål.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31728-2023 FSC-klagomål mail.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31728-2023 tillsynsbegäran.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31728-2023 tillsynsbegäran mail.docx", "A 31728-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31728-2023 prioriterade fågelarter.docx", "A 31728-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 30655-2023</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>45112</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>2.9</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trädporella
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30655-2023 artfynd.xlsx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30655-2023 karta.png", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30655-2023 georefererad karta.tif", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30655-2023 FSC-klagomål.docx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30655-2023 FSC-klagomål mail.docx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30655-2023 tillsynsbegäran.docx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30655-2023 tillsynsbegäran mail.docx", "A 30655-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 30785-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30785-2023 artfynd.xlsx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30785-2023 karta.png", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30785-2023 georefererad karta.tif", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30785-2023 FSC-klagomål.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30785-2023 FSC-klagomål mail.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30785-2023 tillsynsbegäran.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30785-2023 tillsynsbegäran mail.docx", "A 30785-2023")</f>
         <v/>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
         <v>45363</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 13115-2026</t>
+          <t>A 31714-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46093</v>
+        <v>45117</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>2</v>
@@ -1993,702 +1993,702 @@
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 30666-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30792-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 60380-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 26670-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Tofsmes
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 26670-2026 artfynd.xlsx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 26670-2026 karta.png", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 26670-2026 georefererad karta.tif", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 26670-2026 FSC-klagomål.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 26670-2026 FSC-klagomål mail.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 26670-2026 tillsynsbegäran.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 26670-2026 tillsynsbegäran mail.docx", "A 26670-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 30763-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30763-2023 artfynd.xlsx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30763-2023 karta.png", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30763-2023 georefererad karta.tif", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30763-2023 FSC-klagomål.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30763-2023 FSC-klagomål mail.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30763-2023 tillsynsbegäran.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30763-2023 tillsynsbegäran mail.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30763-2023 prioriterade fågelarter.docx", "A 30763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 13115-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 13115-2026 artfynd.xlsx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 13115-2026 karta.png", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 13115-2026 georefererad karta.tif", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 13115-2026 FSC-klagomål.docx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 13115-2026 FSC-klagomål mail.docx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 13115-2026 tillsynsbegäran.docx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 13115-2026 tillsynsbegäran mail.docx", "A 13115-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 30666-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 60380-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26670-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46184</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tofsmes
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 26670-2026 artfynd.xlsx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 26670-2026 karta.png", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 26670-2026 georefererad karta.tif", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 26670-2026 FSC-klagomål.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 26670-2026 FSC-klagomål mail.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 26670-2026 tillsynsbegäran.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 26670-2026 tillsynsbegäran mail.docx", "A 26670-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 31714-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 30763-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30763-2023 artfynd.xlsx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30763-2023 karta.png", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30763-2023 georefererad karta.tif", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30763-2023 FSC-klagomål.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30763-2023 FSC-klagomål mail.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30763-2023 tillsynsbegäran.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30763-2023 tillsynsbegäran mail.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30763-2023 prioriterade fågelarter.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 30792-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30754-2023</t>
+          <t>A 32503-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45112</v>
+        <v>45838</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2758,42 +2758,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32503-2025</t>
+          <t>A 35526-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45838</v>
+        <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2859,46 +2859,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 32503-2025 artfynd.xlsx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35526-2023 artfynd.xlsx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 32503-2025 karta.png", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35526-2023 karta.png", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 32503-2025 georefererad karta.tif", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35526-2023 georefererad karta.tif", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 32503-2025 FSC-klagomål.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35526-2023 FSC-klagomål.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 32503-2025 FSC-klagomål mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35526-2023 FSC-klagomål mail.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 32503-2025 tillsynsbegäran.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35526-2023 tillsynsbegäran.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 32503-2025 tillsynsbegäran mail.docx", "A 32503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35526-2023 tillsynsbegäran mail.docx", "A 35526-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35526-2023</t>
+          <t>A 30653-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45147</v>
+        <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2964,46 +2964,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35526-2023 artfynd.xlsx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35526-2023 karta.png", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35526-2023 georefererad karta.tif", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35526-2023 FSC-klagomål.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35526-2023 FSC-klagomål mail.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35526-2023 tillsynsbegäran.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35526-2023 tillsynsbegäran mail.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18822-2026</t>
+          <t>A 30662-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3017,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46128</v>
+        <v>45112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3033,10 +3037,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3048,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3057,10 +3061,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3069,46 +3073,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7339-2025</t>
+          <t>A 30754-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3122,10 +3126,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45703</v>
+        <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3138,13 +3142,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3178,42 +3182,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30653-2023</t>
+          <t>A 18822-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3227,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45112</v>
+        <v>46128</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3243,23 +3247,23 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -3267,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3279,43 +3283,39 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30653-2023 artfynd.xlsx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 18822-2026 artfynd.xlsx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30653-2023 karta.png", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 18822-2026 karta.png", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30653-2023 georefererad karta.tif", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 18822-2026 georefererad karta.tif", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30653-2023 FSC-klagomål.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 18822-2026 FSC-klagomål.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30653-2023 FSC-klagomål mail.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 18822-2026 FSC-klagomål mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30653-2023 tillsynsbegäran.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 18822-2026 tillsynsbegäran.docx", "A 18822-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30653-2023 tillsynsbegäran mail.docx", "A 30653-2023")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30653-2023 prioriterade fågelarter.docx", "A 30653-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 18822-2026 tillsynsbegäran mail.docx", "A 18822-2026")</f>
         <v/>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35491-2023</t>
+          <t>A 31742-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3441,10 +3441,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45146</v>
+        <v>45117</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3481,62 +3481,62 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30662-2023</t>
+          <t>A 35491-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45112</v>
+        <v>45146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3590,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3602,46 +3602,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31742-2023</t>
+          <t>A 23906-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3655,10 +3659,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45117</v>
+        <v>45455</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3671,10 +3675,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3704,53 +3708,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41586-2026</t>
+          <t>A 7339-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46302</v>
+        <v>45703</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3779,16 +3779,11 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3821,46 +3816,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 41586-2026 artfynd.xlsx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 41586-2026 karta.png", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 41586-2026 georefererad karta.tif", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 41586-2026 FSC-klagomål.docx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 41586-2026 FSC-klagomål mail.docx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 41586-2026 tillsynsbegäran.docx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 41586-2026 tillsynsbegäran mail.docx", "A 41586-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23906-2024</t>
+          <t>A 41586-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3874,10 +3869,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45455</v>
+        <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3889,11 +3884,16 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3926,39 +3926,39 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 23906-2024 artfynd.xlsx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 41586-2026 artfynd.xlsx", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 23906-2024 karta.png", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 41586-2026 karta.png", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 23906-2024 georefererad karta.tif", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 41586-2026 georefererad karta.tif", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 23906-2024 FSC-klagomål.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 41586-2026 FSC-klagomål.docx", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 23906-2024 FSC-klagomål mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 41586-2026 FSC-klagomål mail.docx", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 23906-2024 tillsynsbegäran.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 41586-2026 tillsynsbegäran.docx", "A 41586-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 23906-2024 tillsynsbegäran mail.docx", "A 23906-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 41586-2026 tillsynsbegäran mail.docx", "A 41586-2026")</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
         <v>44637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44764</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44502</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44683</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44585</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6653-2022</t>
+          <t>A 22541-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44602</v>
+        <v>45071</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 64207-2021</t>
+          <t>A 39556-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44510</v>
+        <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39556-2022</t>
+          <t>A 46511-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44818</v>
+        <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2006-2024</t>
+          <t>A 12160-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45308</v>
+        <v>45377</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 24368-2022</t>
+          <t>A 67455-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44726</v>
+        <v>44524</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30633-2023</t>
+          <t>A 69413-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45112</v>
+        <v>44531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31889-2023</t>
+          <t>A 25928-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45118</v>
+        <v>45090</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30772-2023</t>
+          <t>A 9086-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45112</v>
+        <v>45713</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 69413-2021</t>
+          <t>A 30628-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44531</v>
+        <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4782-2024</t>
+          <t>A 30643-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45328</v>
+        <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9086-2025</t>
+          <t>A 50057-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45713</v>
+        <v>45215</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30769-2023</t>
+          <t>A 29658-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45112</v>
+        <v>44754</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5430,7 +5430,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30794-2023</t>
+          <t>A 28073-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5444,10 +5444,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45112</v>
+        <v>45476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>7.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5503,7 +5503,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51229-2022</t>
+          <t>A 18615-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44868</v>
+        <v>45763</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28073-2024</t>
+          <t>A 31717-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45476</v>
+        <v>45117</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 27103-2024</t>
+          <t>A 31719-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45471</v>
+        <v>45117</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25928-2023</t>
+          <t>A 30800-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45090</v>
+        <v>45112</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5795,7 +5795,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29794-2025</t>
+          <t>A 24368-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45825</v>
+        <v>44726</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5868,7 +5868,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6745-2023</t>
+          <t>A 29794-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5878,14 +5878,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44966</v>
+        <v>45825</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10918-2025</t>
+          <t>A 30650-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45722</v>
+        <v>45112</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55159-2024</t>
+          <t>A 10918-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45621</v>
+        <v>45722</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6104,7 +6104,7 @@
         <v>45715</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18615-2025</t>
+          <t>A 31804-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45763</v>
+        <v>45834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6233,7 +6233,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38586-2023</t>
+          <t>A 32506-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45162</v>
+        <v>45838</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6306,7 +6306,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31804-2025</t>
+          <t>A 32320-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45834</v>
+        <v>45836</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>11.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6379,7 +6379,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32320-2025</t>
+          <t>A 54289-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6393,10 +6393,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45836</v>
+        <v>44882</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32506-2025</t>
+          <t>A 60792-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45838</v>
+        <v>44914</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6525,7 +6525,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47522-2024</t>
+          <t>A 9401-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45587</v>
+        <v>45359</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6554,13 +6554,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6603,7 +6598,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 65143-2023</t>
+          <t>A 1922-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6617,10 +6612,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45288</v>
+        <v>45308</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6633,7 +6628,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6676,7 +6671,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9159-2024</t>
+          <t>A 54287-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6690,10 +6685,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45358</v>
+        <v>44882</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6706,7 +6701,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6749,7 +6744,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 40774-2025</t>
+          <t>A 5072-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6763,10 +6758,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45897</v>
+        <v>44958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6779,7 +6774,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6822,7 +6817,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31746-2023</t>
+          <t>A 65118-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6836,10 +6831,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45117</v>
+        <v>45288</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6895,7 +6890,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28158-2024</t>
+          <t>A 30769-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6909,10 +6904,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45476</v>
+        <v>45112</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6925,7 +6920,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.1</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6968,7 +6963,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 435-2025</t>
+          <t>A 54659-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6982,10 +6977,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45664</v>
+        <v>44883</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +6993,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7041,7 +7036,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63725-2023</t>
+          <t>A 30794-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7055,10 +7050,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45276</v>
+        <v>45112</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7066,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7114,7 +7109,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36650-2025</t>
+          <t>A 31718-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7128,10 +7123,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45872</v>
+        <v>45117</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7139,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7187,7 +7182,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59613-2023</t>
+          <t>A 56335-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7201,10 +7196,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45254</v>
+        <v>45624</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7217,7 +7212,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7260,7 +7255,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3237-2023</t>
+          <t>A 28040-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7274,10 +7269,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44946</v>
+        <v>45476</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7290,7 +7285,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7333,7 +7328,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31724-2023</t>
+          <t>A 22834-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7347,10 +7342,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45117</v>
+        <v>45448</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7363,7 +7358,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7406,7 +7401,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31726-2023</t>
+          <t>A 4782-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7420,10 +7415,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45117</v>
+        <v>45328</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7436,7 +7431,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7479,7 +7474,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61671-2022</t>
+          <t>A 47522-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7493,10 +7488,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44917</v>
+        <v>45587</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7508,8 +7503,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7552,7 +7552,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 47279-2025</t>
+          <t>A 435-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7566,10 +7566,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45930</v>
+        <v>45664</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7625,7 +7625,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 56334-2024</t>
+          <t>A 28158-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7639,10 +7639,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45624</v>
+        <v>45476</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62986-2023</t>
+          <t>A 43398-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7712,10 +7712,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45272</v>
+        <v>45568</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59816-2021</t>
+          <t>A 59517-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44494</v>
+        <v>45254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48212-2025</t>
+          <t>A 3237-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45933</v>
+        <v>44946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31546-2022</t>
+          <t>A 59816-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7927,14 +7927,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44775</v>
+        <v>44494</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7990,7 +7990,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 49269-2025</t>
+          <t>A 36650-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45938</v>
+        <v>45872</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8063,7 +8063,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61318-2023</t>
+          <t>A 11605-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8077,10 +8077,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45264</v>
+        <v>45373</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8136,7 +8136,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42483-2023</t>
+          <t>A 70708-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45180</v>
+        <v>44537</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8209,7 +8209,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30650-2023</t>
+          <t>A 65143-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45112</v>
+        <v>45288</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8282,7 +8282,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51613-2025</t>
+          <t>A 6745-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8292,14 +8292,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45951</v>
+        <v>44966</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8355,7 +8355,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47265-2024</t>
+          <t>A 1395-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8369,10 +8369,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45586</v>
+        <v>45303</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8428,7 +8428,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11584-2026</t>
+          <t>A 31546-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8438,14 +8438,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46084</v>
+        <v>44775</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8501,7 +8501,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30637-2023</t>
+          <t>A 30633-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8518,7 +8518,7 @@
         <v>45112</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8574,7 +8574,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52513-2025</t>
+          <t>A 23330-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8584,14 +8584,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45954</v>
+        <v>45453</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8603,8 +8603,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8647,7 +8652,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8570-2025</t>
+          <t>A 57036-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8661,10 +8666,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45709</v>
+        <v>45629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8677,7 +8682,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8720,7 +8725,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 52511-2025</t>
+          <t>A 40774-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8734,10 +8739,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45954</v>
+        <v>45897</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8750,7 +8755,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8793,7 +8798,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12503-2026</t>
+          <t>A 1921-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8807,10 +8812,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46090</v>
+        <v>45308</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8823,7 +8828,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8866,7 +8871,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52939-2025</t>
+          <t>A 42250-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8880,10 +8885,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45957</v>
+        <v>45180</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8896,7 +8901,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8939,7 +8944,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 12469-2026</t>
+          <t>A 9159-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8953,10 +8958,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46090</v>
+        <v>45358</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8969,7 +8974,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9012,7 +9017,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5072-2023</t>
+          <t>A 11021-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9026,10 +9031,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44958</v>
+        <v>44628</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9042,7 +9047,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9085,7 +9090,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12879-2026</t>
+          <t>A 14111-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9095,14 +9100,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9114,13 +9119,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9163,7 +9163,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17925-2022</t>
+          <t>A 50302-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9177,10 +9177,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44683</v>
+        <v>45216</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9236,7 +9236,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13120-2026</t>
+          <t>A 14545-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9246,14 +9246,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46093</v>
+        <v>46100</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9309,7 +9309,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 54295-2023</t>
+          <t>A 58011-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45232</v>
+        <v>44900</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9382,7 +9382,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13121-2026</t>
+          <t>A 53055-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9396,10 +9396,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46093</v>
+        <v>45611</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9455,7 +9455,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 58011-2022</t>
+          <t>A 56452-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9469,10 +9469,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44900</v>
+        <v>44893</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9528,7 +9528,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56452-2022</t>
+          <t>A 58010-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9542,10 +9542,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44893</v>
+        <v>44900</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9601,7 +9601,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14111-2026</t>
+          <t>A 11239-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9615,10 +9615,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46099</v>
+        <v>44992</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9674,7 +9674,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47980-2023</t>
+          <t>A 31889-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9688,10 +9688,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45204</v>
+        <v>45118</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9747,7 +9747,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 9401-2024</t>
+          <t>A 18613-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45359</v>
+        <v>45763</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9820,7 +9820,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58010-2022</t>
+          <t>A 18614-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9834,10 +9834,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44900</v>
+        <v>45763</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9893,7 +9893,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 14545-2026</t>
+          <t>A 31712-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9903,14 +9903,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46100</v>
+        <v>45117</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9966,7 +9966,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 65118-2023</t>
+          <t>A 31715-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9980,10 +9980,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45288</v>
+        <v>45117</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10039,7 +10039,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 9527-2023</t>
+          <t>A 31745-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10053,10 +10053,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44981</v>
+        <v>45117</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10112,7 +10112,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58137-2025</t>
+          <t>A 15112-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45982</v>
+        <v>44658</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10185,7 +10185,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 58139-2025</t>
+          <t>A 3238-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10199,10 +10199,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45982</v>
+        <v>44946</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 18613-2025</t>
+          <t>A 59472-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10272,10 +10272,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45763</v>
+        <v>45254</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10331,7 +10331,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 18614-2025</t>
+          <t>A 47264-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45763</v>
+        <v>45586</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10404,7 +10404,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 60089-2025</t>
+          <t>A 47265-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10418,10 +10418,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45993</v>
+        <v>45586</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 60093-2025</t>
+          <t>A 9530-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45993</v>
+        <v>44981</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10550,7 +10550,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 50981-2023</t>
+          <t>A 19644-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45218</v>
+        <v>46134</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10579,13 +10579,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10628,7 +10623,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60091-2025</t>
+          <t>A 42483-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10642,10 +10637,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45993</v>
+        <v>45180</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10658,7 +10653,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10701,7 +10696,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 60092-2025</t>
+          <t>A 22443-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10715,10 +10710,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45993</v>
+        <v>45070</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10731,7 +10726,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10774,7 +10769,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 59871-2025</t>
+          <t>A 6653-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10788,10 +10783,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45992</v>
+        <v>44602</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10804,7 +10799,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10847,7 +10842,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59872-2025</t>
+          <t>A 54295-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10861,10 +10856,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45992</v>
+        <v>45232</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10877,7 +10872,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10920,7 +10915,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 60181-2025</t>
+          <t>A 6064-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10934,10 +10929,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45994</v>
+        <v>45696</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10950,7 +10945,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10993,7 +10988,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 50302-2023</t>
+          <t>A 30801-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11007,10 +11002,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45216</v>
+        <v>45112</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11023,7 +11018,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11066,7 +11061,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60946-2025</t>
+          <t>A 56331-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11080,10 +11075,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45999</v>
+        <v>45624</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11096,7 +11091,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11139,7 +11134,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19644-2026</t>
+          <t>A 36131-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11153,10 +11148,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46134</v>
+        <v>45534</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11169,7 +11164,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11212,7 +11207,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59472-2023</t>
+          <t>A 36532-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11226,10 +11221,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45254</v>
+        <v>45537</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11242,7 +11237,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11285,7 +11280,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 9530-2023</t>
+          <t>A 20600-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11299,10 +11294,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44981</v>
+        <v>46140</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11315,7 +11310,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11358,7 +11353,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 10610-2025</t>
+          <t>A 31724-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11372,10 +11367,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45721</v>
+        <v>45117</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11388,7 +11383,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11431,7 +11426,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 64005-2025</t>
+          <t>A 31726-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11445,10 +11440,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46021</v>
+        <v>45117</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11461,7 +11456,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11504,7 +11499,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 54289-2022</t>
+          <t>A 17925-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11518,10 +11513,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44882</v>
+        <v>44683</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11534,7 +11529,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11577,7 +11572,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6064-2025</t>
+          <t>A 52371-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11591,10 +11586,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45696</v>
+        <v>45953</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11607,7 +11602,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11650,7 +11645,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 52371-2025</t>
+          <t>A 21751-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11664,10 +11659,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45953</v>
+        <v>44708</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11680,7 +11675,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11723,7 +11718,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56305-2025</t>
+          <t>A 7046-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11737,10 +11732,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45974</v>
+        <v>45701</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11753,7 +11748,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11796,7 +11791,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 36131-2024</t>
+          <t>A 56305-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11810,10 +11805,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45534</v>
+        <v>45974</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11826,7 +11821,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11869,7 +11864,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36532-2024</t>
+          <t>A 20598-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11883,10 +11878,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45537</v>
+        <v>46140</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11899,7 +11894,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11942,7 +11937,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 30628-2023</t>
+          <t>A 42256-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11956,10 +11951,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45112</v>
+        <v>45180</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11972,7 +11967,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12015,7 +12010,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 30643-2023</t>
+          <t>A 25694-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12029,10 +12024,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45112</v>
+        <v>45803</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12045,7 +12040,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12088,7 +12083,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 25694-2025</t>
+          <t>A 41910-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12102,10 +12097,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45803</v>
+        <v>45561</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12118,7 +12113,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12161,7 +12156,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2497-2026</t>
+          <t>A 30637-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12175,10 +12170,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46037</v>
+        <v>45112</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12191,7 +12186,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12234,7 +12229,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 22834-2024</t>
+          <t>A 51564-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12248,10 +12243,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45448</v>
+        <v>45604</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12264,7 +12259,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12307,7 +12302,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 41910-2024</t>
+          <t>A 62986-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12321,10 +12316,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45561</v>
+        <v>45272</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12337,7 +12332,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12380,7 +12375,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 67455-2021</t>
+          <t>A 20782-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12394,10 +12389,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44524</v>
+        <v>46141</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12410,7 +12405,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12453,7 +12448,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4119-2026</t>
+          <t>A 31746-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12467,10 +12462,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46044</v>
+        <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12482,13 +12477,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12531,7 +12521,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 58093-2023</t>
+          <t>A 31711-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12545,10 +12535,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45248</v>
+        <v>45117</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12561,7 +12551,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12604,7 +12594,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 4587-2026</t>
+          <t>A 31727-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12618,10 +12608,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46048</v>
+        <v>45117</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12634,7 +12624,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12677,7 +12667,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4588-2026</t>
+          <t>A 51314-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12687,14 +12677,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46048</v>
+        <v>45219</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12750,7 +12740,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 54144-2022</t>
+          <t>A 59613-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12764,10 +12754,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44881</v>
+        <v>45254</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12780,7 +12770,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12823,7 +12813,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 20598-2026</t>
+          <t>A 47980-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12837,10 +12827,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46140</v>
+        <v>45204</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12853,7 +12843,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12896,7 +12886,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20600-2026</t>
+          <t>A 8570-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12910,10 +12900,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46140</v>
+        <v>45709</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12926,7 +12916,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12969,7 +12959,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 6071-2026</t>
+          <t>A 61318-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12983,10 +12973,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46052</v>
+        <v>45264</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12999,7 +12989,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13042,7 +13032,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 6074-2026</t>
+          <t>A 18337-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13056,10 +13046,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46052</v>
+        <v>45041</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13072,7 +13062,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13115,7 +13105,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 20782-2026</t>
+          <t>A 55159-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13129,10 +13119,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46141</v>
+        <v>45621</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13188,7 +13178,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 6104-2026</t>
+          <t>A 47279-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13202,10 +13192,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46052</v>
+        <v>45930</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13218,7 +13208,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13261,7 +13251,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 6103-2026</t>
+          <t>A 24965-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13275,10 +13265,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46052</v>
+        <v>46174</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13291,7 +13281,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13334,7 +13324,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 42250-2023</t>
+          <t>A 48212-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13348,10 +13338,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45180</v>
+        <v>45933</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13364,7 +13354,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13407,7 +13397,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 42256-2023</t>
+          <t>A 54144-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13421,10 +13411,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45180</v>
+        <v>44881</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13437,7 +13427,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13480,7 +13470,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 50057-2023</t>
+          <t>A 49269-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13494,10 +13484,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45215</v>
+        <v>45938</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13510,7 +13500,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13553,7 +13543,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 46511-2023</t>
+          <t>A 26642-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13567,10 +13557,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45197</v>
+        <v>46184</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13583,7 +13573,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13626,7 +13616,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 7546-2026</t>
+          <t>A 2006-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13640,10 +13630,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46059</v>
+        <v>45308</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13656,7 +13646,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13699,7 +13689,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 1921-2024</t>
+          <t>A 27248-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13713,10 +13703,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45308</v>
+        <v>46188</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13729,7 +13719,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13772,7 +13762,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 31711-2023</t>
+          <t>A 61671-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13786,10 +13776,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45117</v>
+        <v>44917</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13802,7 +13792,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13845,7 +13835,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31727-2023</t>
+          <t>A 27782-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13859,10 +13849,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45117</v>
+        <v>46191</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13875,7 +13865,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.1</v>
+        <v>6.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13918,7 +13908,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 11605-2024</t>
+          <t>A 51229-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13932,10 +13922,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45373</v>
+        <v>44868</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13948,7 +13938,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13991,7 +13981,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 53055-2024</t>
+          <t>A 61334-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14005,10 +13995,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45611</v>
+        <v>44915</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14021,7 +14011,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14064,7 +14054,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 29658-2022</t>
+          <t>A 30793-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14078,10 +14068,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44754</v>
+        <v>45112</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14094,7 +14084,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14137,7 +14127,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 57036-2024</t>
+          <t>A 30795-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14151,10 +14141,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45629</v>
+        <v>45112</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14167,7 +14157,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14210,7 +14200,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 24965-2026</t>
+          <t>A 30724-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14224,10 +14214,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46174</v>
+        <v>45112</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14240,7 +14230,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14283,7 +14273,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 26642-2026</t>
+          <t>A 54311-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14297,10 +14287,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46184</v>
+        <v>44882</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14313,7 +14303,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14356,7 +14346,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 54287-2022</t>
+          <t>A 56334-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14370,10 +14360,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44882</v>
+        <v>45624</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14386,7 +14376,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14429,7 +14419,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 15112-2022</t>
+          <t>A 61026-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14443,10 +14433,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44658</v>
+        <v>44914</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14459,7 +14449,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14502,7 +14492,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27248-2026</t>
+          <t>A 30098-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14516,10 +14506,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46188</v>
+        <v>46206</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14532,7 +14522,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14575,7 +14565,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27782-2026</t>
+          <t>A 51613-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14589,10 +14579,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46191</v>
+        <v>45951</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14605,7 +14595,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14648,7 +14638,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 1922-2024</t>
+          <t>A 63725-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14662,10 +14652,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45308</v>
+        <v>45276</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14678,7 +14668,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14721,7 +14711,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 61334-2022</t>
+          <t>A 9527-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14735,10 +14725,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44915</v>
+        <v>44981</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14751,7 +14741,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14794,7 +14784,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 51564-2024</t>
+          <t>A 52511-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14808,10 +14798,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45604</v>
+        <v>45954</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14824,7 +14814,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14867,7 +14857,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 7046-2025</t>
+          <t>A 30760-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14881,10 +14871,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45701</v>
+        <v>45112</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14897,7 +14887,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14940,7 +14930,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 30098-2026</t>
+          <t>A 30762-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14954,10 +14944,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46206</v>
+        <v>45112</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14970,7 +14960,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15013,7 +15003,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 30760-2023</t>
+          <t>A 52513-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15027,10 +15017,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45112</v>
+        <v>45954</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15043,7 +15033,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15086,7 +15076,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 30762-2023</t>
+          <t>A 52939-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15100,10 +15090,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45112</v>
+        <v>45957</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15116,7 +15106,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15159,7 +15149,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 56331-2024</t>
+          <t>A 38586-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15173,10 +15163,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45624</v>
+        <v>45162</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15189,7 +15179,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15232,7 +15222,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 51314-2023</t>
+          <t>A 36861-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15242,14 +15232,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45219</v>
+        <v>46272</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15262,7 +15252,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15305,7 +15295,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3238-2023</t>
+          <t>A 31907-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15319,10 +15309,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44946</v>
+        <v>46231</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15334,8 +15324,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15378,7 +15373,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 12160-2024</t>
+          <t>A 30772-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15392,10 +15387,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45377</v>
+        <v>45112</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15408,7 +15403,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15451,7 +15446,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 54659-2022</t>
+          <t>A 2398-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15465,10 +15460,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44883</v>
+        <v>45310</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15481,7 +15476,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15524,7 +15519,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 36861-2026</t>
+          <t>A 38521-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15538,10 +15533,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46272</v>
+        <v>46283</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15554,7 +15549,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15597,7 +15592,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31718-2023</t>
+          <t>A 50981-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15611,10 +15606,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45117</v>
+        <v>45218</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15626,8 +15621,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15670,7 +15670,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31907-2026</t>
+          <t>A 38601-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15684,10 +15684,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46231</v>
+        <v>46283</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15699,13 +15699,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15748,7 +15743,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 43398-2024</t>
+          <t>A 58093-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15762,10 +15757,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45568</v>
+        <v>45248</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15778,7 +15773,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15821,7 +15816,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 54311-2022</t>
+          <t>A 64207-2021</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15835,10 +15830,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44882</v>
+        <v>44510</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15851,7 +15846,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15894,7 +15889,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 22443-2023</t>
+          <t>A 39344-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15908,10 +15903,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45070</v>
+        <v>46288</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15924,7 +15919,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15967,7 +15962,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 38521-2026</t>
+          <t>A 58139-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15981,10 +15976,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46283</v>
+        <v>45982</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15997,7 +15992,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16040,7 +16035,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 38601-2026</t>
+          <t>A 47258-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16054,10 +16049,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46283</v>
+        <v>45930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16070,7 +16065,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16113,7 +16108,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 60792-2022</t>
+          <t>A 58137-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16127,10 +16122,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44914</v>
+        <v>45982</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16143,7 +16138,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16186,7 +16181,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 47258-2025</t>
+          <t>A 27103-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16200,10 +16195,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45930</v>
+        <v>45471</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16216,7 +16211,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16259,7 +16254,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 61026-2022</t>
+          <t>A 39852-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16273,10 +16268,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44914</v>
+        <v>46290</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16289,7 +16284,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16332,7 +16327,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 47264-2024</t>
+          <t>A 57443-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16346,10 +16341,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45586</v>
+        <v>45629</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16362,7 +16357,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16405,7 +16400,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 22541-2023</t>
+          <t>A 39841-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16419,10 +16414,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45071</v>
+        <v>46290</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16435,7 +16430,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16478,7 +16473,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 21751-2022</t>
+          <t>A 39896-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16492,10 +16487,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44708</v>
+        <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16508,7 +16503,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16551,7 +16546,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 1395-2024</t>
+          <t>A 21878-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16565,10 +16560,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45303</v>
+        <v>45784</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16581,7 +16576,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16624,7 +16619,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 2398-2024</t>
+          <t>A 59871-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16638,10 +16633,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45310</v>
+        <v>45992</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16654,7 +16649,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16697,7 +16692,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 30793-2023</t>
+          <t>A 60091-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16711,10 +16706,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45112</v>
+        <v>45993</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16727,7 +16722,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16770,7 +16765,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 30795-2023</t>
+          <t>A 60092-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16784,10 +16779,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45112</v>
+        <v>45993</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16800,7 +16795,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16843,7 +16838,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 30800-2023</t>
+          <t>A 23907-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16857,10 +16852,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45112</v>
+        <v>45455</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16873,7 +16868,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16916,7 +16911,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 39344-2026</t>
+          <t>A 60089-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16930,10 +16925,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46288</v>
+        <v>45993</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16946,7 +16941,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16989,7 +16984,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 28040-2024</t>
+          <t>A 60093-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17003,10 +16998,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45476</v>
+        <v>45993</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17019,7 +17014,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17062,7 +17057,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 18337-2023</t>
+          <t>A 59872-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17076,10 +17071,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45041</v>
+        <v>45992</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17092,7 +17087,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17135,7 +17130,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 39852-2026</t>
+          <t>A 60181-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17149,10 +17144,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46290</v>
+        <v>45994</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17165,7 +17160,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17208,7 +17203,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 39841-2026</t>
+          <t>A 60946-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17222,10 +17217,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46290</v>
+        <v>45999</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17238,7 +17233,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17281,7 +17276,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 11021-2022</t>
+          <t>A 33852-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17295,10 +17290,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44628</v>
+        <v>46251</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17311,7 +17306,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17354,7 +17349,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 11239-2023</t>
+          <t>A 33853-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17368,10 +17363,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44992</v>
+        <v>46251</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17384,7 +17379,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17427,7 +17422,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 39896-2026</t>
+          <t>A 43938-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17441,10 +17436,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46290</v>
+        <v>45572</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17457,7 +17452,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17500,7 +17495,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31717-2023</t>
+          <t>A 10610-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17514,10 +17509,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45117</v>
+        <v>45721</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17530,7 +17525,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17573,7 +17568,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 31719-2023</t>
+          <t>A 64005-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17587,10 +17582,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45117</v>
+        <v>46021</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17603,7 +17598,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17646,7 +17641,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 33852-2026</t>
+          <t>A 17434-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17656,14 +17651,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46251</v>
+        <v>46120</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17676,7 +17671,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17719,7 +17714,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 33853-2026</t>
+          <t>A 35071-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17733,10 +17728,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17749,7 +17744,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17792,7 +17787,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 31745-2023</t>
+          <t>A 35072-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17806,10 +17801,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45117</v>
+        <v>46259</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17822,7 +17817,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17865,7 +17860,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 56335-2024</t>
+          <t>A 12124-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17879,10 +17874,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45624</v>
+        <v>45377</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17894,8 +17889,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17938,7 +17938,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 30801-2023</t>
+          <t>A 2497-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17952,10 +17952,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45112</v>
+        <v>46037</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18011,7 +18011,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 70708-2021</t>
+          <t>A 4119-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18025,10 +18025,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44537</v>
+        <v>46044</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18040,8 +18040,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18084,7 +18089,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 31712-2023</t>
+          <t>A 4587-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18098,10 +18103,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45117</v>
+        <v>46048</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18114,7 +18119,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18157,7 +18162,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 31715-2023</t>
+          <t>A 4588-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18171,10 +18176,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45117</v>
+        <v>46048</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18187,7 +18192,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>12.4</v>
+        <v>1.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18230,7 +18235,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 17434-2026</t>
+          <t>A 6071-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18240,14 +18245,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46120</v>
+        <v>46052</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18260,7 +18265,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18303,7 +18308,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 59517-2023</t>
+          <t>A 6074-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18317,10 +18322,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45254</v>
+        <v>46052</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18333,7 +18338,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18376,7 +18381,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 30724-2023</t>
+          <t>A 6104-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18390,10 +18395,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45112</v>
+        <v>46052</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18406,7 +18411,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18449,7 +18454,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 35072-2026</t>
+          <t>A 6103-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18463,10 +18468,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46259</v>
+        <v>46052</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18479,7 +18484,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18522,7 +18527,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 12124-2024</t>
+          <t>A 7546-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18536,10 +18541,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45377</v>
+        <v>46059</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18551,13 +18556,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18600,7 +18600,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 35071-2026</t>
+          <t>A 42821-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18614,10 +18614,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46259</v>
+        <v>46309</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18673,7 +18673,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 57443-2024</t>
+          <t>A 42822-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18687,10 +18687,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45629</v>
+        <v>46309</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18746,7 +18746,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 23330-2024</t>
+          <t>A 11584-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18756,14 +18756,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45453</v>
+        <v>46084</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18775,13 +18775,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18824,7 +18819,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 23907-2024</t>
+          <t>A 12469-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18838,10 +18833,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45455</v>
+        <v>46090</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18854,7 +18849,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18897,7 +18892,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 21878-2025</t>
+          <t>A 12503-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18911,10 +18906,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45784</v>
+        <v>46090</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18927,7 +18922,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18970,7 +18965,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 43938-2024</t>
+          <t>A 13120-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18984,10 +18979,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45572</v>
+        <v>46093</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19000,7 +18995,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19043,7 +19038,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 42821-2026</t>
+          <t>A 13121-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19057,10 +19052,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46309</v>
+        <v>46093</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19073,7 +19068,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19116,7 +19111,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 42822-2026</t>
+          <t>A 12879-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19126,14 +19121,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46309</v>
+        <v>46092</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19145,8 +19140,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19206,7 +19206,7 @@
         <v>45934</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>46154</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>46246</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45215</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45112</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45363</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46184</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45703</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>45146</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>46128</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>45455</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>46302</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44764</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44502</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44683</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44585</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45118</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45328</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44868</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44966</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45117</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45117</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45624</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45264</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45180</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44958</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45709</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44683</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45359</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44981</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>45218</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45254</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44981</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45953</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45974</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45534</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44775</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45587</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45288</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45897</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45090</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46140</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46141</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45112</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45112</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45448</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45561</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44524</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45248</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44881</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45215</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>45197</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45930</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>45933</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44602</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44510</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45308</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44726</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45471</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>45951</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45621</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45954</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>45954</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45957</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>45162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45358</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45117</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>45276</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45254</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>45272</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>44494</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>45112</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>45112</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>45982</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45982</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45288</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45993</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45763</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45763</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45993</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45993</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45992</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45992</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>44882</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45994</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45999</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45180</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45180</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45308</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>46174</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45117</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45117</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45373</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45721</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>46021</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45611</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>46037</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>46044</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>46048</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>46048</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44754</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>46052</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>46052</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>46052</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>46052</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45629</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>46184</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>46059</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46188</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44882</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44658</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>46090</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>46090</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>46092</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>46191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>46093</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>46093</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>44900</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44893</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>46099</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44900</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45308</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>46100</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44915</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>45604</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45701</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>45112</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45112</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45624</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45219</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44946</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>46134</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>46206</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45377</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>44883</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45117</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45568</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44882</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45070</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>46272</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44914</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44914</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45586</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>46231</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45071</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44708</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45303</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45310</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45112</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45112</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45112</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45476</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>46283</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>46283</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45930</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45041</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44628</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44992</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>46288</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45117</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>45117</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45117</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45624</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45112</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>46290</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>44537</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>46290</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45117</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45117</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46290</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45254</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>46251</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>46251</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45629</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>46120</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>45453</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45455</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45784</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45572</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>46259</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45377</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46259</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>46309</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>46309</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>46311</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45713</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45476</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45825</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45722</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45715</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45834</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45836</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45838</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45476</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45664</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45872</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45934</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>46154</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>46246</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>45112</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45943</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45215</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>45117</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>45112</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45112</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45112</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45363</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46184</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>46093</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45147</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>45703</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>45146</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>46128</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45117</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>45455</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>46302</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44764</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44502</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44683</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44585</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45118</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45328</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44868</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45112</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44966</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45763</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>45117</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45117</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45624</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45264</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>45180</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44958</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45709</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44683</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45232</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>45204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>45359</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44981</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>45218</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45216</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45586</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45696</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45254</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44981</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45953</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45974</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45534</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44775</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45587</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45288</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45897</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45090</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>46140</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46140</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46141</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45112</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45112</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45448</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45561</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44524</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45248</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44881</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45215</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>45197</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45930</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>45933</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45938</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44602</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44510</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45308</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44726</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45471</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>45951</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45621</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45954</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>45954</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45957</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>45162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45358</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45117</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>45276</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45254</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>45272</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>44494</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>45112</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>45112</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>45982</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45982</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45288</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45993</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45763</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45763</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45993</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45993</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45992</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45992</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>44882</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45994</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45999</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45180</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45180</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45308</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>46174</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45117</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45117</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45373</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45721</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>46021</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45611</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>46037</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>46044</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>46048</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>46048</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44754</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>46052</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>46052</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>46052</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>46052</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45629</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>46184</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>46059</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46188</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44882</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44658</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>46090</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>46090</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>46092</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>46191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>46093</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>46093</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>44900</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44893</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>46099</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44900</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45308</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>46100</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44915</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>45604</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45701</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>45112</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45112</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45624</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45219</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44946</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>46134</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>46206</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45377</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>44883</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45117</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45568</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44882</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45070</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>46272</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44914</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44914</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45586</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>46231</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45071</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>44708</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45303</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45310</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45112</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45112</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45112</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45476</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>46283</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>46283</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45930</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45041</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44628</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44992</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>46288</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45117</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>45117</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>45117</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45624</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45112</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>46290</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>44537</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>46290</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45117</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45117</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46290</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45254</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>46251</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>46251</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45629</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>46120</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>45453</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45455</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45784</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45572</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>46259</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45377</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46259</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>46309</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>46309</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>46311</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45713</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45476</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45825</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45722</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45715</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45834</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45836</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45838</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45476</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45664</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45872</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45934</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>46154</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>46246</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>

--- a/Översikt BOLLEBYGD.xlsx
+++ b/Översikt BOLLEBYGD.xlsx
@@ -601,7 +601,7 @@
         <v>45952</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 30777-2023</t>
+          <t>A 50011-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45112</v>
+        <v>45215</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -845,45 +845,271 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Svartbent strandpipare
+Sexfläckig bastardsvärmare
+Grönsångare
+Strandskata
+Sädesärla</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 50084-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Spillkråka
+Grönsiska
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50084-2025 artfynd.xlsx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50084-2025 karta.png", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50084-2025 georefererad karta.tif", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50084-2025 FSC-klagomål.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50084-2025 FSC-klagomål mail.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50084-2025 tillsynsbegäran.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50084-2025 tillsynsbegäran mail.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50084-2025 prioriterade fågelarter.docx", "A 50084-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 30777-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
         <v>10</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U6" t="n">
         <v>8</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Oxtungssvamp
 Vågbandad barkbock
@@ -892,258 +1118,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30777-2023 artfynd.xlsx", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30777-2023 karta.png", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30777-2023 georefererad karta.tif", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30777-2023 FSC-klagomål.docx", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30777-2023 FSC-klagomål mail.docx", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30777-2023 tillsynsbegäran.docx", "A 30777-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30777-2023 tillsynsbegäran mail.docx", "A 30777-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 50084-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45943</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Spillkråka
-Grönsiska
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50084-2025 artfynd.xlsx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50084-2025 karta.png", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50084-2025 georefererad karta.tif", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50084-2025 FSC-klagomål.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50084-2025 FSC-klagomål mail.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50084-2025 tillsynsbegäran.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50084-2025 tillsynsbegäran mail.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50084-2025 prioriterade fågelarter.docx", "A 50084-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 50011-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45215</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Svartbent strandpipare
-Sexfläckig bastardsvärmare
-Grönsångare
-Strandskata
-Sädesärla</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 50011-2023 artfynd.xlsx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 50011-2023 karta.png", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 50011-2023 georefererad karta.tif", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 50011-2023 FSC-klagomål.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 50011-2023 FSC-klagomål mail.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 50011-2023 tillsynsbegäran.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 50011-2023 tillsynsbegäran mail.docx", "A 50011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 50011-2023 prioriterade fågelarter.docx", "A 50011-2023")</f>
         <v/>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         <v>45377</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45966</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30671-2023</t>
+          <t>A 30785-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1397,7 +1397,7 @@
         <v>45112</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1422,405 +1422,405 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Lunglav
+Grönvit nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30785-2023 artfynd.xlsx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30785-2023 karta.png", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30785-2023 georefererad karta.tif", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30785-2023 FSC-klagomål.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30785-2023 FSC-klagomål mail.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30785-2023 tillsynsbegäran.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30785-2023 tillsynsbegäran mail.docx", "A 30785-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31728-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Gammelgransskål
+Kattfotslav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31728-2023 artfynd.xlsx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31728-2023 karta.png", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31728-2023 georefererad karta.tif", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31728-2023 FSC-klagomål.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31728-2023 FSC-klagomål mail.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31728-2023 tillsynsbegäran.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31728-2023 tillsynsbegäran mail.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31728-2023 prioriterade fågelarter.docx", "A 31728-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 30671-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>12</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>10</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Järnsparv
 Spillkråka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30671-2023 artfynd.xlsx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30671-2023 karta.png", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30671-2023 georefererad karta.tif", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 30671-2023 karta knärot.png", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30671-2023 FSC-klagomål.docx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30671-2023 FSC-klagomål mail.docx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30671-2023 tillsynsbegäran.docx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30671-2023 tillsynsbegäran mail.docx", "A 30671-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30671-2023 prioriterade fågelarter.docx", "A 30671-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 31728-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 30655-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gammelgransskål
-Kattfotslav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31728-2023 artfynd.xlsx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31728-2023 karta.png", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31728-2023 georefererad karta.tif", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31728-2023 FSC-klagomål.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31728-2023 FSC-klagomål mail.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31728-2023 tillsynsbegäran.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31728-2023 tillsynsbegäran mail.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31728-2023 prioriterade fågelarter.docx", "A 31728-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 30655-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Trädporella
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30655-2023 artfynd.xlsx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30655-2023 karta.png", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30655-2023 georefererad karta.tif", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30655-2023 FSC-klagomål.docx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30655-2023 FSC-klagomål mail.docx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30655-2023 tillsynsbegäran.docx", "A 30655-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30655-2023 tillsynsbegäran mail.docx", "A 30655-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 30785-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Lunglav
-Grönvit nattviol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30785-2023 artfynd.xlsx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30785-2023 karta.png", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30785-2023 georefererad karta.tif", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30785-2023 FSC-klagomål.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30785-2023 FSC-klagomål mail.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30785-2023 tillsynsbegäran.docx", "A 30785-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30785-2023 tillsynsbegäran mail.docx", "A 30785-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30666-2023</t>
+          <t>A 9930-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45112</v>
+        <v>45363</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1890,805 +1890,805 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
+          <t>Större träfjäril
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 9930-2024 artfynd.xlsx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 9930-2024 karta.png", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 9930-2024 georefererad karta.tif", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 9930-2024 FSC-klagomål.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 9930-2024 FSC-klagomål mail.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 9930-2024 tillsynsbegäran.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 9930-2024 tillsynsbegäran mail.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 9930-2024 prioriterade fågelarter.docx", "A 9930-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 31714-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45117</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 60380-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30666-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>Talltita
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30666-2023 artfynd.xlsx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30666-2023 karta.png", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30666-2023 georefererad karta.tif", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30666-2023 FSC-klagomål.docx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30666-2023 FSC-klagomål mail.docx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30666-2023 tillsynsbegäran.docx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30666-2023 tillsynsbegäran mail.docx", "A 30666-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30666-2023 prioriterade fågelarter.docx", "A 30666-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 60380-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" t="n">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 30792-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 60380-2025 artfynd.xlsx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 60380-2025 karta.png", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 60380-2025 georefererad karta.tif", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 60380-2025 FSC-klagomål.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 60380-2025 FSC-klagomål mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 60380-2025 tillsynsbegäran.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 60380-2025 tillsynsbegäran mail.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 60380-2025 prioriterade fågelarter.docx", "A 60380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9930-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45363</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Större träfjäril
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 9930-2024 artfynd.xlsx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 9930-2024 karta.png", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 9930-2024 georefererad karta.tif", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 9930-2024 FSC-klagomål.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 9930-2024 FSC-klagomål mail.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 9930-2024 tillsynsbegäran.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 9930-2024 tillsynsbegäran mail.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 9930-2024 prioriterade fågelarter.docx", "A 9930-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel
+Ärtsångare</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 26670-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46184</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>15.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tofsmes
 Grönsiska</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 26670-2026 artfynd.xlsx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 26670-2026 karta.png", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 26670-2026 georefererad karta.tif", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 26670-2026 FSC-klagomål.docx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 26670-2026 FSC-klagomål mail.docx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 26670-2026 tillsynsbegäran.docx", "A 26670-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 26670-2026 tillsynsbegäran mail.docx", "A 26670-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 13115-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>46093</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>6.5</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 13115-2026 artfynd.xlsx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 13115-2026 karta.png", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 13115-2026 georefererad karta.tif", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 13115-2026 FSC-klagomål.docx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 13115-2026 FSC-klagomål mail.docx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 13115-2026 tillsynsbegäran.docx", "A 13115-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 13115-2026 tillsynsbegäran mail.docx", "A 13115-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 31714-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45117</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 30763-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45112</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>BOLLEBYGD</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31714-2023 artfynd.xlsx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31714-2023 karta.png", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31714-2023 georefererad karta.tif", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31714-2023 FSC-klagomål.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31714-2023 FSC-klagomål mail.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31714-2023 tillsynsbegäran.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31714-2023 tillsynsbegäran mail.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31714-2023 prioriterade fågelarter.docx", "A 31714-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 30763-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Vågbandad barkbock
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30763-2023 artfynd.xlsx", "A 30763-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30763-2023 karta.png", "A 30763-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30763-2023 georefererad karta.tif", "A 30763-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30763-2023 FSC-klagomål.docx", "A 30763-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30763-2023 FSC-klagomål mail.docx", "A 30763-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30763-2023 tillsynsbegäran.docx", "A 30763-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30763-2023 tillsynsbegäran mail.docx", "A 30763-2023")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 30763-2023 prioriterade fågelarter.docx", "A 30763-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 30792-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45112</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BOLLEBYGD</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel
-Ärtsångare</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30792-2023 artfynd.xlsx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30792-2023 karta.png", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30792-2023 georefererad karta.tif", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30792-2023 FSC-klagomål.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30792-2023 FSC-klagomål mail.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30792-2023 tillsynsbegäran.docx", "A 30792-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30792-2023 tillsynsbegäran mail.docx", "A 30792-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30754-2023</t>
+          <t>A 35526-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45112</v>
+        <v>45147</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2754,46 +2754,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35526-2023 artfynd.xlsx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35526-2023 karta.png", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35526-2023 georefererad karta.tif", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35526-2023 FSC-klagomål.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35526-2023 FSC-klagomål mail.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35526-2023 tillsynsbegäran.docx", "A 35526-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35526-2023 tillsynsbegäran mail.docx", "A 35526-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 35526-2023</t>
+          <t>A 30745-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45147</v>
+        <v>45112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2859,39 +2859,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35526-2023 artfynd.xlsx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30745-2023 artfynd.xlsx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35526-2023 karta.png", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30745-2023 karta.png", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35526-2023 georefererad karta.tif", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30745-2023 georefererad karta.tif", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35526-2023 FSC-klagomål.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30745-2023 FSC-klagomål.docx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35526-2023 FSC-klagomål mail.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30745-2023 FSC-klagomål mail.docx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35526-2023 tillsynsbegäran.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30745-2023 tillsynsbegäran.docx", "A 30745-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35526-2023 tillsynsbegäran mail.docx", "A 35526-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30745-2023 tillsynsbegäran mail.docx", "A 30745-2023")</f>
         <v/>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7339-2025</t>
+          <t>A 30662-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45703</v>
+        <v>45112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3077,42 +3077,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Bäckbräsma</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30745-2023</t>
+          <t>A 30754-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3129,7 +3129,7 @@
         <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3186,38 +3186,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30745-2023 artfynd.xlsx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30754-2023 artfynd.xlsx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30745-2023 karta.png", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30754-2023 karta.png", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30745-2023 georefererad karta.tif", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30754-2023 georefererad karta.tif", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30745-2023 FSC-klagomål.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30754-2023 FSC-klagomål.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30745-2023 FSC-klagomål mail.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30754-2023 FSC-klagomål mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30745-2023 tillsynsbegäran.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30754-2023 tillsynsbegäran.docx", "A 30754-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30745-2023 tillsynsbegäran mail.docx", "A 30745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30754-2023 tillsynsbegäran mail.docx", "A 30754-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35491-2023</t>
+          <t>A 7339-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45146</v>
+        <v>45703</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3247,10 +3247,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3271,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3283,43 +3283,39 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 7339-2025 artfynd.xlsx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 7339-2025 karta.png", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 7339-2025 georefererad karta.tif", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 7339-2025 FSC-klagomål.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 7339-2025 FSC-klagomål mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 7339-2025 tillsynsbegäran.docx", "A 7339-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 7339-2025 tillsynsbegäran mail.docx", "A 7339-2025")</f>
         <v/>
       </c>
     </row>
@@ -3343,7 +3339,7 @@
         <v>46128</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3431,7 +3427,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30662-2023</t>
+          <t>A 31742-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3445,10 +3441,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45112</v>
+        <v>45117</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3461,7 +3457,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3494,49 +3490,53 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 30662-2023 artfynd.xlsx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 30662-2023 karta.png", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 30662-2023 georefererad karta.tif", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 30662-2023 FSC-klagomål.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 30662-2023 FSC-klagomål mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 30662-2023 tillsynsbegäran.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 30662-2023 tillsynsbegäran mail.docx", "A 30662-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31742-2023</t>
+          <t>A 35491-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45117</v>
+        <v>45146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3590,55 +3590,55 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 31742-2023 artfynd.xlsx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/artfynd/A 35491-2023 artfynd.xlsx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 31742-2023 karta.png", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor/A 35491-2023 karta.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 31742-2023 georefererad karta.tif", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/kartor_geotiff/A 35491-2023 georefererad karta.tif", "A 35491-2023")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/knärot/A 35491-2023 karta knärot.png", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 31742-2023 FSC-klagomål.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomål/A 35491-2023 FSC-klagomål.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 31742-2023 FSC-klagomål mail.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/klagomålsmail/A 35491-2023 FSC-klagomål mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 31742-2023 tillsynsbegäran.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsyn/A 35491-2023 tillsynsbegäran.docx", "A 35491-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 31742-2023 tillsynsbegäran mail.docx", "A 31742-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1443/fåglar/A 31742-2023 prioriterade fågelarter.docx", "A 31742-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1443/tillsynsmail/A 35491-2023 tillsynsbegäran mail.docx", "A 35491-2023")</f>
         <v/>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
         <v>45455</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>46302</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>44637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44764</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44570</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44727</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44502</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44530</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44683</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44585</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30633-2023</t>
+          <t>A 46511-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45112</v>
+        <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30772-2023</t>
+          <t>A 50057-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45112</v>
+        <v>45215</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31889-2023</t>
+          <t>A 29658-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45118</v>
+        <v>44754</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4782-2024</t>
+          <t>A 12160-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45328</v>
+        <v>45377</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51229-2022</t>
+          <t>A 60792-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44868</v>
+        <v>44914</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30769-2023</t>
+          <t>A 9401-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45112</v>
+        <v>45359</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30794-2023</t>
+          <t>A 54287-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45112</v>
+        <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6745-2023</t>
+          <t>A 30769-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44966</v>
+        <v>45112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18615-2025</t>
+          <t>A 54659-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45763</v>
+        <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3237-2023</t>
+          <t>A 30794-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44946</v>
+        <v>45112</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31724-2023</t>
+          <t>A 31718-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5447,7 +5447,7 @@
         <v>45117</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5503,7 +5503,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31726-2023</t>
+          <t>A 4782-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45117</v>
+        <v>45328</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61671-2022</t>
+          <t>A 28040-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44917</v>
+        <v>45476</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56334-2024</t>
+          <t>A 22834-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5663,10 +5663,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45624</v>
+        <v>45448</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61318-2023</t>
+          <t>A 3237-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45264</v>
+        <v>44946</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5795,7 +5795,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 42483-2023</t>
+          <t>A 11605-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45180</v>
+        <v>45373</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5868,7 +5868,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5072-2023</t>
+          <t>A 70708-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44958</v>
+        <v>44537</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8570-2025</t>
+          <t>A 1395-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45709</v>
+        <v>45303</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17925-2022</t>
+          <t>A 30633-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44683</v>
+        <v>45112</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6087,7 +6087,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54295-2023</t>
+          <t>A 9159-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6101,10 +6101,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45232</v>
+        <v>45358</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47980-2023</t>
+          <t>A 23330-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6170,14 +6170,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45204</v>
+        <v>45453</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6189,8 +6189,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6233,7 +6238,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9401-2024</t>
+          <t>A 57036-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6247,10 +6252,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45359</v>
+        <v>45629</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6268,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6306,7 +6311,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9527-2023</t>
+          <t>A 11021-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6320,10 +6325,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44981</v>
+        <v>44628</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6341,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6379,7 +6384,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50981-2023</t>
+          <t>A 50302-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6393,10 +6398,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45218</v>
+        <v>45216</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6408,13 +6413,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 50302-2023</t>
+          <t>A 53055-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45216</v>
+        <v>45611</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47265-2024</t>
+          <t>A 15112-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45586</v>
+        <v>44658</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6064-2025</t>
+          <t>A 3238-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45696</v>
+        <v>44946</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6676,7 +6676,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 59472-2023</t>
+          <t>A 31889-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45254</v>
+        <v>45118</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9530-2023</t>
+          <t>A 59472-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44981</v>
+        <v>45254</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52371-2025</t>
+          <t>A 9530-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45953</v>
+        <v>44981</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6895,7 +6895,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56305-2025</t>
+          <t>A 22443-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45974</v>
+        <v>45070</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6968,7 +6968,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36131-2024</t>
+          <t>A 54295-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45534</v>
+        <v>45232</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7041,7 +7041,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36532-2024</t>
+          <t>A 56331-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45537</v>
+        <v>45624</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31546-2022</t>
+          <t>A 30801-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7124,14 +7124,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44775</v>
+        <v>45112</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25694-2025</t>
+          <t>A 31546-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45803</v>
+        <v>44775</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7260,7 +7260,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47522-2024</t>
+          <t>A 36532-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45587</v>
+        <v>45537</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7289,13 +7289,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7338,7 +7333,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 65143-2023</t>
+          <t>A 30637-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7352,10 +7347,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45288</v>
+        <v>45112</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7368,7 +7363,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7411,7 +7406,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40774-2025</t>
+          <t>A 20600-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7425,10 +7420,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45897</v>
+        <v>46140</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7441,7 +7436,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.7</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7484,7 +7479,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25928-2023</t>
+          <t>A 52371-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7498,10 +7493,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45090</v>
+        <v>45953</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7514,7 +7509,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7557,7 +7552,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20598-2026</t>
+          <t>A 51564-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7571,10 +7566,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46140</v>
+        <v>45604</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7587,7 +7582,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7630,7 +7625,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20600-2026</t>
+          <t>A 25928-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7644,10 +7639,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46140</v>
+        <v>45090</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7660,7 +7655,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7703,7 +7698,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20782-2026</t>
+          <t>A 47522-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7717,10 +7712,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46141</v>
+        <v>45587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7732,8 +7727,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30628-2023</t>
+          <t>A 65143-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45112</v>
+        <v>45288</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30643-2023</t>
+          <t>A 56305-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45112</v>
+        <v>45974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 22834-2024</t>
+          <t>A 31746-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45448</v>
+        <v>45117</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7995,7 +7995,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41910-2024</t>
+          <t>A 31711-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45561</v>
+        <v>45117</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8068,7 +8068,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 67455-2021</t>
+          <t>A 31727-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44524</v>
+        <v>45117</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58093-2023</t>
+          <t>A 40774-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45248</v>
+        <v>45897</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.8</v>
+        <v>6.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54144-2022</t>
+          <t>A 20598-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44881</v>
+        <v>46140</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 50057-2023</t>
+          <t>A 51314-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8297,14 +8297,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45215</v>
+        <v>45219</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8360,7 +8360,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 46511-2023</t>
+          <t>A 25694-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45197</v>
+        <v>45803</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8433,7 +8433,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47279-2025</t>
+          <t>A 47980-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45930</v>
+        <v>45204</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8506,7 +8506,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48212-2025</t>
+          <t>A 8570-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45933</v>
+        <v>45709</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8579,7 +8579,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49269-2025</t>
+          <t>A 20782-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8593,10 +8593,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45938</v>
+        <v>46141</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 6653-2022</t>
+          <t>A 18337-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44602</v>
+        <v>45041</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8725,7 +8725,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 64207-2021</t>
+          <t>A 22541-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44510</v>
+        <v>45071</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8798,7 +8798,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2006-2024</t>
+          <t>A 47279-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45308</v>
+        <v>45930</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8871,7 +8871,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24368-2022</t>
+          <t>A 67455-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8885,10 +8885,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44726</v>
+        <v>44524</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8944,7 +8944,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 27103-2024</t>
+          <t>A 30628-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45471</v>
+        <v>45112</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9017,7 +9017,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 51613-2025</t>
+          <t>A 30643-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45951</v>
+        <v>45112</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9090,7 +9090,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 55159-2024</t>
+          <t>A 48212-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45621</v>
+        <v>45933</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9163,7 +9163,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52513-2025</t>
+          <t>A 49269-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9177,10 +9177,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45954</v>
+        <v>45938</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9236,7 +9236,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52511-2025</t>
+          <t>A 18615-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45954</v>
+        <v>45763</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9309,7 +9309,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52939-2025</t>
+          <t>A 31717-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45957</v>
+        <v>45117</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9382,7 +9382,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 38586-2023</t>
+          <t>A 31719-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9396,10 +9396,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45162</v>
+        <v>45117</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9455,7 +9455,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9159-2024</t>
+          <t>A 30800-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9469,10 +9469,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45358</v>
+        <v>45112</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9528,7 +9528,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31746-2023</t>
+          <t>A 24368-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9542,10 +9542,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45117</v>
+        <v>44726</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9601,7 +9601,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 63725-2023</t>
+          <t>A 30650-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9615,10 +9615,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45276</v>
+        <v>45112</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9674,7 +9674,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59613-2023</t>
+          <t>A 51613-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9688,10 +9688,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45254</v>
+        <v>45951</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9747,7 +9747,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 62986-2023</t>
+          <t>A 54289-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45272</v>
+        <v>44882</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9820,7 +9820,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59816-2021</t>
+          <t>A 52511-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9834,10 +9834,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44494</v>
+        <v>45954</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9893,7 +9893,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 30650-2023</t>
+          <t>A 52513-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9907,10 +9907,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45112</v>
+        <v>45954</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9966,7 +9966,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 30637-2023</t>
+          <t>A 1922-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9980,10 +9980,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45112</v>
+        <v>45308</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10039,7 +10039,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58137-2025</t>
+          <t>A 52939-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10053,10 +10053,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45982</v>
+        <v>45957</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10112,7 +10112,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58139-2025</t>
+          <t>A 5072-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10126,10 +10126,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45982</v>
+        <v>44958</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10202,7 +10202,7 @@
         <v>45288</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 60089-2025</t>
+          <t>A 56335-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10272,10 +10272,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45993</v>
+        <v>45624</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10331,7 +10331,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 60093-2025</t>
+          <t>A 43398-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45993</v>
+        <v>45568</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10404,7 +10404,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18613-2025</t>
+          <t>A 59517-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10418,10 +10418,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45763</v>
+        <v>45254</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 18614-2025</t>
+          <t>A 59816-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45763</v>
+        <v>44494</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>9.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10550,7 +10550,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60091-2025</t>
+          <t>A 58139-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45993</v>
+        <v>45982</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10623,7 +10623,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60092-2025</t>
+          <t>A 6745-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10633,14 +10633,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45993</v>
+        <v>44966</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10696,7 +10696,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59871-2025</t>
+          <t>A 58137-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45992</v>
+        <v>45982</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10769,7 +10769,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 59872-2025</t>
+          <t>A 1921-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10783,10 +10783,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45992</v>
+        <v>45308</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10842,7 +10842,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 54289-2022</t>
+          <t>A 42250-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10856,10 +10856,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44882</v>
+        <v>45180</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10915,7 +10915,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 60181-2025</t>
+          <t>A 59871-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45994</v>
+        <v>45992</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10988,7 +10988,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60946-2025</t>
+          <t>A 60091-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11002,10 +11002,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45999</v>
+        <v>45993</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11061,7 +11061,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 42250-2023</t>
+          <t>A 60092-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11075,10 +11075,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45180</v>
+        <v>45993</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11134,7 +11134,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 42256-2023</t>
+          <t>A 60089-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11148,10 +11148,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45180</v>
+        <v>45993</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11207,7 +11207,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1921-2024</t>
+          <t>A 60093-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45308</v>
+        <v>45993</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24965-2026</t>
+          <t>A 59872-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11294,10 +11294,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46174</v>
+        <v>45992</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31711-2023</t>
+          <t>A 60181-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11367,10 +11367,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45117</v>
+        <v>45994</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11426,7 +11426,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 31727-2023</t>
+          <t>A 60946-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45117</v>
+        <v>45999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11499,7 +11499,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11605-2024</t>
+          <t>A 11239-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45373</v>
+        <v>44992</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11572,7 +11572,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 10610-2025</t>
+          <t>A 18613-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45721</v>
+        <v>45763</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11645,7 +11645,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 64005-2025</t>
+          <t>A 18614-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11659,10 +11659,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46021</v>
+        <v>45763</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11718,7 +11718,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 53055-2024</t>
+          <t>A 31712-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11732,10 +11732,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45611</v>
+        <v>45117</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11791,7 +11791,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 2497-2026</t>
+          <t>A 31715-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46037</v>
+        <v>45117</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11864,7 +11864,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 4119-2026</t>
+          <t>A 31745-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46044</v>
+        <v>45117</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11893,13 +11893,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11942,7 +11937,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4587-2026</t>
+          <t>A 10610-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11956,10 +11951,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46048</v>
+        <v>45721</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11972,7 +11967,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12015,7 +12010,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4588-2026</t>
+          <t>A 64005-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12029,10 +12024,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46048</v>
+        <v>46021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12045,7 +12040,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12088,7 +12083,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 29658-2022</t>
+          <t>A 47264-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12102,10 +12097,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44754</v>
+        <v>45586</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12118,7 +12113,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12161,7 +12156,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 6071-2026</t>
+          <t>A 47265-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12175,10 +12170,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46052</v>
+        <v>45586</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12191,7 +12186,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12234,7 +12229,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 6074-2026</t>
+          <t>A 42483-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12248,10 +12243,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46052</v>
+        <v>45180</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12264,7 +12259,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12307,7 +12302,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6104-2026</t>
+          <t>A 24965-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12321,10 +12316,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46052</v>
+        <v>46174</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12337,7 +12332,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12380,7 +12375,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 6103-2026</t>
+          <t>A 6653-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12394,10 +12389,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46052</v>
+        <v>44602</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12410,7 +12405,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12453,7 +12448,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 57036-2024</t>
+          <t>A 2497-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12467,10 +12462,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45629</v>
+        <v>46037</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12483,7 +12478,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12526,7 +12521,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 26642-2026</t>
+          <t>A 4119-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12540,10 +12535,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46184</v>
+        <v>46044</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12555,8 +12550,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12599,7 +12599,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 7546-2026</t>
+          <t>A 4587-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12613,10 +12613,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46059</v>
+        <v>46048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12672,7 +12672,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 27248-2026</t>
+          <t>A 4588-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12686,10 +12686,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46188</v>
+        <v>46048</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 11584-2026</t>
+          <t>A 6071-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46084</v>
+        <v>46052</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12818,7 +12818,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 54287-2022</t>
+          <t>A 6074-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12832,10 +12832,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44882</v>
+        <v>46052</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12891,7 +12891,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 15112-2022</t>
+          <t>A 6104-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44658</v>
+        <v>46052</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12964,7 +12964,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 12503-2026</t>
+          <t>A 6103-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46090</v>
+        <v>46052</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13037,7 +13037,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 12469-2026</t>
+          <t>A 31724-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13051,10 +13051,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46090</v>
+        <v>45117</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13110,7 +13110,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 12879-2026</t>
+          <t>A 31726-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13120,14 +13120,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46092</v>
+        <v>45117</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13139,13 +13139,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13188,7 +13183,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27782-2026</t>
+          <t>A 17925-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13202,10 +13197,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46191</v>
+        <v>44683</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13218,7 +13213,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13261,7 +13256,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 13120-2026</t>
+          <t>A 21751-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13275,10 +13270,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46093</v>
+        <v>44708</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13291,7 +13286,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13334,7 +13329,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 13121-2026</t>
+          <t>A 7546-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13348,10 +13343,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46093</v>
+        <v>46059</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13364,7 +13359,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13407,7 +13402,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 58011-2022</t>
+          <t>A 7046-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13421,10 +13416,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44900</v>
+        <v>45701</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13437,7 +13432,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13480,7 +13475,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56452-2022</t>
+          <t>A 42256-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13494,10 +13489,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44893</v>
+        <v>45180</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13510,7 +13505,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13553,7 +13548,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 14111-2026</t>
+          <t>A 41910-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13567,10 +13562,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46099</v>
+        <v>45561</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13583,7 +13578,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13626,7 +13621,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 58010-2022</t>
+          <t>A 62986-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13640,10 +13635,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44900</v>
+        <v>45272</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13656,7 +13651,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13699,7 +13694,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 1922-2024</t>
+          <t>A 26642-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13713,10 +13708,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45308</v>
+        <v>46184</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13729,7 +13724,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13772,7 +13767,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 14545-2026</t>
+          <t>A 11584-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13782,14 +13777,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46100</v>
+        <v>46084</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13802,7 +13797,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13845,7 +13840,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 61334-2022</t>
+          <t>A 27248-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13859,10 +13854,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44915</v>
+        <v>46188</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13875,7 +13870,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13918,7 +13913,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 51564-2024</t>
+          <t>A 12469-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13932,10 +13927,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45604</v>
+        <v>46090</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13948,7 +13943,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13991,7 +13986,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 7046-2025</t>
+          <t>A 12503-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14005,10 +14000,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45701</v>
+        <v>46090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14021,7 +14016,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14064,7 +14059,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 30760-2023</t>
+          <t>A 13120-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14078,10 +14073,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45112</v>
+        <v>46093</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14094,7 +14089,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14137,7 +14132,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 30762-2023</t>
+          <t>A 13121-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14151,10 +14146,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45112</v>
+        <v>46093</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14167,7 +14162,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14210,7 +14205,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 56331-2024</t>
+          <t>A 12879-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14220,14 +14215,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45624</v>
+        <v>46092</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14239,8 +14234,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14283,7 +14283,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 51314-2023</t>
+          <t>A 27782-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14293,14 +14293,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45219</v>
+        <v>46191</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14356,7 +14356,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 3238-2023</t>
+          <t>A 59613-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14370,10 +14370,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44946</v>
+        <v>45254</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14429,7 +14429,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 19644-2026</t>
+          <t>A 14111-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14443,10 +14443,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46134</v>
+        <v>46099</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14502,7 +14502,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 30098-2026</t>
+          <t>A 14545-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14512,14 +14512,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46206</v>
+        <v>46100</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14575,7 +14575,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 12160-2024</t>
+          <t>A 58011-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45377</v>
+        <v>44900</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14648,7 +14648,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 54659-2022</t>
+          <t>A 56452-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14662,10 +14662,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44883</v>
+        <v>44893</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14721,7 +14721,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 31718-2023</t>
+          <t>A 58010-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14735,10 +14735,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45117</v>
+        <v>44900</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14794,7 +14794,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 43398-2024</t>
+          <t>A 61318-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14808,10 +14808,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45568</v>
+        <v>45264</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14867,7 +14867,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 54311-2022</t>
+          <t>A 55159-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14881,10 +14881,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44882</v>
+        <v>45621</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14940,7 +14940,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 22443-2023</t>
+          <t>A 19644-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14954,10 +14954,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45070</v>
+        <v>46134</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15013,7 +15013,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 36861-2026</t>
+          <t>A 6064-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15027,10 +15027,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46272</v>
+        <v>45696</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15086,7 +15086,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 60792-2022</t>
+          <t>A 36131-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15100,10 +15100,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44914</v>
+        <v>45534</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 61026-2022</t>
+          <t>A 30098-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15173,10 +15173,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44914</v>
+        <v>46206</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15232,7 +15232,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 47264-2024</t>
+          <t>A 54144-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15246,10 +15246,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45586</v>
+        <v>44881</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15305,7 +15305,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 31907-2026</t>
+          <t>A 2006-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15319,10 +15319,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46231</v>
+        <v>45308</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15334,13 +15334,8 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15383,7 +15378,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 22541-2023</t>
+          <t>A 61671-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15397,10 +15392,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45071</v>
+        <v>44917</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15413,7 +15408,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15456,7 +15451,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 21751-2022</t>
+          <t>A 51229-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15470,10 +15465,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44708</v>
+        <v>44868</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15486,7 +15481,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15529,7 +15524,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 1395-2024</t>
+          <t>A 61334-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15543,10 +15538,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45303</v>
+        <v>44915</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15559,7 +15554,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15602,7 +15597,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 2398-2024</t>
+          <t>A 31907-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15616,10 +15611,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45310</v>
+        <v>46231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15631,8 +15626,13 @@
           <t>BOLLEBYGD</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15692,7 +15692,7 @@
         <v>45112</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45112</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 30800-2023</t>
+          <t>A 30724-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15838,7 +15838,7 @@
         <v>45112</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15894,7 +15894,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28040-2024</t>
+          <t>A 54311-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15908,10 +15908,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45476</v>
+        <v>44882</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15967,7 +15967,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 38521-2026</t>
+          <t>A 56334-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15981,10 +15981,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46283</v>
+        <v>45624</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 38601-2026</t>
+          <t>A 61026-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16054,10 +16054,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46283</v>
+        <v>44914</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 47258-2025</t>
+          <t>A 63725-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16127,10 +16127,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45930</v>
+        <v>45276</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16186,7 +16186,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 18337-2023</t>
+          <t>A 9527-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16200,10 +16200,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45041</v>
+        <v>44981</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16259,7 +16259,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 11021-2022</t>
+          <t>A 30760-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16273,10 +16273,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44628</v>
+        <v>45112</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16332,7 +16332,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 11239-2023</t>
+          <t>A 30762-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16346,10 +16346,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44992</v>
+        <v>45112</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16405,7 +16405,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 39344-2026</t>
+          <t>A 38586-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16419,10 +16419,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46288</v>
+        <v>45162</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
     <row r